--- a/data/historico/semanas_313-317.xlsx
+++ b/data/historico/semanas_313-317.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$380</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Resumo Semanal'!$A$2:$AE$195</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Ranking'!$A$2:$E$51</definedName>
@@ -6287,19 +6287,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (67 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (18 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D7" s="44" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Equipe 1</t>
         </is>
       </c>
     </row>
@@ -6456,85 +6456,85 @@
       </c>
       <c r="D8" s="44" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Equipe 2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C9" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D9" s="44" t="inlineStr">
-        <is>
-          <t>Raquel Ortiz dos Santos</t>
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C10" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
         <is>
           <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C11" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D11" s="44" t="inlineStr">
-        <is>
-          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="44" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B12" s="44" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="C12" s="44" t="inlineStr">
@@ -6544,19 +6544,19 @@
       </c>
       <c r="D12" s="44" t="inlineStr">
         <is>
-          <t>Adriana de Jesus Saraiva</t>
+          <t>Equipe 4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B13" s="44" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="C13" s="44" t="inlineStr">
@@ -6566,19 +6566,19 @@
       </c>
       <c r="D13" s="44" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Equipe 2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B14" s="44" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="C14" s="44" t="inlineStr">
@@ -6588,85 +6588,85 @@
       </c>
       <c r="D14" s="44" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Equipe 3</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C15" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D15" s="44" t="inlineStr">
-        <is>
-          <t>Carlos Alberto Albiero</t>
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D15" s="43" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C16" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D16" s="44" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="inlineStr">
+        <is>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C17" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D17" s="44" t="inlineStr">
-        <is>
-          <t>Fabiana de Figueredo Vieira</t>
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="inlineStr">
+        <is>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="B18" s="44" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="C18" s="44" t="inlineStr">
@@ -6676,1134 +6676,56 @@
       </c>
       <c r="D18" s="44" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Equipe 3</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C19" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D19" s="44" t="inlineStr">
-        <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="45" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="45" t="inlineStr">
+        <is>
+          <t>Recuperação de Casas</t>
+        </is>
+      </c>
+      <c r="D19" s="45" t="inlineStr">
+        <is>
+          <t>Todos os agentes</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C20" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D20" s="44" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C21" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D21" s="44" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C22" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D22" s="44" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C23" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D23" s="44" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C24" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D24" s="44" t="inlineStr">
-        <is>
-          <t>Mateus Falcao de Souza</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C25" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D25" s="44" t="inlineStr">
-        <is>
-          <t>Bianca Afonso Narbaez</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C26" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D26" s="44" t="inlineStr">
-        <is>
-          <t>Teonilda Florentino Vieira</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C27" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D27" s="44" t="inlineStr">
-        <is>
-          <t>Gisele Olimpia Torres</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="43" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="43" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="C28" s="43" t="inlineStr">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D28" s="43" t="inlineStr">
-        <is>
-          <t>Geancarlos Ferreira Barrios</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="43" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="43" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
-        </is>
-      </c>
-      <c r="C29" s="43" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D29" s="43" t="inlineStr">
-        <is>
-          <t>Miglidiane Maciel Ajala</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="43" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="43" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="C30" s="43" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D30" s="43" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="44" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C31" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D31" s="44" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="44" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C32" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D32" s="44" t="inlineStr">
-        <is>
-          <t>Anderson Jose de Santana</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="44" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C33" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D33" s="44" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="44" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C34" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D34" s="44" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="44" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C35" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D35" s="44" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="44" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C36" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D36" s="44" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="44" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C37" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D37" s="44" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="44" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C38" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D38" s="44" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="44" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C39" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D39" s="44" t="inlineStr">
-        <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C40" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D40" s="44" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C41" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D41" s="44" t="inlineStr">
-        <is>
-          <t>Fabiana de Figueredo Vieira</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C42" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D42" s="44" t="inlineStr">
-        <is>
-          <t>Cicero Isrrael Sanabria</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C43" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D43" s="44" t="inlineStr">
-        <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C44" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D44" s="44" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C45" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D45" s="44" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C46" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D46" s="44" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C47" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D47" s="44" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C48" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D48" s="44" t="inlineStr">
-        <is>
-          <t>Mateus Falcao de Souza</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C49" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D49" s="44" t="inlineStr">
-        <is>
-          <t>Bianca Afonso Narbaez</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C50" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D50" s="44" t="inlineStr">
-        <is>
-          <t>Teonilda Florentino Vieira</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C51" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D51" s="44" t="inlineStr">
-        <is>
-          <t>Gisele Olimpia Torres</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C52" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D52" s="44" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C53" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D53" s="44" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C54" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D54" s="44" t="inlineStr">
-        <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C55" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D55" s="44" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C56" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D56" s="44" t="inlineStr">
+      <c r="D20" s="43" t="inlineStr">
         <is>
           <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C57" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D57" s="44" t="inlineStr">
-        <is>
-          <t>Naime Cristina Freitas</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C58" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D58" s="44" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="43" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="43" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
-        </is>
-      </c>
-      <c r="C59" s="43" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D59" s="43" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="43" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="43" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
-        </is>
-      </c>
-      <c r="C60" s="43" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D60" s="43" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="43" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="43" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="C61" s="43" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D61" s="43" t="inlineStr">
-        <is>
-          <t>Teonilda Florentino Vieira</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="44" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="44" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="C62" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D62" s="44" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="44" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="44" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="C63" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D63" s="44" t="inlineStr">
-        <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="44" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="44" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="C64" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D64" s="44" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="44" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="44" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="C65" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D65" s="44" t="inlineStr">
-        <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="44" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="44" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="C66" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D66" s="44" t="inlineStr">
-        <is>
-          <t>Naime Cristina Freitas</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="44" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="44" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="C67" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D67" s="44" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="45" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="45" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="C68" s="45" t="inlineStr">
-        <is>
-          <t>Recuperação de Casas</t>
-        </is>
-      </c>
-      <c r="D68" s="45" t="inlineStr">
-        <is>
-          <t>Todos os agentes</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="43" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="43" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="C69" s="43" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D69" s="43" t="inlineStr">
-        <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D69"/>
+  <autoFilter ref="A2:D20"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -33009,16 +31931,16 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Emerson de Carvalho Miranda</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Equipe Bloqueio</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>110.6</v>
+        <v>100</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -33033,16 +31955,16 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Emerson de Carvalho Miranda</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe Bloqueio</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>106.3</v>
+        <v>100</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -33057,7 +31979,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Robson Pavão Montania</t>
+          <t>Josoé de Oliveira</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -33066,7 +31988,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>103.2</v>
+        <v>100</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -33081,7 +32003,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Silvio de Aquino</t>
+          <t>Marcos Alcindo Insalbralde</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -33090,7 +32012,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>101.6</v>
+        <v>100</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -33105,7 +32027,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Josoé de Oliveira</t>
+          <t>Robson Pavão Montania</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -33114,7 +32036,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>101.4</v>
+        <v>100</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -33129,7 +32051,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Marcos Alcindo Insalbralde</t>
+          <t>Silvio de Aquino</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -33138,7 +32060,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>100.4</v>
+        <v>100</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -33177,16 +32099,16 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>96.02</v>
+        <v>96.8</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -33201,16 +32123,16 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Fabio Teodoro Alves Alexo</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Equipe Bloqueio</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>96</v>
+        <v>95.52</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -33225,7 +32147,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -33234,7 +32156,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>95.87</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -33249,16 +32171,16 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>95.8</v>
+        <v>94.62</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -33273,16 +32195,16 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Fabio Teodoro Alves Alexo</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe Bloqueio</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>95.56999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -33297,16 +32219,16 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>95.28</v>
+        <v>93.39</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -33321,16 +32243,16 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Anderson Salabarrieto</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe Bloqueio</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>94.94</v>
+        <v>93</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
@@ -33345,16 +32267,16 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Anderson Salabarrieto</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Equipe Bloqueio</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>93</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
@@ -33369,16 +32291,16 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>92.34999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -33393,16 +32315,16 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>90.8</v>
+        <v>90.2</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -33417,7 +32339,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -33426,7 +32348,7 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>90.2</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -33441,7 +32363,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -33450,7 +32372,7 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>89.93000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -33465,7 +32387,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -33474,7 +32396,7 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>87.8</v>
+        <v>87.78</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -33498,7 +32420,7 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>87</v>
+        <v>86.5</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -33522,7 +32444,7 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -33546,7 +32468,7 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>85.37</v>
+        <v>85.97</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
@@ -33570,7 +32492,7 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>84.7</v>
+        <v>84.13</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -33594,7 +32516,7 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>82.69</v>
+        <v>83.3</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -33618,7 +32540,7 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>80.51000000000001</v>
+        <v>80.16</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -33642,7 +32564,7 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>79.04000000000001</v>
+        <v>77.23</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -33666,7 +32588,7 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>76.73999999999999</v>
+        <v>76.31</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -33690,7 +32612,7 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>75.91</v>
+        <v>75.41</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -33705,16 +32627,16 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>74.33</v>
+        <v>70.7</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -33729,16 +32651,16 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>70.7</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -33753,16 +32675,16 @@
       </c>
       <c r="B34" s="41" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="C34" s="41" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D34" s="41" t="n">
-        <v>65.90000000000001</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="E34" s="41" t="inlineStr">
         <is>
@@ -33777,16 +32699,16 @@
       </c>
       <c r="B35" s="41" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C35" s="41" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D35" s="41" t="n">
-        <v>64.8</v>
+        <v>63.57</v>
       </c>
       <c r="E35" s="41" t="inlineStr">
         <is>
@@ -33801,16 +32723,16 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>59.46</v>
+        <v>57.97</v>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
@@ -33825,16 +32747,16 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>57.63</v>
+        <v>52.31</v>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
@@ -33849,16 +32771,16 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>54.2</v>
+        <v>49.2</v>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
@@ -33873,16 +32795,16 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>54.2</v>
+        <v>47.04</v>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
@@ -33897,16 +32819,16 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>49.84</v>
+        <v>46.2</v>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
@@ -33930,7 +32852,7 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>46.97</v>
+        <v>45.63</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
@@ -33954,7 +32876,7 @@
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>44.06</v>
+        <v>43.77</v>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
@@ -33978,7 +32900,7 @@
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>35.42</v>
+        <v>32.19</v>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
@@ -33993,16 +32915,16 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Carlos Alberto Albiero</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>29</v>
+        <v>24.1</v>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
@@ -34017,16 +32939,16 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Carlos Alberto Albiero</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>24.1</v>
+        <v>20.5</v>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
@@ -34050,7 +32972,7 @@
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>13.1</v>
+        <v>11.85</v>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
@@ -34074,7 +32996,7 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>10.61</v>
+        <v>9.27</v>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
@@ -34098,7 +33020,7 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>5.53</v>
+        <v>2.74</v>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
@@ -34122,7 +33044,7 @@
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>1.84</v>
+        <v>1.27</v>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
@@ -34262,7 +33184,7 @@
         <v>1</v>
       </c>
       <c r="F56" s="53" t="n">
-        <v>16.21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
@@ -34288,7 +33210,7 @@
         <v>0.5</v>
       </c>
       <c r="F57" s="54" t="n">
-        <v>-2.89</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="58">
@@ -34496,7 +33418,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="53" t="n">
-        <v>20.43</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
@@ -34522,7 +33444,7 @@
         <v>0.5</v>
       </c>
       <c r="F66" s="54" t="n">
-        <v>-0.79</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="67">
@@ -34730,7 +33652,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="53" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
@@ -34756,7 +33678,7 @@
         <v>0.5</v>
       </c>
       <c r="F75" s="54" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="76">
@@ -34990,7 +33912,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -35016,7 +33938,7 @@
         <v>0.5</v>
       </c>
       <c r="F85" s="54" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="86">
@@ -35094,7 +34016,7 @@
         <v>1</v>
       </c>
       <c r="F88" s="53" t="n">
-        <v>11.52</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89">
@@ -35120,7 +34042,7 @@
         <v>0.5</v>
       </c>
       <c r="F89" s="54" t="n">
-        <v>-5.24</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="90">
@@ -35302,7 +34224,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="53" t="n">
-        <v>13.89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97">
@@ -35328,7 +34250,7 @@
         <v>0.5</v>
       </c>
       <c r="F97" s="54" t="n">
-        <v>-4.05</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="98">
@@ -35562,7 +34484,7 @@
         <v>1</v>
       </c>
       <c r="F106" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -35588,7 +34510,7 @@
         <v>0.5</v>
       </c>
       <c r="F107" s="54" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="108">
@@ -35744,7 +34666,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="53" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114">
@@ -35770,7 +34692,7 @@
         <v>0.5</v>
       </c>
       <c r="F114" s="54" t="n">
-        <v>-2.75</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="115">
@@ -35978,7 +34900,7 @@
         <v>1</v>
       </c>
       <c r="F122" s="53" t="n">
-        <v>15.89</v>
+        <v>13</v>
       </c>
     </row>
     <row r="123">
@@ -36004,7 +34926,7 @@
         <v>0.5</v>
       </c>
       <c r="F123" s="54" t="n">
-        <v>-3.06</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="124">
@@ -36498,7 +35420,7 @@
         <v>1</v>
       </c>
       <c r="F142" s="53" t="n">
-        <v>16.26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="143">
@@ -36524,7 +35446,7 @@
         <v>0.5</v>
       </c>
       <c r="F143" s="54" t="n">
-        <v>-2.87</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="144">
@@ -36732,7 +35654,7 @@
         <v>1</v>
       </c>
       <c r="F151" s="53" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152">
@@ -36758,7 +35680,7 @@
         <v>0.5</v>
       </c>
       <c r="F152" s="54" t="n">
-        <v>-2.75</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="153">
@@ -36966,7 +35888,7 @@
         <v>1</v>
       </c>
       <c r="F160" s="53" t="n">
-        <v>13.62</v>
+        <v>13</v>
       </c>
     </row>
     <row r="161">
@@ -36992,7 +35914,7 @@
         <v>0.5</v>
       </c>
       <c r="F161" s="54" t="n">
-        <v>-4.19</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="162">
@@ -37252,7 +36174,7 @@
         <v>1</v>
       </c>
       <c r="F171" s="53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -37278,7 +36200,7 @@
         <v>0.5</v>
       </c>
       <c r="F172" s="54" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="173">
@@ -37356,7 +36278,7 @@
         <v>1</v>
       </c>
       <c r="F175" s="53" t="n">
-        <v>12.43</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176">
@@ -37382,7 +36304,7 @@
         <v>0.5</v>
       </c>
       <c r="F176" s="54" t="n">
-        <v>-4.78</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="177">
@@ -37824,7 +36746,7 @@
         <v>1</v>
       </c>
       <c r="F193" s="53" t="n">
-        <v>18.7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="194">
@@ -37850,7 +36772,7 @@
         <v>0.5</v>
       </c>
       <c r="F194" s="54" t="n">
-        <v>-1.65</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="195">
@@ -38032,7 +36954,7 @@
         <v>1</v>
       </c>
       <c r="F201" s="53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -38058,7 +36980,7 @@
         <v>0.5</v>
       </c>
       <c r="F202" s="54" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="203">
@@ -38188,7 +37110,7 @@
         <v>1</v>
       </c>
       <c r="F207" s="53" t="n">
-        <v>12.57</v>
+        <v>12</v>
       </c>
     </row>
     <row r="208">
@@ -38214,7 +37136,7 @@
         <v>0.5</v>
       </c>
       <c r="F208" s="54" t="n">
-        <v>-4.71</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="209">
@@ -38396,7 +37318,7 @@
         <v>0.5</v>
       </c>
       <c r="F215" s="54" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="216">
@@ -38500,7 +37422,7 @@
         <v>1</v>
       </c>
       <c r="F219" s="53" t="n">
-        <v>14.67</v>
+        <v>14</v>
       </c>
     </row>
     <row r="220">
@@ -38526,7 +37448,7 @@
         <v>0.5</v>
       </c>
       <c r="F220" s="54" t="n">
-        <v>-3.67</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="221">
@@ -38734,7 +37656,7 @@
         <v>1</v>
       </c>
       <c r="F228" s="53" t="n">
-        <v>16.26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="229">
@@ -38760,7 +37682,7 @@
         <v>0.5</v>
       </c>
       <c r="F229" s="54" t="n">
-        <v>-2.87</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="230">
@@ -38994,7 +37916,7 @@
         <v>1</v>
       </c>
       <c r="F238" s="53" t="n">
-        <v>15.53</v>
+        <v>12</v>
       </c>
     </row>
     <row r="239">
@@ -39020,7 +37942,7 @@
         <v>0.5</v>
       </c>
       <c r="F239" s="54" t="n">
-        <v>-3.24</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="240">
@@ -39202,7 +38124,7 @@
         <v>1</v>
       </c>
       <c r="F246" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -39228,7 +38150,7 @@
         <v>0.5</v>
       </c>
       <c r="F247" s="54" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="248">
@@ -39358,7 +38280,7 @@
         <v>1</v>
       </c>
       <c r="F252" s="53" t="n">
-        <v>19.07</v>
+        <v>13</v>
       </c>
     </row>
     <row r="253">
@@ -39384,7 +38306,7 @@
         <v>0.5</v>
       </c>
       <c r="F253" s="54" t="n">
-        <v>-1.47</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="254">
@@ -39566,7 +38488,7 @@
         <v>1</v>
       </c>
       <c r="F260" s="53" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="261">
@@ -39592,7 +38514,7 @@
         <v>0.5</v>
       </c>
       <c r="F261" s="54" t="n">
-        <v>-2.75</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="262">
@@ -39800,7 +38722,7 @@
         <v>1</v>
       </c>
       <c r="F269" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -39826,7 +38748,7 @@
         <v>0.5</v>
       </c>
       <c r="F270" s="54" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="271">
@@ -39982,7 +38904,7 @@
         <v>1</v>
       </c>
       <c r="F276" s="53" t="n">
-        <v>13.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="277">
@@ -40008,7 +38930,7 @@
         <v>0.5</v>
       </c>
       <c r="F277" s="54" t="n">
-        <v>-4.4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="278">
@@ -40190,7 +39112,7 @@
         <v>0.5</v>
       </c>
       <c r="F284" s="54" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="285">
@@ -40294,7 +39216,7 @@
         <v>1</v>
       </c>
       <c r="F288" s="53" t="n">
-        <v>15.71</v>
+        <v>15</v>
       </c>
     </row>
     <row r="289">
@@ -40320,7 +39242,7 @@
         <v>0.5</v>
       </c>
       <c r="F289" s="54" t="n">
-        <v>-3.14</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="290">
@@ -40606,7 +39528,7 @@
         <v>1</v>
       </c>
       <c r="F300" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
@@ -40632,7 +39554,7 @@
         <v>0.5</v>
       </c>
       <c r="F301" s="54" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="302">
@@ -40944,7 +39866,7 @@
         <v>1</v>
       </c>
       <c r="F313" s="53" t="n">
-        <v>18.62</v>
+        <v>11</v>
       </c>
     </row>
     <row r="314">
@@ -40970,7 +39892,7 @@
         <v>0.5</v>
       </c>
       <c r="F314" s="54" t="n">
-        <v>-1.69</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="315">
@@ -41178,7 +40100,7 @@
         <v>1</v>
       </c>
       <c r="F322" s="53" t="n">
-        <v>15.71</v>
+        <v>15</v>
       </c>
     </row>
     <row r="323">
@@ -41204,7 +40126,7 @@
         <v>0.5</v>
       </c>
       <c r="F323" s="54" t="n">
-        <v>-3.14</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="324">
@@ -41438,7 +40360,7 @@
         <v>1</v>
       </c>
       <c r="F332" s="53" t="n">
-        <v>16.82</v>
+        <v>13</v>
       </c>
     </row>
     <row r="333">
@@ -41464,7 +40386,7 @@
         <v>0.5</v>
       </c>
       <c r="F333" s="54" t="n">
-        <v>-2.59</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="334">
@@ -41672,7 +40594,7 @@
         <v>1</v>
       </c>
       <c r="F341" s="53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
@@ -41698,7 +40620,7 @@
         <v>0.5</v>
       </c>
       <c r="F342" s="54" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="343">
@@ -42010,7 +40932,7 @@
         <v>1</v>
       </c>
       <c r="F354" s="53" t="n">
-        <v>13.89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="355">
@@ -42036,7 +40958,7 @@
         <v>0.5</v>
       </c>
       <c r="F355" s="54" t="n">
-        <v>-4.05</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="356">
@@ -42218,7 +41140,7 @@
         <v>1</v>
       </c>
       <c r="F362" s="53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="363">
@@ -42244,7 +41166,7 @@
         <v>0.5</v>
       </c>
       <c r="F363" s="54" t="n">
-        <v>-5.5</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="364">
@@ -42712,7 +41634,7 @@
         <v>1</v>
       </c>
       <c r="F381" s="53" t="n">
-        <v>18.33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="382">
@@ -42738,7 +41660,7 @@
         <v>0.5</v>
       </c>
       <c r="F382" s="54" t="n">
-        <v>-1.83</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="383">
@@ -42894,7 +41816,7 @@
         <v>1</v>
       </c>
       <c r="F388" s="53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -42920,7 +41842,7 @@
         <v>0.5</v>
       </c>
       <c r="F389" s="54" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="390">
@@ -43258,7 +42180,7 @@
         <v>1</v>
       </c>
       <c r="F402" s="53" t="n">
-        <v>19.41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="403">
@@ -43284,7 +42206,7 @@
         <v>0.5</v>
       </c>
       <c r="F403" s="54" t="n">
-        <v>-1.29</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="404">
@@ -43388,7 +42310,7 @@
         <v>1</v>
       </c>
       <c r="F407" s="53" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="408">
@@ -43414,7 +42336,7 @@
         <v>0.5</v>
       </c>
       <c r="F408" s="54" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="409">
@@ -43570,7 +42492,7 @@
         <v>1</v>
       </c>
       <c r="F414" s="53" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="415">
@@ -43596,7 +42518,7 @@
         <v>0.5</v>
       </c>
       <c r="F415" s="54" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="416">
@@ -43726,7 +42648,7 @@
         <v>1</v>
       </c>
       <c r="F420" s="53" t="n">
-        <v>11.52</v>
+        <v>11</v>
       </c>
     </row>
     <row r="421">
@@ -43752,7 +42674,7 @@
         <v>0.5</v>
       </c>
       <c r="F421" s="54" t="n">
-        <v>-5.24</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="422">
@@ -43960,7 +42882,7 @@
         <v>1</v>
       </c>
       <c r="F429" s="53" t="n">
-        <v>14.67</v>
+        <v>14</v>
       </c>
     </row>
     <row r="430">
@@ -43986,7 +42908,7 @@
         <v>0.5</v>
       </c>
       <c r="F430" s="54" t="n">
-        <v>-3.67</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="431">
@@ -44142,7 +43064,7 @@
         <v>1</v>
       </c>
       <c r="F436" s="53" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="437">
@@ -44168,7 +43090,7 @@
         <v>0.5</v>
       </c>
       <c r="F437" s="54" t="n">
-        <v>-2.75</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="438">

--- a/data/historico/semanas_313-317.xlsx
+++ b/data/historico/semanas_313-317.xlsx
@@ -6512,7 +6512,7 @@
       </c>
       <c r="B11" s="43" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="C11" s="43" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="D11" s="43" t="inlineStr">
         <is>
-          <t>Adriana de Jesus Saraiva</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="B12" s="43" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C12" s="43" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="D12" s="43" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Adriana de Jesus Saraiva</t>
         </is>
       </c>
     </row>

--- a/data/historico/semanas_313-317.xlsx
+++ b/data/historico/semanas_313-317.xlsx
@@ -6918,7 +6918,7 @@
       </c>
       <c r="D29" s="43" t="inlineStr">
         <is>
-          <t>Agente_86</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D31" s="43" t="inlineStr">
         <is>
-          <t>Agente_86</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="B53" s="43" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="C53" s="43" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="B56" s="43" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="C56" s="43" t="inlineStr">

--- a/data/historico/semanas_313-317.xlsx
+++ b/data/historico/semanas_313-317.xlsx
@@ -33174,193 +33174,193 @@
       <c r="F21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Adriana de Jesus Saraiva</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="5" t="n">
         <v>89.38</v>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Selba Ramona Afonso</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="5" t="n">
         <v>87.78</v>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Tania Maria Montania</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="5" t="n">
         <v>87.68000000000001</v>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="5" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="5" t="n">
         <v>87.41</v>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="5" t="n">
         <v>87.28</v>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="5" t="n">
         <v>86.5</v>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="5" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F29" s="2" t="n"/>
@@ -33462,73 +33462,73 @@
       <c r="F33" s="2" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="41" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="41" t="inlineStr">
         <is>
           <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="41" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D34" s="41" t="n">
         <v>72.37</v>
       </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
+      <c r="E34" s="41" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
         </is>
       </c>
       <c r="F34" s="2" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="41" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="41" t="inlineStr">
         <is>
           <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="41" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D35" s="41" t="n">
         <v>71.17</v>
       </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
+      <c r="E35" s="41" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
         </is>
       </c>
       <c r="F35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="41" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="41" t="inlineStr">
         <is>
           <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="41" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D36" s="5" t="n">
+      <c r="D36" s="41" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
+      <c r="E36" s="41" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
         </is>
       </c>
       <c r="F36" s="2" t="n"/>

--- a/data/historico/semanas_313-317.xlsx
+++ b/data/historico/semanas_313-317.xlsx
@@ -7436,7 +7436,7 @@
       </c>
       <c r="B53" s="43" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C53" s="43" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="B56" s="43" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C56" s="43" t="inlineStr">

--- a/data/historico/semanas_313-317.xlsx
+++ b/data/historico/semanas_313-317.xlsx
@@ -31,8 +31,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$216</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$246</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Resumo Semanal'!$A$2:$AE$195</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Ranking'!$A$2:$E$51</definedName>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6299,7 +6299,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (54 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (50 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="B5" s="43" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="C5" s="43" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D5" s="43" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D6" s="43" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="B7" s="43" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C7" s="43" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D7" s="43" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="B8" s="43" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C8" s="43" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D8" s="43" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="D9" s="43" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="B10" s="43" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C10" s="43" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="D10" s="43" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="B12" s="43" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="C12" s="43" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="D12" s="43" t="inlineStr">
         <is>
-          <t>Adriana de Jesus Saraiva</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="B13" s="43" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="C13" s="43" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="D13" s="43" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="D14" s="43" t="inlineStr">
         <is>
-          <t>Carlos Alberto Albiero</t>
+          <t>Adriana de Jesus Saraiva</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="B16" s="43" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C16" s="43" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="D16" s="43" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Carlos Alberto Albiero</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="D17" s="43" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="B18" s="43" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C18" s="43" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="D18" s="43" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="B19" s="43" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C19" s="43" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="D19" s="43" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6720,7 @@
       </c>
       <c r="D20" s="43" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="B21" s="43" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C21" s="43" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="D21" s="43" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="D22" s="43" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="D23" s="43" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="D24" s="43" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="D25" s="43" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="D26" s="43" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="D27" s="43" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="D28" s="43" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="B29" s="43" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C29" s="43" t="inlineStr">
@@ -6918,234 +6918,234 @@
       </c>
       <c r="D29" s="43" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="43" t="inlineStr">
+      <c r="A30" s="44" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="43" t="inlineStr">
-        <is>
-          <t>29/07/2026</t>
-        </is>
-      </c>
-      <c r="C30" s="43" t="inlineStr">
+      <c r="B30" s="44" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="C30" s="44" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D30" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="44" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="44" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="C31" s="44" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D31" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="C32" s="43" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D30" s="43" t="inlineStr">
-        <is>
-          <t>Kátia Cilene Silveira Machado</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="43" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="43" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="C31" s="43" t="inlineStr">
+      <c r="D32" s="43" t="inlineStr">
+        <is>
+          <t>Geancarlos Ferreira Barrios</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="C33" s="43" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D31" s="43" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C32" s="44" t="inlineStr">
+      <c r="D33" s="43" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="44" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="C34" s="44" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
         </is>
       </c>
-      <c r="D32" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="44" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="C33" s="44" t="inlineStr">
+      <c r="D34" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="44" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="44" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="C35" s="44" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
         </is>
       </c>
-      <c r="D33" s="44" t="inlineStr">
+      <c r="D35" s="44" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="43" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="43" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="C34" s="43" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="44" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="44" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="C36" s="44" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D36" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="C37" s="43" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D34" s="43" t="inlineStr">
-        <is>
-          <t>Geancarlos Ferreira Barrios</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="43" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="43" t="inlineStr">
+      <c r="D37" s="43" t="inlineStr">
+        <is>
+          <t>Adriana de Jesus Saraiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="43" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="43" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="C38" s="43" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="inlineStr">
+        <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="43" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
       </c>
-      <c r="C35" s="43" t="inlineStr">
+      <c r="C39" s="43" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D35" s="43" t="inlineStr">
-        <is>
-          <t>Miglidiane Maciel Ajala</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="43" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="43" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="C36" s="43" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D36" s="43" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="44" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C37" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D37" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C38" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D38" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="44" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C39" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D39" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
+      <c r="D39" s="43" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="43" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="B40" s="43" t="inlineStr">
@@ -7160,19 +7160,19 @@
       </c>
       <c r="D40" s="43" t="inlineStr">
         <is>
-          <t>Adriana de Jesus Saraiva</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="43" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="B41" s="43" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C41" s="43" t="inlineStr">
@@ -7182,19 +7182,19 @@
       </c>
       <c r="D41" s="43" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="43" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="B42" s="43" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="C42" s="43" t="inlineStr">
@@ -7204,19 +7204,19 @@
       </c>
       <c r="D42" s="43" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="43" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="B43" s="43" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="C43" s="43" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="D43" s="43" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="B44" s="43" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="C44" s="43" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="D44" s="43" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
     </row>
@@ -7270,73 +7270,73 @@
       </c>
       <c r="D45" s="43" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="43" t="inlineStr">
+      <c r="A46" s="44" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="B46" s="43" t="inlineStr">
-        <is>
-          <t>12/08/2026</t>
-        </is>
-      </c>
-      <c r="C46" s="43" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D46" s="43" t="inlineStr">
-        <is>
-          <t>Teonilda Florentino Vieira</t>
+      <c r="B46" s="44" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="C46" s="44" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D46" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="43" t="inlineStr">
+      <c r="A47" s="44" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="B47" s="43" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="C47" s="43" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D47" s="43" t="inlineStr">
-        <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+      <c r="B47" s="44" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="C47" s="44" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D47" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="43" t="inlineStr">
+      <c r="A48" s="44" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="B48" s="43" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="C48" s="43" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D48" s="43" t="inlineStr">
-        <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+      <c r="B48" s="44" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="C48" s="44" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D48" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
         </is>
       </c>
     </row>
@@ -7358,19 +7358,19 @@
       </c>
       <c r="D49" s="44" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="B50" s="44" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="C50" s="44" t="inlineStr">
@@ -7380,144 +7380,56 @@
       </c>
       <c r="D50" s="44" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="44" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="44" t="inlineStr">
-        <is>
-          <t>24/07/2026</t>
-        </is>
-      </c>
-      <c r="C51" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D51" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
+      <c r="A51" s="45" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="45" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="C51" s="45" t="inlineStr">
+        <is>
+          <t>Recuperação de Casas</t>
+        </is>
+      </c>
+      <c r="D51" s="45" t="inlineStr">
+        <is>
+          <t>Todos os agentes</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="44" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="44" t="inlineStr">
-        <is>
-          <t>24/07/2026</t>
-        </is>
-      </c>
-      <c r="C52" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D52" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="43" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="43" t="inlineStr">
+      <c r="A52" s="43" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="43" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="C53" s="43" t="inlineStr">
+      <c r="C52" s="43" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D53" s="43" t="inlineStr">
-        <is>
-          <t>Teonilda Florentino Vieira</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="44" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="44" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="C54" s="44" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D54" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="45" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="45" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="C55" s="45" t="inlineStr">
-        <is>
-          <t>Recuperação de Casas</t>
-        </is>
-      </c>
-      <c r="D55" s="45" t="inlineStr">
-        <is>
-          <t>Todos os agentes</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="43" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="43" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C56" s="43" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D56" s="43" t="inlineStr">
+      <c r="D52" s="43" t="inlineStr">
         <is>
           <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D56"/>
+  <autoFilter ref="A2:D52"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -33558,25 +33470,25 @@
       <c r="F37" s="2" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="n">
+      <c r="A38" s="41" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>57.97</v>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
+      <c r="B38" s="41" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D38" s="41" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="E38" s="41" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
         </is>
       </c>
       <c r="F38" s="2" t="n"/>
@@ -33587,16 +33499,16 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>52.57</v>
+        <v>57.97</v>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
@@ -33611,16 +33523,16 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>52.2</v>
+        <v>52.57</v>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
@@ -43274,43 +43186,43 @@
       </c>
       <c r="C414" s="53" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D414" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E414" s="53" t="n">
+        <v>5</v>
+      </c>
+      <c r="F414" s="53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="53" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B415" s="53" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C415" s="53" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D414" s="53" t="n">
+      <c r="D415" s="53" t="n">
         <v>9</v>
       </c>
-      <c r="E414" s="53" t="n">
+      <c r="E415" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="F414" s="53" t="n">
+      <c r="F415" s="53" t="n">
         <v>9</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" s="54" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B415" s="54" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C415" s="54" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D415" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="E415" s="54" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F415" s="54" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="416">
@@ -43326,17 +43238,17 @@
       </c>
       <c r="C416" s="54" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D416" s="54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E416" s="54" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F416" s="54" t="n">
-        <v>-2.4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="417">
@@ -43352,17 +43264,17 @@
       </c>
       <c r="C417" s="54" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D417" s="54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E417" s="54" t="n">
         <v>0.3</v>
       </c>
       <c r="F417" s="54" t="n">
-        <v>-4.2</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="418">
@@ -43378,17 +43290,17 @@
       </c>
       <c r="C418" s="54" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D418" s="54" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E418" s="54" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F418" s="54" t="n">
-        <v>-3</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="419">
@@ -69962,7 +69874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G246"/>
+  <dimension ref="A1:G245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -69977,7 +69889,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (244 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (243 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -72056,31 +71968,31 @@
     </row>
     <row r="61">
       <c r="A61" s="40" t="n">
-        <v>116</v>
+        <v>2917</v>
       </c>
       <c r="B61" s="40" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C61" s="40" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D61" s="40" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="E61" s="40" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F61" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G61" s="40" t="inlineStr">
@@ -72091,11 +72003,11 @@
     </row>
     <row r="62">
       <c r="A62" s="40" t="n">
-        <v>2917</v>
+        <v>125</v>
       </c>
       <c r="B62" s="40" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C62" s="40" t="inlineStr">
@@ -72126,11 +72038,11 @@
     </row>
     <row r="63">
       <c r="A63" s="40" t="n">
-        <v>125</v>
+        <v>2030</v>
       </c>
       <c r="B63" s="40" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C63" s="40" t="inlineStr">
@@ -72161,11 +72073,11 @@
     </row>
     <row r="64">
       <c r="A64" s="40" t="n">
-        <v>2030</v>
+        <v>134</v>
       </c>
       <c r="B64" s="40" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C64" s="40" t="inlineStr">
@@ -72196,11 +72108,11 @@
     </row>
     <row r="65">
       <c r="A65" s="40" t="n">
-        <v>134</v>
+        <v>3035</v>
       </c>
       <c r="B65" s="40" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C65" s="40" t="inlineStr">
@@ -72231,11 +72143,11 @@
     </row>
     <row r="66">
       <c r="A66" s="40" t="n">
-        <v>3035</v>
+        <v>81</v>
       </c>
       <c r="B66" s="40" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C66" s="40" t="inlineStr">
@@ -72266,11 +72178,11 @@
     </row>
     <row r="67">
       <c r="A67" s="40" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="B67" s="40" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C67" s="40" t="inlineStr">
@@ -72301,11 +72213,11 @@
     </row>
     <row r="68">
       <c r="A68" s="40" t="n">
-        <v>142</v>
+        <v>2917</v>
       </c>
       <c r="B68" s="40" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C68" s="40" t="inlineStr">
@@ -72315,12 +72227,12 @@
       </c>
       <c r="D68" s="40" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="E68" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F68" s="40" t="inlineStr">
@@ -72336,11 +72248,11 @@
     </row>
     <row r="69">
       <c r="A69" s="40" t="n">
-        <v>2917</v>
+        <v>125</v>
       </c>
       <c r="B69" s="40" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C69" s="40" t="inlineStr">
@@ -72371,11 +72283,11 @@
     </row>
     <row r="70">
       <c r="A70" s="40" t="n">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="B70" s="40" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C70" s="40" t="inlineStr">
@@ -72406,11 +72318,11 @@
     </row>
     <row r="71">
       <c r="A71" s="40" t="n">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="B71" s="40" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C71" s="40" t="inlineStr">
@@ -72441,11 +72353,11 @@
     </row>
     <row r="72">
       <c r="A72" s="40" t="n">
-        <v>151</v>
+        <v>3127</v>
       </c>
       <c r="B72" s="40" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C72" s="40" t="inlineStr">
@@ -72476,11 +72388,11 @@
     </row>
     <row r="73">
       <c r="A73" s="40" t="n">
-        <v>3127</v>
+        <v>2030</v>
       </c>
       <c r="B73" s="40" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C73" s="40" t="inlineStr">
@@ -72511,11 +72423,11 @@
     </row>
     <row r="74">
       <c r="A74" s="40" t="n">
-        <v>2030</v>
+        <v>134</v>
       </c>
       <c r="B74" s="40" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C74" s="40" t="inlineStr">
@@ -72546,11 +72458,11 @@
     </row>
     <row r="75">
       <c r="A75" s="40" t="n">
-        <v>134</v>
+        <v>3035</v>
       </c>
       <c r="B75" s="40" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C75" s="40" t="inlineStr">
@@ -72581,11 +72493,11 @@
     </row>
     <row r="76">
       <c r="A76" s="40" t="n">
-        <v>3035</v>
+        <v>81</v>
       </c>
       <c r="B76" s="40" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C76" s="40" t="inlineStr">
@@ -72616,11 +72528,11 @@
     </row>
     <row r="77">
       <c r="A77" s="40" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="B77" s="40" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C77" s="40" t="inlineStr">
@@ -72651,11 +72563,11 @@
     </row>
     <row r="78">
       <c r="A78" s="40" t="n">
-        <v>142</v>
+        <v>2917</v>
       </c>
       <c r="B78" s="40" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C78" s="40" t="inlineStr">
@@ -72675,7 +72587,7 @@
       </c>
       <c r="F78" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G78" s="40" t="inlineStr">
@@ -72686,11 +72598,11 @@
     </row>
     <row r="79">
       <c r="A79" s="40" t="n">
-        <v>2917</v>
+        <v>125</v>
       </c>
       <c r="B79" s="40" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C79" s="40" t="inlineStr">
@@ -72721,11 +72633,11 @@
     </row>
     <row r="80">
       <c r="A80" s="40" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B80" s="40" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="C80" s="40" t="inlineStr">
@@ -72756,11 +72668,11 @@
     </row>
     <row r="81">
       <c r="A81" s="40" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B81" s="40" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C81" s="40" t="inlineStr">
@@ -72791,11 +72703,11 @@
     </row>
     <row r="82">
       <c r="A82" s="40" t="n">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="B82" s="40" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C82" s="40" t="inlineStr">
@@ -72826,11 +72738,11 @@
     </row>
     <row r="83">
       <c r="A83" s="40" t="n">
-        <v>151</v>
+        <v>3127</v>
       </c>
       <c r="B83" s="40" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C83" s="40" t="inlineStr">
@@ -72861,11 +72773,11 @@
     </row>
     <row r="84">
       <c r="A84" s="40" t="n">
-        <v>3127</v>
+        <v>2030</v>
       </c>
       <c r="B84" s="40" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C84" s="40" t="inlineStr">
@@ -72896,11 +72808,11 @@
     </row>
     <row r="85">
       <c r="A85" s="40" t="n">
-        <v>2030</v>
+        <v>134</v>
       </c>
       <c r="B85" s="40" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C85" s="40" t="inlineStr">
@@ -72931,11 +72843,11 @@
     </row>
     <row r="86">
       <c r="A86" s="40" t="n">
-        <v>134</v>
+        <v>3035</v>
       </c>
       <c r="B86" s="40" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C86" s="40" t="inlineStr">
@@ -72966,11 +72878,11 @@
     </row>
     <row r="87">
       <c r="A87" s="40" t="n">
-        <v>3035</v>
+        <v>81</v>
       </c>
       <c r="B87" s="40" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C87" s="40" t="inlineStr">
@@ -73001,11 +72913,11 @@
     </row>
     <row r="88">
       <c r="A88" s="40" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="B88" s="40" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C88" s="40" t="inlineStr">
@@ -73036,11 +72948,11 @@
     </row>
     <row r="89">
       <c r="A89" s="40" t="n">
-        <v>142</v>
+        <v>2917</v>
       </c>
       <c r="B89" s="40" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C89" s="40" t="inlineStr">
@@ -73050,17 +72962,17 @@
       </c>
       <c r="D89" s="40" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="E89" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F89" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G89" s="40" t="inlineStr">
@@ -73071,11 +72983,11 @@
     </row>
     <row r="90">
       <c r="A90" s="40" t="n">
-        <v>2917</v>
+        <v>125</v>
       </c>
       <c r="B90" s="40" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C90" s="40" t="inlineStr">
@@ -73106,11 +73018,11 @@
     </row>
     <row r="91">
       <c r="A91" s="40" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B91" s="40" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="C91" s="40" t="inlineStr">
@@ -73141,11 +73053,11 @@
     </row>
     <row r="92">
       <c r="A92" s="40" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B92" s="40" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C92" s="40" t="inlineStr">
@@ -73176,11 +73088,11 @@
     </row>
     <row r="93">
       <c r="A93" s="40" t="n">
-        <v>99</v>
+        <v>3127</v>
       </c>
       <c r="B93" s="40" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C93" s="40" t="inlineStr">
@@ -73211,11 +73123,11 @@
     </row>
     <row r="94">
       <c r="A94" s="40" t="n">
-        <v>3127</v>
+        <v>465</v>
       </c>
       <c r="B94" s="40" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C94" s="40" t="inlineStr">
@@ -73246,11 +73158,11 @@
     </row>
     <row r="95">
       <c r="A95" s="40" t="n">
-        <v>465</v>
+        <v>134</v>
       </c>
       <c r="B95" s="40" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C95" s="40" t="inlineStr">
@@ -73281,11 +73193,11 @@
     </row>
     <row r="96">
       <c r="A96" s="40" t="n">
-        <v>134</v>
+        <v>3035</v>
       </c>
       <c r="B96" s="40" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C96" s="40" t="inlineStr">
@@ -73316,11 +73228,11 @@
     </row>
     <row r="97">
       <c r="A97" s="40" t="n">
-        <v>3035</v>
+        <v>81</v>
       </c>
       <c r="B97" s="40" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C97" s="40" t="inlineStr">
@@ -73351,11 +73263,11 @@
     </row>
     <row r="98">
       <c r="A98" s="40" t="n">
-        <v>81</v>
+        <v>3035</v>
       </c>
       <c r="B98" s="40" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C98" s="40" t="inlineStr">
@@ -73375,7 +73287,7 @@
       </c>
       <c r="F98" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G98" s="40" t="inlineStr">
@@ -73386,11 +73298,11 @@
     </row>
     <row r="99">
       <c r="A99" s="40" t="n">
-        <v>3035</v>
+        <v>125</v>
       </c>
       <c r="B99" s="40" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C99" s="40" t="inlineStr">
@@ -73400,17 +73312,17 @@
       </c>
       <c r="D99" s="40" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E99" s="40" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F99" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G99" s="40" t="inlineStr">
@@ -73421,11 +73333,11 @@
     </row>
     <row r="100">
       <c r="A100" s="40" t="n">
-        <v>125</v>
+        <v>2030</v>
       </c>
       <c r="B100" s="40" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C100" s="40" t="inlineStr">
@@ -73456,11 +73368,11 @@
     </row>
     <row r="101">
       <c r="A101" s="40" t="n">
-        <v>2030</v>
+        <v>81</v>
       </c>
       <c r="B101" s="40" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C101" s="40" t="inlineStr">
@@ -73491,11 +73403,11 @@
     </row>
     <row r="102">
       <c r="A102" s="40" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="B102" s="40" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C102" s="40" t="inlineStr">
@@ -73526,11 +73438,11 @@
     </row>
     <row r="103">
       <c r="A103" s="40" t="n">
-        <v>142</v>
+        <v>2030</v>
       </c>
       <c r="B103" s="40" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C103" s="40" t="inlineStr">
@@ -73550,7 +73462,7 @@
       </c>
       <c r="F103" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G103" s="40" t="inlineStr">
@@ -73561,11 +73473,11 @@
     </row>
     <row r="104">
       <c r="A104" s="40" t="n">
-        <v>2030</v>
+        <v>142</v>
       </c>
       <c r="B104" s="40" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C104" s="40" t="inlineStr">
@@ -73596,11 +73508,11 @@
     </row>
     <row r="105">
       <c r="A105" s="40" t="n">
-        <v>142</v>
+        <v>3035</v>
       </c>
       <c r="B105" s="40" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C105" s="40" t="inlineStr">
@@ -73610,17 +73522,17 @@
       </c>
       <c r="D105" s="40" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E105" s="40" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F105" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G105" s="40" t="inlineStr">
@@ -73631,11 +73543,11 @@
     </row>
     <row r="106">
       <c r="A106" s="40" t="n">
-        <v>3035</v>
+        <v>142</v>
       </c>
       <c r="B106" s="40" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C106" s="40" t="inlineStr">
@@ -73655,7 +73567,7 @@
       </c>
       <c r="F106" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G106" s="40" t="inlineStr">
@@ -73666,11 +73578,11 @@
     </row>
     <row r="107">
       <c r="A107" s="40" t="n">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="B107" s="40" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C107" s="40" t="inlineStr">
@@ -73680,17 +73592,17 @@
       </c>
       <c r="D107" s="40" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E107" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F107" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G107" s="40" t="inlineStr">
@@ -73701,11 +73613,11 @@
     </row>
     <row r="108">
       <c r="A108" s="40" t="n">
-        <v>125</v>
+        <v>3035</v>
       </c>
       <c r="B108" s="40" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C108" s="40" t="inlineStr">
@@ -73736,11 +73648,11 @@
     </row>
     <row r="109">
       <c r="A109" s="40" t="n">
-        <v>3035</v>
+        <v>125</v>
       </c>
       <c r="B109" s="40" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C109" s="40" t="inlineStr">
@@ -73760,7 +73672,7 @@
       </c>
       <c r="F109" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G109" s="40" t="inlineStr">
@@ -73771,11 +73683,11 @@
     </row>
     <row r="110">
       <c r="A110" s="40" t="n">
-        <v>125</v>
+        <v>3035</v>
       </c>
       <c r="B110" s="40" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C110" s="40" t="inlineStr">
@@ -73785,17 +73697,17 @@
       </c>
       <c r="D110" s="40" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="E110" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F110" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G110" s="40" t="inlineStr">
@@ -73830,7 +73742,7 @@
       </c>
       <c r="F111" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G111" s="40" t="inlineStr">
@@ -73841,11 +73753,11 @@
     </row>
     <row r="112">
       <c r="A112" s="40" t="n">
-        <v>3035</v>
+        <v>115</v>
       </c>
       <c r="B112" s="40" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="C112" s="40" t="inlineStr">
@@ -73855,17 +73767,17 @@
       </c>
       <c r="D112" s="40" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="E112" s="40" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F112" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G112" s="40" t="inlineStr">
@@ -73876,11 +73788,11 @@
     </row>
     <row r="113">
       <c r="A113" s="40" t="n">
-        <v>115</v>
+        <v>3127</v>
       </c>
       <c r="B113" s="40" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C113" s="40" t="inlineStr">
@@ -73890,17 +73802,17 @@
       </c>
       <c r="D113" s="40" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E113" s="40" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F113" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G113" s="40" t="inlineStr">
@@ -73911,11 +73823,11 @@
     </row>
     <row r="114">
       <c r="A114" s="40" t="n">
-        <v>3127</v>
+        <v>142</v>
       </c>
       <c r="B114" s="40" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C114" s="40" t="inlineStr">
@@ -73946,11 +73858,11 @@
     </row>
     <row r="115">
       <c r="A115" s="40" t="n">
-        <v>142</v>
+        <v>3035</v>
       </c>
       <c r="B115" s="40" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C115" s="40" t="inlineStr">
@@ -73960,17 +73872,17 @@
       </c>
       <c r="D115" s="40" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E115" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F115" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G115" s="40" t="inlineStr">
@@ -74005,7 +73917,7 @@
       </c>
       <c r="F116" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G116" s="40" t="inlineStr">
@@ -74016,11 +73928,11 @@
     </row>
     <row r="117">
       <c r="A117" s="40" t="n">
-        <v>3035</v>
+        <v>134</v>
       </c>
       <c r="B117" s="40" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C117" s="40" t="inlineStr">
@@ -74030,12 +73942,12 @@
       </c>
       <c r="D117" s="40" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E117" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F117" s="40" t="inlineStr">
@@ -74051,11 +73963,11 @@
     </row>
     <row r="118">
       <c r="A118" s="40" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B118" s="40" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C118" s="40" t="inlineStr">
@@ -74065,12 +73977,12 @@
       </c>
       <c r="D118" s="40" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="E118" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F118" s="40" t="inlineStr">
@@ -74086,11 +73998,11 @@
     </row>
     <row r="119">
       <c r="A119" s="40" t="n">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="B119" s="40" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C119" s="40" t="inlineStr">
@@ -74100,17 +74012,17 @@
       </c>
       <c r="D119" s="40" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="E119" s="40" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F119" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G119" s="40" t="inlineStr">
@@ -74121,11 +74033,11 @@
     </row>
     <row r="120">
       <c r="A120" s="40" t="n">
-        <v>99</v>
+        <v>2030</v>
       </c>
       <c r="B120" s="40" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C120" s="40" t="inlineStr">
@@ -74156,11 +74068,11 @@
     </row>
     <row r="121">
       <c r="A121" s="40" t="n">
-        <v>2030</v>
+        <v>134</v>
       </c>
       <c r="B121" s="40" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C121" s="40" t="inlineStr">
@@ -74191,11 +74103,11 @@
     </row>
     <row r="122">
       <c r="A122" s="40" t="n">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="B122" s="40" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C122" s="40" t="inlineStr">
@@ -74226,11 +74138,11 @@
     </row>
     <row r="123">
       <c r="A123" s="40" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="B123" s="40" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C123" s="40" t="inlineStr">
@@ -74261,26 +74173,26 @@
     </row>
     <row r="124">
       <c r="A124" s="40" t="n">
-        <v>142</v>
+        <v>2951</v>
       </c>
       <c r="B124" s="40" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C124" s="40" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D124" s="40" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="E124" s="40" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F124" s="40" t="inlineStr">
@@ -74296,11 +74208,11 @@
     </row>
     <row r="125">
       <c r="A125" s="40" t="n">
-        <v>2951</v>
+        <v>2918</v>
       </c>
       <c r="B125" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C125" s="40" t="inlineStr">
@@ -74331,11 +74243,11 @@
     </row>
     <row r="126">
       <c r="A126" s="40" t="n">
-        <v>2918</v>
+        <v>120</v>
       </c>
       <c r="B126" s="40" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C126" s="40" t="inlineStr">
@@ -74366,11 +74278,11 @@
     </row>
     <row r="127">
       <c r="A127" s="40" t="n">
-        <v>120</v>
+        <v>3038</v>
       </c>
       <c r="B127" s="40" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C127" s="40" t="inlineStr">
@@ -74401,11 +74313,11 @@
     </row>
     <row r="128">
       <c r="A128" s="40" t="n">
-        <v>3038</v>
+        <v>113</v>
       </c>
       <c r="B128" s="40" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C128" s="40" t="inlineStr">
@@ -74436,11 +74348,11 @@
     </row>
     <row r="129">
       <c r="A129" s="40" t="n">
-        <v>113</v>
+        <v>2951</v>
       </c>
       <c r="B129" s="40" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C129" s="40" t="inlineStr">
@@ -74460,7 +74372,7 @@
       </c>
       <c r="F129" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G129" s="40" t="inlineStr">
@@ -74471,11 +74383,11 @@
     </row>
     <row r="130">
       <c r="A130" s="40" t="n">
-        <v>2951</v>
+        <v>3038</v>
       </c>
       <c r="B130" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C130" s="40" t="inlineStr">
@@ -74506,11 +74418,11 @@
     </row>
     <row r="131">
       <c r="A131" s="40" t="n">
-        <v>3038</v>
+        <v>2951</v>
       </c>
       <c r="B131" s="40" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C131" s="40" t="inlineStr">
@@ -74520,17 +74432,17 @@
       </c>
       <c r="D131" s="40" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="E131" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F131" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G131" s="40" t="inlineStr">
@@ -74541,11 +74453,11 @@
     </row>
     <row r="132">
       <c r="A132" s="40" t="n">
-        <v>2951</v>
+        <v>2918</v>
       </c>
       <c r="B132" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C132" s="40" t="inlineStr">
@@ -74576,11 +74488,11 @@
     </row>
     <row r="133">
       <c r="A133" s="40" t="n">
-        <v>2918</v>
+        <v>1938</v>
       </c>
       <c r="B133" s="40" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C133" s="40" t="inlineStr">
@@ -74611,11 +74523,11 @@
     </row>
     <row r="134">
       <c r="A134" s="40" t="n">
-        <v>1938</v>
+        <v>3128</v>
       </c>
       <c r="B134" s="40" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C134" s="40" t="inlineStr">
@@ -74646,11 +74558,11 @@
     </row>
     <row r="135">
       <c r="A135" s="40" t="n">
-        <v>3128</v>
+        <v>113</v>
       </c>
       <c r="B135" s="40" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C135" s="40" t="inlineStr">
@@ -74681,11 +74593,11 @@
     </row>
     <row r="136">
       <c r="A136" s="40" t="n">
-        <v>113</v>
+        <v>2951</v>
       </c>
       <c r="B136" s="40" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C136" s="40" t="inlineStr">
@@ -74705,7 +74617,7 @@
       </c>
       <c r="F136" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G136" s="40" t="inlineStr">
@@ -74716,11 +74628,11 @@
     </row>
     <row r="137">
       <c r="A137" s="40" t="n">
-        <v>2951</v>
+        <v>2918</v>
       </c>
       <c r="B137" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C137" s="40" t="inlineStr">
@@ -74751,11 +74663,11 @@
     </row>
     <row r="138">
       <c r="A138" s="40" t="n">
-        <v>2918</v>
+        <v>120</v>
       </c>
       <c r="B138" s="40" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C138" s="40" t="inlineStr">
@@ -74786,11 +74698,11 @@
     </row>
     <row r="139">
       <c r="A139" s="40" t="n">
-        <v>120</v>
+        <v>1938</v>
       </c>
       <c r="B139" s="40" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C139" s="40" t="inlineStr">
@@ -74821,11 +74733,11 @@
     </row>
     <row r="140">
       <c r="A140" s="40" t="n">
-        <v>1938</v>
+        <v>3038</v>
       </c>
       <c r="B140" s="40" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C140" s="40" t="inlineStr">
@@ -74856,11 +74768,11 @@
     </row>
     <row r="141">
       <c r="A141" s="40" t="n">
-        <v>3038</v>
+        <v>3128</v>
       </c>
       <c r="B141" s="40" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C141" s="40" t="inlineStr">
@@ -74891,11 +74803,11 @@
     </row>
     <row r="142">
       <c r="A142" s="40" t="n">
-        <v>3128</v>
+        <v>113</v>
       </c>
       <c r="B142" s="40" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C142" s="40" t="inlineStr">
@@ -74926,11 +74838,11 @@
     </row>
     <row r="143">
       <c r="A143" s="40" t="n">
-        <v>113</v>
+        <v>2951</v>
       </c>
       <c r="B143" s="40" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C143" s="40" t="inlineStr">
@@ -74940,17 +74852,17 @@
       </c>
       <c r="D143" s="40" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="E143" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F143" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G143" s="40" t="inlineStr">
@@ -74961,11 +74873,11 @@
     </row>
     <row r="144">
       <c r="A144" s="40" t="n">
-        <v>2951</v>
+        <v>1938</v>
       </c>
       <c r="B144" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C144" s="40" t="inlineStr">
@@ -74996,11 +74908,11 @@
     </row>
     <row r="145">
       <c r="A145" s="40" t="n">
-        <v>1938</v>
+        <v>3038</v>
       </c>
       <c r="B145" s="40" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C145" s="40" t="inlineStr">
@@ -75031,11 +74943,11 @@
     </row>
     <row r="146">
       <c r="A146" s="40" t="n">
-        <v>3038</v>
+        <v>3128</v>
       </c>
       <c r="B146" s="40" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C146" s="40" t="inlineStr">
@@ -75066,11 +74978,11 @@
     </row>
     <row r="147">
       <c r="A147" s="40" t="n">
-        <v>3128</v>
+        <v>2951</v>
       </c>
       <c r="B147" s="40" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C147" s="40" t="inlineStr">
@@ -75090,7 +75002,7 @@
       </c>
       <c r="F147" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G147" s="40" t="inlineStr">
@@ -75101,11 +75013,11 @@
     </row>
     <row r="148">
       <c r="A148" s="40" t="n">
-        <v>2951</v>
+        <v>1938</v>
       </c>
       <c r="B148" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C148" s="40" t="inlineStr">
@@ -75136,11 +75048,11 @@
     </row>
     <row r="149">
       <c r="A149" s="40" t="n">
-        <v>1938</v>
+        <v>2918</v>
       </c>
       <c r="B149" s="40" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C149" s="40" t="inlineStr">
@@ -75150,17 +75062,17 @@
       </c>
       <c r="D149" s="40" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E149" s="40" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F149" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G149" s="40" t="inlineStr">
@@ -75171,11 +75083,11 @@
     </row>
     <row r="150">
       <c r="A150" s="40" t="n">
-        <v>2918</v>
+        <v>120</v>
       </c>
       <c r="B150" s="40" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C150" s="40" t="inlineStr">
@@ -75206,11 +75118,11 @@
     </row>
     <row r="151">
       <c r="A151" s="40" t="n">
-        <v>120</v>
+        <v>3038</v>
       </c>
       <c r="B151" s="40" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C151" s="40" t="inlineStr">
@@ -75241,11 +75153,11 @@
     </row>
     <row r="152">
       <c r="A152" s="40" t="n">
-        <v>3038</v>
+        <v>3128</v>
       </c>
       <c r="B152" s="40" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C152" s="40" t="inlineStr">
@@ -75276,11 +75188,11 @@
     </row>
     <row r="153">
       <c r="A153" s="40" t="n">
-        <v>3128</v>
+        <v>2951</v>
       </c>
       <c r="B153" s="40" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C153" s="40" t="inlineStr">
@@ -75290,12 +75202,12 @@
       </c>
       <c r="D153" s="40" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E153" s="40" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F153" s="40" t="inlineStr">
@@ -75311,11 +75223,11 @@
     </row>
     <row r="154">
       <c r="A154" s="40" t="n">
-        <v>2951</v>
+        <v>1938</v>
       </c>
       <c r="B154" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C154" s="40" t="inlineStr">
@@ -75360,17 +75272,17 @@
       </c>
       <c r="D155" s="40" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E155" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F155" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G155" s="40" t="inlineStr">
@@ -75381,11 +75293,11 @@
     </row>
     <row r="156">
       <c r="A156" s="40" t="n">
-        <v>1938</v>
+        <v>2951</v>
       </c>
       <c r="B156" s="40" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C156" s="40" t="inlineStr">
@@ -75395,17 +75307,17 @@
       </c>
       <c r="D156" s="40" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E156" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F156" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G156" s="40" t="inlineStr">
@@ -75440,7 +75352,7 @@
       </c>
       <c r="F157" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G157" s="40" t="inlineStr">
@@ -75451,11 +75363,11 @@
     </row>
     <row r="158">
       <c r="A158" s="40" t="n">
-        <v>2951</v>
+        <v>113</v>
       </c>
       <c r="B158" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C158" s="40" t="inlineStr">
@@ -75486,11 +75398,11 @@
     </row>
     <row r="159">
       <c r="A159" s="40" t="n">
-        <v>113</v>
+        <v>2951</v>
       </c>
       <c r="B159" s="40" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C159" s="40" t="inlineStr">
@@ -75500,17 +75412,17 @@
       </c>
       <c r="D159" s="40" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="E159" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F159" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G159" s="40" t="inlineStr">
@@ -75521,11 +75433,11 @@
     </row>
     <row r="160">
       <c r="A160" s="40" t="n">
-        <v>2951</v>
+        <v>1938</v>
       </c>
       <c r="B160" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C160" s="40" t="inlineStr">
@@ -75556,11 +75468,11 @@
     </row>
     <row r="161">
       <c r="A161" s="40" t="n">
-        <v>1938</v>
+        <v>2951</v>
       </c>
       <c r="B161" s="40" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C161" s="40" t="inlineStr">
@@ -75580,7 +75492,7 @@
       </c>
       <c r="F161" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G161" s="40" t="inlineStr">
@@ -75605,17 +75517,17 @@
       </c>
       <c r="D162" s="40" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="E162" s="40" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F162" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G162" s="40" t="inlineStr">
@@ -75650,7 +75562,7 @@
       </c>
       <c r="F163" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G163" s="40" t="inlineStr">
@@ -75661,11 +75573,11 @@
     </row>
     <row r="164">
       <c r="A164" s="40" t="n">
-        <v>2951</v>
+        <v>1938</v>
       </c>
       <c r="B164" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C164" s="40" t="inlineStr">
@@ -75696,11 +75608,11 @@
     </row>
     <row r="165">
       <c r="A165" s="40" t="n">
-        <v>1938</v>
+        <v>2951</v>
       </c>
       <c r="B165" s="40" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C165" s="40" t="inlineStr">
@@ -75710,17 +75622,17 @@
       </c>
       <c r="D165" s="40" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E165" s="40" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F165" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G165" s="40" t="inlineStr">
@@ -75731,11 +75643,11 @@
     </row>
     <row r="166">
       <c r="A166" s="40" t="n">
-        <v>2951</v>
+        <v>2918</v>
       </c>
       <c r="B166" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C166" s="40" t="inlineStr">
@@ -75766,11 +75678,11 @@
     </row>
     <row r="167">
       <c r="A167" s="40" t="n">
-        <v>2918</v>
+        <v>2951</v>
       </c>
       <c r="B167" s="40" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C167" s="40" t="inlineStr">
@@ -75790,7 +75702,7 @@
       </c>
       <c r="F167" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G167" s="40" t="inlineStr">
@@ -75801,11 +75713,11 @@
     </row>
     <row r="168">
       <c r="A168" s="40" t="n">
-        <v>2951</v>
+        <v>2918</v>
       </c>
       <c r="B168" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C168" s="40" t="inlineStr">
@@ -75836,11 +75748,11 @@
     </row>
     <row r="169">
       <c r="A169" s="40" t="n">
-        <v>2918</v>
+        <v>120</v>
       </c>
       <c r="B169" s="40" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C169" s="40" t="inlineStr">
@@ -75871,11 +75783,11 @@
     </row>
     <row r="170">
       <c r="A170" s="40" t="n">
-        <v>120</v>
+        <v>2951</v>
       </c>
       <c r="B170" s="40" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C170" s="40" t="inlineStr">
@@ -75885,17 +75797,17 @@
       </c>
       <c r="D170" s="40" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E170" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F170" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G170" s="40" t="inlineStr">
@@ -75906,11 +75818,11 @@
     </row>
     <row r="171">
       <c r="A171" s="40" t="n">
-        <v>2951</v>
+        <v>1938</v>
       </c>
       <c r="B171" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C171" s="40" t="inlineStr">
@@ -75941,11 +75853,11 @@
     </row>
     <row r="172">
       <c r="A172" s="40" t="n">
-        <v>1938</v>
+        <v>2951</v>
       </c>
       <c r="B172" s="40" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C172" s="40" t="inlineStr">
@@ -75965,7 +75877,7 @@
       </c>
       <c r="F172" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G172" s="40" t="inlineStr">
@@ -75976,11 +75888,11 @@
     </row>
     <row r="173">
       <c r="A173" s="40" t="n">
-        <v>2951</v>
+        <v>1938</v>
       </c>
       <c r="B173" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C173" s="40" t="inlineStr">
@@ -76011,11 +75923,11 @@
     </row>
     <row r="174">
       <c r="A174" s="40" t="n">
-        <v>1938</v>
+        <v>113</v>
       </c>
       <c r="B174" s="40" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C174" s="40" t="inlineStr">
@@ -76046,11 +75958,11 @@
     </row>
     <row r="175">
       <c r="A175" s="40" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B175" s="40" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C175" s="40" t="inlineStr">
@@ -76060,12 +75972,12 @@
       </c>
       <c r="D175" s="40" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E175" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F175" s="40" t="inlineStr">
@@ -76081,11 +75993,11 @@
     </row>
     <row r="176">
       <c r="A176" s="40" t="n">
-        <v>120</v>
+        <v>2951</v>
       </c>
       <c r="B176" s="40" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C176" s="40" t="inlineStr">
@@ -76095,12 +76007,12 @@
       </c>
       <c r="D176" s="40" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="E176" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F176" s="40" t="inlineStr">
@@ -76116,11 +76028,11 @@
     </row>
     <row r="177">
       <c r="A177" s="40" t="n">
-        <v>2951</v>
+        <v>2918</v>
       </c>
       <c r="B177" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C177" s="40" t="inlineStr">
@@ -76151,11 +76063,11 @@
     </row>
     <row r="178">
       <c r="A178" s="40" t="n">
-        <v>2918</v>
+        <v>120</v>
       </c>
       <c r="B178" s="40" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C178" s="40" t="inlineStr">
@@ -76186,11 +76098,11 @@
     </row>
     <row r="179">
       <c r="A179" s="40" t="n">
-        <v>120</v>
+        <v>1936</v>
       </c>
       <c r="B179" s="40" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C179" s="40" t="inlineStr">
@@ -76221,11 +76133,11 @@
     </row>
     <row r="180">
       <c r="A180" s="40" t="n">
-        <v>1936</v>
+        <v>2721</v>
       </c>
       <c r="B180" s="40" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C180" s="40" t="inlineStr">
@@ -76256,11 +76168,11 @@
     </row>
     <row r="181">
       <c r="A181" s="40" t="n">
-        <v>2721</v>
+        <v>3038</v>
       </c>
       <c r="B181" s="40" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C181" s="40" t="inlineStr">
@@ -76291,11 +76203,11 @@
     </row>
     <row r="182">
       <c r="A182" s="40" t="n">
-        <v>3038</v>
+        <v>3128</v>
       </c>
       <c r="B182" s="40" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C182" s="40" t="inlineStr">
@@ -76326,11 +76238,11 @@
     </row>
     <row r="183">
       <c r="A183" s="40" t="n">
-        <v>3128</v>
+        <v>113</v>
       </c>
       <c r="B183" s="40" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C183" s="40" t="inlineStr">
@@ -76360,47 +76272,47 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="40" t="n">
-        <v>113</v>
-      </c>
-      <c r="B184" s="40" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="C184" s="40" t="inlineStr">
+      <c r="A184" s="41" t="n">
+        <v>2951</v>
+      </c>
+      <c r="B184" s="41" t="inlineStr">
+        <is>
+          <t>Alana Amanda Fernandes Ovelar</t>
+        </is>
+      </c>
+      <c r="C184" s="41" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D184" s="40" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="E184" s="40" t="inlineStr">
-        <is>
-          <t>Segunda</t>
-        </is>
-      </c>
-      <c r="F184" s="40" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G184" s="40" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+      <c r="D184" s="41" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="E184" s="41" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F184" s="41" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G184" s="41" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="41" t="n">
-        <v>2951</v>
+        <v>2918</v>
       </c>
       <c r="B185" s="41" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C185" s="41" t="inlineStr">
@@ -76431,11 +76343,11 @@
     </row>
     <row r="186">
       <c r="A186" s="41" t="n">
-        <v>2918</v>
+        <v>120</v>
       </c>
       <c r="B186" s="41" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C186" s="41" t="inlineStr">
@@ -76466,11 +76378,11 @@
     </row>
     <row r="187">
       <c r="A187" s="41" t="n">
-        <v>120</v>
+        <v>1936</v>
       </c>
       <c r="B187" s="41" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C187" s="41" t="inlineStr">
@@ -76501,11 +76413,11 @@
     </row>
     <row r="188">
       <c r="A188" s="41" t="n">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="B188" s="41" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C188" s="41" t="inlineStr">
@@ -76536,11 +76448,11 @@
     </row>
     <row r="189">
       <c r="A189" s="41" t="n">
-        <v>1938</v>
+        <v>2721</v>
       </c>
       <c r="B189" s="41" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C189" s="41" t="inlineStr">
@@ -76571,11 +76483,11 @@
     </row>
     <row r="190">
       <c r="A190" s="41" t="n">
-        <v>2721</v>
+        <v>3038</v>
       </c>
       <c r="B190" s="41" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C190" s="41" t="inlineStr">
@@ -76606,11 +76518,11 @@
     </row>
     <row r="191">
       <c r="A191" s="41" t="n">
-        <v>3038</v>
+        <v>3128</v>
       </c>
       <c r="B191" s="41" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C191" s="41" t="inlineStr">
@@ -76641,11 +76553,11 @@
     </row>
     <row r="192">
       <c r="A192" s="41" t="n">
-        <v>3128</v>
+        <v>113</v>
       </c>
       <c r="B192" s="41" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C192" s="41" t="inlineStr">
@@ -76675,47 +76587,47 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="41" t="n">
-        <v>113</v>
-      </c>
-      <c r="B193" s="41" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="C193" s="41" t="inlineStr">
+      <c r="A193" s="40" t="n">
+        <v>2951</v>
+      </c>
+      <c r="B193" s="40" t="inlineStr">
+        <is>
+          <t>Alana Amanda Fernandes Ovelar</t>
+        </is>
+      </c>
+      <c r="C193" s="40" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D193" s="41" t="inlineStr">
+      <c r="D193" s="40" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="E193" s="41" t="inlineStr">
+      <c r="E193" s="40" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F193" s="41" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G193" s="41" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+      <c r="F193" s="40" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G193" s="40" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="40" t="n">
-        <v>2951</v>
+        <v>2918</v>
       </c>
       <c r="B194" s="40" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C194" s="40" t="inlineStr">
@@ -76746,31 +76658,31 @@
     </row>
     <row r="195">
       <c r="A195" s="40" t="n">
-        <v>2918</v>
+        <v>110</v>
       </c>
       <c r="B195" s="40" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C195" s="40" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D195" s="40" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="E195" s="40" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F195" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G195" s="40" t="inlineStr">
@@ -76781,11 +76693,11 @@
     </row>
     <row r="196">
       <c r="A196" s="40" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="B196" s="40" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C196" s="40" t="inlineStr">
@@ -76816,11 +76728,11 @@
     </row>
     <row r="197">
       <c r="A197" s="40" t="n">
-        <v>80</v>
+        <v>2789</v>
       </c>
       <c r="B197" s="40" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C197" s="40" t="inlineStr">
@@ -76851,11 +76763,11 @@
     </row>
     <row r="198">
       <c r="A198" s="40" t="n">
-        <v>2789</v>
+        <v>1942</v>
       </c>
       <c r="B198" s="40" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C198" s="40" t="inlineStr">
@@ -76886,11 +76798,11 @@
     </row>
     <row r="199">
       <c r="A199" s="40" t="n">
-        <v>1942</v>
+        <v>124</v>
       </c>
       <c r="B199" s="40" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
       <c r="C199" s="40" t="inlineStr">
@@ -76921,11 +76833,11 @@
     </row>
     <row r="200">
       <c r="A200" s="40" t="n">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="B200" s="40" t="inlineStr">
         <is>
-          <t>Ramona dos Santos Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C200" s="40" t="inlineStr">
@@ -76956,11 +76868,11 @@
     </row>
     <row r="201">
       <c r="A201" s="40" t="n">
-        <v>161</v>
+        <v>1996</v>
       </c>
       <c r="B201" s="40" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C201" s="40" t="inlineStr">
@@ -76991,11 +76903,11 @@
     </row>
     <row r="202">
       <c r="A202" s="40" t="n">
-        <v>1996</v>
+        <v>157</v>
       </c>
       <c r="B202" s="40" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C202" s="40" t="inlineStr">
@@ -77026,11 +76938,11 @@
     </row>
     <row r="203">
       <c r="A203" s="40" t="n">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="B203" s="40" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C203" s="40" t="inlineStr">
@@ -77050,7 +76962,7 @@
       </c>
       <c r="F203" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G203" s="40" t="inlineStr">
@@ -77061,11 +76973,11 @@
     </row>
     <row r="204">
       <c r="A204" s="40" t="n">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="B204" s="40" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C204" s="40" t="inlineStr">
@@ -77096,11 +77008,11 @@
     </row>
     <row r="205">
       <c r="A205" s="40" t="n">
-        <v>161</v>
+        <v>1943</v>
       </c>
       <c r="B205" s="40" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C205" s="40" t="inlineStr">
@@ -77110,17 +77022,17 @@
       </c>
       <c r="D205" s="40" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="E205" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F205" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G205" s="40" t="inlineStr">
@@ -77131,11 +77043,11 @@
     </row>
     <row r="206">
       <c r="A206" s="40" t="n">
-        <v>1943</v>
+        <v>2789</v>
       </c>
       <c r="B206" s="40" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C206" s="40" t="inlineStr">
@@ -77166,11 +77078,11 @@
     </row>
     <row r="207">
       <c r="A207" s="40" t="n">
-        <v>2789</v>
+        <v>1996</v>
       </c>
       <c r="B207" s="40" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C207" s="40" t="inlineStr">
@@ -77201,11 +77113,11 @@
     </row>
     <row r="208">
       <c r="A208" s="40" t="n">
-        <v>1996</v>
+        <v>110</v>
       </c>
       <c r="B208" s="40" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C208" s="40" t="inlineStr">
@@ -77215,12 +77127,12 @@
       </c>
       <c r="D208" s="40" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E208" s="40" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F208" s="40" t="inlineStr">
@@ -77236,11 +77148,11 @@
     </row>
     <row r="209">
       <c r="A209" s="40" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="B209" s="40" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C209" s="40" t="inlineStr">
@@ -77271,11 +77183,11 @@
     </row>
     <row r="210">
       <c r="A210" s="40" t="n">
-        <v>80</v>
+        <v>2789</v>
       </c>
       <c r="B210" s="40" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C210" s="40" t="inlineStr">
@@ -77306,11 +77218,11 @@
     </row>
     <row r="211">
       <c r="A211" s="40" t="n">
-        <v>2789</v>
+        <v>1942</v>
       </c>
       <c r="B211" s="40" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C211" s="40" t="inlineStr">
@@ -77341,11 +77253,11 @@
     </row>
     <row r="212">
       <c r="A212" s="40" t="n">
-        <v>1942</v>
+        <v>161</v>
       </c>
       <c r="B212" s="40" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C212" s="40" t="inlineStr">
@@ -77376,11 +77288,11 @@
     </row>
     <row r="213">
       <c r="A213" s="40" t="n">
-        <v>161</v>
+        <v>1996</v>
       </c>
       <c r="B213" s="40" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C213" s="40" t="inlineStr">
@@ -77411,11 +77323,11 @@
     </row>
     <row r="214">
       <c r="A214" s="40" t="n">
-        <v>1996</v>
+        <v>157</v>
       </c>
       <c r="B214" s="40" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C214" s="40" t="inlineStr">
@@ -77446,11 +77358,11 @@
     </row>
     <row r="215">
       <c r="A215" s="40" t="n">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="B215" s="40" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C215" s="40" t="inlineStr">
@@ -77460,12 +77372,12 @@
       </c>
       <c r="D215" s="40" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E215" s="40" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F215" s="40" t="inlineStr">
@@ -77505,7 +77417,7 @@
       </c>
       <c r="F216" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G216" s="40" t="inlineStr">
@@ -77516,11 +77428,11 @@
     </row>
     <row r="217">
       <c r="A217" s="40" t="n">
-        <v>110</v>
+        <v>1943</v>
       </c>
       <c r="B217" s="40" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C217" s="40" t="inlineStr">
@@ -77530,17 +77442,17 @@
       </c>
       <c r="D217" s="40" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E217" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F217" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G217" s="40" t="inlineStr">
@@ -77575,7 +77487,7 @@
       </c>
       <c r="F218" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G218" s="40" t="inlineStr">
@@ -77600,17 +77512,17 @@
       </c>
       <c r="D219" s="40" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E219" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F219" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G219" s="40" t="inlineStr">
@@ -77621,11 +77533,11 @@
     </row>
     <row r="220">
       <c r="A220" s="40" t="n">
-        <v>1943</v>
+        <v>157</v>
       </c>
       <c r="B220" s="40" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C220" s="40" t="inlineStr">
@@ -77656,11 +77568,11 @@
     </row>
     <row r="221">
       <c r="A221" s="40" t="n">
-        <v>157</v>
+        <v>1943</v>
       </c>
       <c r="B221" s="40" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C221" s="40" t="inlineStr">
@@ -77680,7 +77592,7 @@
       </c>
       <c r="F221" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G221" s="40" t="inlineStr">
@@ -77705,17 +77617,17 @@
       </c>
       <c r="D222" s="40" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="E222" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F222" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G222" s="40" t="inlineStr">
@@ -77726,11 +77638,11 @@
     </row>
     <row r="223">
       <c r="A223" s="40" t="n">
-        <v>1943</v>
+        <v>2789</v>
       </c>
       <c r="B223" s="40" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C223" s="40" t="inlineStr">
@@ -77761,11 +77673,11 @@
     </row>
     <row r="224">
       <c r="A224" s="40" t="n">
-        <v>2789</v>
+        <v>157</v>
       </c>
       <c r="B224" s="40" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C224" s="40" t="inlineStr">
@@ -77796,11 +77708,11 @@
     </row>
     <row r="225">
       <c r="A225" s="40" t="n">
-        <v>157</v>
+        <v>2789</v>
       </c>
       <c r="B225" s="40" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C225" s="40" t="inlineStr">
@@ -77820,7 +77732,7 @@
       </c>
       <c r="F225" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G225" s="40" t="inlineStr">
@@ -77831,11 +77743,11 @@
     </row>
     <row r="226">
       <c r="A226" s="40" t="n">
-        <v>2789</v>
+        <v>1996</v>
       </c>
       <c r="B226" s="40" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C226" s="40" t="inlineStr">
@@ -77866,11 +77778,11 @@
     </row>
     <row r="227">
       <c r="A227" s="40" t="n">
-        <v>1996</v>
+        <v>124</v>
       </c>
       <c r="B227" s="40" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
       <c r="C227" s="40" t="inlineStr">
@@ -77880,17 +77792,17 @@
       </c>
       <c r="D227" s="40" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E227" s="40" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F227" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G227" s="40" t="inlineStr">
@@ -77901,11 +77813,11 @@
     </row>
     <row r="228">
       <c r="A228" s="40" t="n">
-        <v>124</v>
+        <v>2789</v>
       </c>
       <c r="B228" s="40" t="inlineStr">
         <is>
-          <t>Ramona dos Santos Oliveira</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C228" s="40" t="inlineStr">
@@ -77915,17 +77827,17 @@
       </c>
       <c r="D228" s="40" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E228" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F228" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G228" s="40" t="inlineStr">
@@ -77936,11 +77848,11 @@
     </row>
     <row r="229">
       <c r="A229" s="40" t="n">
-        <v>2789</v>
+        <v>110</v>
       </c>
       <c r="B229" s="40" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C229" s="40" t="inlineStr">
@@ -77950,12 +77862,12 @@
       </c>
       <c r="D229" s="40" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="E229" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F229" s="40" t="inlineStr">
@@ -77971,11 +77883,11 @@
     </row>
     <row r="230">
       <c r="A230" s="40" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="B230" s="40" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C230" s="40" t="inlineStr">
@@ -78006,11 +77918,11 @@
     </row>
     <row r="231">
       <c r="A231" s="40" t="n">
-        <v>80</v>
+        <v>1942</v>
       </c>
       <c r="B231" s="40" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C231" s="40" t="inlineStr">
@@ -78041,11 +77953,11 @@
     </row>
     <row r="232">
       <c r="A232" s="40" t="n">
-        <v>1942</v>
+        <v>124</v>
       </c>
       <c r="B232" s="40" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
       <c r="C232" s="40" t="inlineStr">
@@ -78076,11 +77988,11 @@
     </row>
     <row r="233">
       <c r="A233" s="40" t="n">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="B233" s="40" t="inlineStr">
         <is>
-          <t>Ramona dos Santos Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C233" s="40" t="inlineStr">
@@ -78111,11 +78023,11 @@
     </row>
     <row r="234">
       <c r="A234" s="40" t="n">
-        <v>161</v>
+        <v>1996</v>
       </c>
       <c r="B234" s="40" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C234" s="40" t="inlineStr">
@@ -78146,11 +78058,11 @@
     </row>
     <row r="235">
       <c r="A235" s="40" t="n">
-        <v>1996</v>
+        <v>157</v>
       </c>
       <c r="B235" s="40" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C235" s="40" t="inlineStr">
@@ -78181,11 +78093,11 @@
     </row>
     <row r="236">
       <c r="A236" s="40" t="n">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="B236" s="40" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C236" s="40" t="inlineStr">
@@ -78195,17 +78107,17 @@
       </c>
       <c r="D236" s="40" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="E236" s="40" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F236" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G236" s="40" t="inlineStr">
@@ -78216,11 +78128,11 @@
     </row>
     <row r="237">
       <c r="A237" s="40" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="B237" s="40" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C237" s="40" t="inlineStr">
@@ -78251,11 +78163,11 @@
     </row>
     <row r="238">
       <c r="A238" s="40" t="n">
-        <v>80</v>
+        <v>2789</v>
       </c>
       <c r="B238" s="40" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C238" s="40" t="inlineStr">
@@ -78286,11 +78198,11 @@
     </row>
     <row r="239">
       <c r="A239" s="40" t="n">
-        <v>2789</v>
+        <v>1942</v>
       </c>
       <c r="B239" s="40" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C239" s="40" t="inlineStr">
@@ -78321,11 +78233,11 @@
     </row>
     <row r="240">
       <c r="A240" s="40" t="n">
-        <v>1942</v>
+        <v>124</v>
       </c>
       <c r="B240" s="40" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
       <c r="C240" s="40" t="inlineStr">
@@ -78356,11 +78268,11 @@
     </row>
     <row r="241">
       <c r="A241" s="40" t="n">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="B241" s="40" t="inlineStr">
         <is>
-          <t>Ramona dos Santos Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C241" s="40" t="inlineStr">
@@ -78391,11 +78303,11 @@
     </row>
     <row r="242">
       <c r="A242" s="40" t="n">
-        <v>161</v>
+        <v>1996</v>
       </c>
       <c r="B242" s="40" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C242" s="40" t="inlineStr">
@@ -78426,11 +78338,11 @@
     </row>
     <row r="243">
       <c r="A243" s="40" t="n">
-        <v>1996</v>
+        <v>157</v>
       </c>
       <c r="B243" s="40" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C243" s="40" t="inlineStr">
@@ -78461,11 +78373,11 @@
     </row>
     <row r="244">
       <c r="A244" s="40" t="n">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="B244" s="40" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C244" s="40" t="inlineStr">
@@ -78485,7 +78397,7 @@
       </c>
       <c r="F244" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G244" s="40" t="inlineStr">
@@ -78496,11 +78408,11 @@
     </row>
     <row r="245">
       <c r="A245" s="40" t="n">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="B245" s="40" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C245" s="40" t="inlineStr">
@@ -78529,43 +78441,8 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="40" t="n">
-        <v>161</v>
-      </c>
-      <c r="B246" s="40" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="C246" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D246" s="40" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="E246" s="40" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F246" s="40" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G246" s="40" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G246"/>
+  <autoFilter ref="A2:G245"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semanas_313-317.xlsx
+++ b/data/historico/semanas_313-317.xlsx
@@ -6644,7 +6644,7 @@
       </c>
       <c r="B17" s="43" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="C17" s="43" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B22" s="43" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="C22" s="43" t="inlineStr">

--- a/data/historico/semanas_313-317.xlsx
+++ b/data/historico/semanas_313-317.xlsx
@@ -6644,7 +6644,7 @@
       </c>
       <c r="B17" s="43" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="C17" s="43" t="inlineStr">

--- a/data/historico/semanas_313-317.xlsx
+++ b/data/historico/semanas_313-317.xlsx
@@ -35,7 +35,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Resumo Semanal'!$A$2:$AE$195</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Ranking'!$A$2:$E$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Ranking'!$A$2:$G$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31962,15 +31962,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F442"/>
+  <dimension ref="A1:G442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -31984,6 +31985,7 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -32003,15 +32005,24 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Dias Trabalhados</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Dias Úteis Esperados no Mês</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
           <t>Pontuação Final</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -32028,14 +32039,19 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -32052,14 +32068,19 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -32076,14 +32097,19 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -32100,14 +32126,19 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -32124,14 +32155,19 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -32148,14 +32184,19 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -32172,14 +32213,19 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -32196,14 +32242,19 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>96.8</v>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -32220,14 +32271,19 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>95.52</v>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -32244,14 +32300,19 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>95.06999999999999</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -32268,14 +32329,19 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>94.62</v>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -32292,14 +32358,19 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F14" s="4" t="n">
         <v>94.5</v>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -32316,14 +32387,19 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F15" s="4" t="n">
         <v>93.39</v>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -32340,14 +32416,19 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F16" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -32364,14 +32445,19 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F17" s="4" t="n">
         <v>91.09999999999999</v>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -32379,47 +32465,57 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
+        <v>22</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Claine Luisa Figueiredo Torraca</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n"/>
+      <c r="D19" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -32427,23 +32523,28 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>88.68000000000001</v>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
+        <v>22</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>89.84</v>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -32460,14 +32561,19 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
+        <v>22</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>88.73999999999999</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -32484,14 +32590,19 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F22" s="5" t="n">
         <v>87.78</v>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -32499,7 +32610,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -32508,14 +32619,19 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
+        <v>23</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -32523,23 +32639,28 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -32547,23 +32668,28 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>85.97</v>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -32580,14 +32706,19 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>84.13</v>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
+        <v>21</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -32604,14 +32735,19 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F27" s="5" t="n">
         <v>83.3</v>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -32628,14 +32764,19 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>80.16</v>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
+        <v>21</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>78.91</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -32652,62 +32793,77 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>77.23</v>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>75.67</v>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="41" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="41" t="inlineStr">
         <is>
           <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="41" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n">
-        <v>76.31</v>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n"/>
+      <c r="D30" s="41" t="n">
+        <v>21</v>
+      </c>
+      <c r="E30" s="41" t="n">
+        <v>23</v>
+      </c>
+      <c r="F30" s="41" t="n">
+        <v>74.83</v>
+      </c>
+      <c r="G30" s="41" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="41" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="41" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="41" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n">
-        <v>75.41</v>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="n"/>
+      <c r="D31" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="E31" s="41" t="n">
+        <v>23</v>
+      </c>
+      <c r="F31" s="41" t="n">
+        <v>74.06</v>
+      </c>
+      <c r="G31" s="41" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="41" t="n">
@@ -32724,14 +32880,19 @@
         </is>
       </c>
       <c r="D32" s="41" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="E32" s="41" t="inlineStr">
+        <v>22</v>
+      </c>
+      <c r="E32" s="41" t="n">
+        <v>21</v>
+      </c>
+      <c r="F32" s="41" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="G32" s="41" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="41" t="n">
@@ -32748,14 +32909,19 @@
         </is>
       </c>
       <c r="D33" s="41" t="n">
+        <v>17</v>
+      </c>
+      <c r="E33" s="41" t="n">
+        <v>22</v>
+      </c>
+      <c r="F33" s="41" t="n">
         <v>70.20999999999999</v>
       </c>
-      <c r="E33" s="41" t="inlineStr">
+      <c r="G33" s="41" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
         </is>
       </c>
-      <c r="F33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="41" t="n">
@@ -32763,23 +32929,28 @@
       </c>
       <c r="B34" s="41" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C34" s="41" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D34" s="41" t="n">
-        <v>64.51000000000001</v>
-      </c>
-      <c r="E34" s="41" t="inlineStr">
+        <v>18</v>
+      </c>
+      <c r="E34" s="41" t="n">
+        <v>22</v>
+      </c>
+      <c r="F34" s="41" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="G34" s="41" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="41" t="n">
@@ -32787,47 +32958,57 @@
       </c>
       <c r="B35" s="41" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="C35" s="41" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D35" s="41" t="n">
-        <v>63.57</v>
-      </c>
-      <c r="E35" s="41" t="inlineStr">
+        <v>21</v>
+      </c>
+      <c r="E35" s="41" t="n">
+        <v>23</v>
+      </c>
+      <c r="F35" s="41" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="G35" s="41" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="41" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="41" t="inlineStr">
         <is>
           <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="41" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
-        <v>57.97</v>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="n"/>
+      <c r="D36" s="41" t="n">
+        <v>23</v>
+      </c>
+      <c r="E36" s="41" t="n">
+        <v>21</v>
+      </c>
+      <c r="F36" s="41" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="G36" s="41" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -32835,23 +33016,28 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>52.31</v>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>49.72</v>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -32859,23 +33045,28 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
+        <v>14</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -32883,23 +33074,28 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>47.04</v>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -32907,23 +33103,28 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -32931,7 +33132,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -32940,14 +33141,19 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>45.63</v>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
+        <v>21</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -32955,23 +33161,28 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>43.77</v>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -32988,14 +33199,19 @@
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>32.19</v>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -33003,23 +33219,28 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Carlos Alberto Albiero</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -33027,23 +33248,28 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Carlos Alberto Albiero</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
+        <v>22</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -33060,14 +33286,19 @@
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -33084,14 +33315,19 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>9.27</v>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
@@ -33108,14 +33344,19 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F48" s="6" t="n">
         <v>2.74</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -33132,14 +33373,19 @@
         </is>
       </c>
       <c r="D49" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F49" s="6" t="n">
         <v>1.27</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -33156,14 +33402,19 @@
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -33180,14 +33431,19 @@
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
+        <v>13</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -33196,6 +33452,7 @@
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="n"/>
       <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -33204,6 +33461,7 @@
       <c r="D53" s="2" t="n"/>
       <c r="E53" s="2" t="n"/>
       <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="52" t="inlineStr">
@@ -33216,6 +33474,7 @@
       <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="n"/>
       <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -33248,6 +33507,7 @@
           <t>Pontos Aplicados</t>
         </is>
       </c>
+      <c r="G55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="53" t="inlineStr">
@@ -33274,6 +33534,7 @@
       <c r="F56" s="53" t="n">
         <v>14</v>
       </c>
+      <c r="G56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="54" t="inlineStr">
@@ -33300,6 +33561,7 @@
       <c r="F57" s="54" t="n">
         <v>-2.5</v>
       </c>
+      <c r="G57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="54" t="inlineStr">
@@ -33321,11 +33583,12 @@
         <v>3</v>
       </c>
       <c r="E58" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3632</v>
       </c>
       <c r="F58" s="54" t="n">
-        <v>-1.04</v>
-      </c>
+        <v>-1.09</v>
+      </c>
+      <c r="G58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="54" t="inlineStr">
@@ -33347,11 +33610,12 @@
         <v>9</v>
       </c>
       <c r="E59" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3632</v>
       </c>
       <c r="F59" s="54" t="n">
-        <v>-3.13</v>
-      </c>
+        <v>-3.27</v>
+      </c>
+      <c r="G59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="54" t="inlineStr">
@@ -33373,11 +33637,12 @@
         <v>15</v>
       </c>
       <c r="E60" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3632</v>
       </c>
       <c r="F60" s="54" t="n">
-        <v>-5.21</v>
-      </c>
+        <v>-5.45</v>
+      </c>
+      <c r="G60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="54" t="inlineStr">
@@ -33399,11 +33664,12 @@
         <v>8</v>
       </c>
       <c r="E61" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3632</v>
       </c>
       <c r="F61" s="54" t="n">
-        <v>-2.78</v>
-      </c>
+        <v>-2.91</v>
+      </c>
+      <c r="G61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="54" t="inlineStr">
@@ -33425,11 +33691,12 @@
         <v>11</v>
       </c>
       <c r="E62" s="54" t="n">
-        <v>1.5</v>
+        <v>1.8158</v>
       </c>
       <c r="F62" s="54" t="n">
-        <v>-19.11</v>
-      </c>
+        <v>-19.97</v>
+      </c>
+      <c r="G62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="54" t="inlineStr">
@@ -33451,11 +33718,12 @@
         <v>1</v>
       </c>
       <c r="E63" s="54" t="n">
-        <v>0.5</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="F63" s="54" t="n">
-        <v>-0.58</v>
-      </c>
+        <v>-0.61</v>
+      </c>
+      <c r="G63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="54" t="inlineStr">
@@ -33477,11 +33745,12 @@
         <v>7</v>
       </c>
       <c r="E64" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3632</v>
       </c>
       <c r="F64" s="54" t="n">
-        <v>-2.43</v>
-      </c>
+        <v>-2.54</v>
+      </c>
+      <c r="G64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="53" t="inlineStr">
@@ -33508,6 +33777,7 @@
       <c r="F65" s="53" t="n">
         <v>13</v>
       </c>
+      <c r="G65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="54" t="inlineStr">
@@ -33534,6 +33804,7 @@
       <c r="F66" s="54" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="54" t="inlineStr">
@@ -33555,11 +33826,12 @@
         <v>4</v>
       </c>
       <c r="E67" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4929</v>
       </c>
       <c r="F67" s="54" t="n">
-        <v>-1.89</v>
-      </c>
+        <v>-1.97</v>
+      </c>
+      <c r="G67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="54" t="inlineStr">
@@ -33581,11 +33853,12 @@
         <v>6</v>
       </c>
       <c r="E68" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4929</v>
       </c>
       <c r="F68" s="54" t="n">
-        <v>-2.83</v>
-      </c>
+        <v>-2.96</v>
+      </c>
+      <c r="G68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="54" t="inlineStr">
@@ -33607,11 +33880,12 @@
         <v>13</v>
       </c>
       <c r="E69" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4929</v>
       </c>
       <c r="F69" s="54" t="n">
-        <v>-6.13</v>
-      </c>
+        <v>-6.41</v>
+      </c>
+      <c r="G69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="54" t="inlineStr">
@@ -33633,11 +33907,12 @@
         <v>7</v>
       </c>
       <c r="E70" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4929</v>
       </c>
       <c r="F70" s="54" t="n">
-        <v>-3.3</v>
-      </c>
+        <v>-3.45</v>
+      </c>
+      <c r="G70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="54" t="inlineStr">
@@ -33659,11 +33934,12 @@
         <v>10</v>
       </c>
       <c r="E71" s="54" t="n">
-        <v>1.5</v>
+        <v>2.4643</v>
       </c>
       <c r="F71" s="54" t="n">
-        <v>-23.57</v>
-      </c>
+        <v>-24.64</v>
+      </c>
+      <c r="G71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="54" t="inlineStr">
@@ -33685,11 +33961,12 @@
         <v>1</v>
       </c>
       <c r="E72" s="54" t="n">
-        <v>0.5</v>
+        <v>0.8214</v>
       </c>
       <c r="F72" s="54" t="n">
-        <v>-0.79</v>
-      </c>
+        <v>-0.82</v>
+      </c>
+      <c r="G72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="54" t="inlineStr">
@@ -33711,11 +33988,12 @@
         <v>46</v>
       </c>
       <c r="E73" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4929</v>
       </c>
       <c r="F73" s="54" t="n">
-        <v>-21.69</v>
-      </c>
+        <v>-22.67</v>
+      </c>
+      <c r="G73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="53" t="inlineStr">
@@ -33742,6 +34020,7 @@
       <c r="F74" s="53" t="n">
         <v>9</v>
       </c>
+      <c r="G74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="54" t="inlineStr">
@@ -33768,6 +34047,7 @@
       <c r="F75" s="54" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="54" t="inlineStr">
@@ -33789,11 +34069,12 @@
         <v>1</v>
       </c>
       <c r="E76" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F76" s="54" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="54" t="inlineStr">
@@ -33815,11 +34096,12 @@
         <v>2</v>
       </c>
       <c r="E77" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F77" s="54" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="54" t="inlineStr">
@@ -33841,11 +34123,12 @@
         <v>1</v>
       </c>
       <c r="E78" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F78" s="54" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="54" t="inlineStr">
@@ -33867,11 +34150,12 @@
         <v>26</v>
       </c>
       <c r="E79" s="54" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F79" s="54" t="n">
         <v>-78</v>
       </c>
+      <c r="G79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="54" t="inlineStr">
@@ -33893,11 +34177,12 @@
         <v>5</v>
       </c>
       <c r="E80" s="54" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F80" s="54" t="n">
         <v>-5</v>
       </c>
+      <c r="G80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="54" t="inlineStr">
@@ -33919,11 +34204,12 @@
         <v>2</v>
       </c>
       <c r="E81" s="54" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F81" s="54" t="n">
         <v>-2</v>
       </c>
+      <c r="G81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="54" t="inlineStr">
@@ -33945,11 +34231,12 @@
         <v>1</v>
       </c>
       <c r="E82" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F82" s="54" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="53" t="inlineStr">
@@ -33976,6 +34263,7 @@
       <c r="F83" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="53" t="inlineStr">
@@ -34002,6 +34290,7 @@
       <c r="F84" s="53" t="n">
         <v>1</v>
       </c>
+      <c r="G84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="54" t="inlineStr">
@@ -34028,6 +34317,7 @@
       <c r="F85" s="54" t="n">
         <v>-1</v>
       </c>
+      <c r="G85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="54" t="inlineStr">
@@ -34049,11 +34339,12 @@
         <v>3</v>
       </c>
       <c r="E86" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F86" s="54" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="54" t="inlineStr">
@@ -34075,11 +34366,12 @@
         <v>6</v>
       </c>
       <c r="E87" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F87" s="54" t="n">
         <v>-3.6</v>
       </c>
+      <c r="G87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="53" t="inlineStr">
@@ -34106,6 +34398,7 @@
       <c r="F88" s="53" t="n">
         <v>11</v>
       </c>
+      <c r="G88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="54" t="inlineStr">
@@ -34132,6 +34425,7 @@
       <c r="F89" s="54" t="n">
         <v>-5</v>
       </c>
+      <c r="G89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="54" t="inlineStr">
@@ -34153,11 +34447,12 @@
         <v>4</v>
       </c>
       <c r="E90" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3286</v>
       </c>
       <c r="F90" s="54" t="n">
-        <v>-1.26</v>
-      </c>
+        <v>-1.31</v>
+      </c>
+      <c r="G90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="54" t="inlineStr">
@@ -34179,11 +34474,12 @@
         <v>10</v>
       </c>
       <c r="E91" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3286</v>
       </c>
       <c r="F91" s="54" t="n">
-        <v>-3.14</v>
-      </c>
+        <v>-3.29</v>
+      </c>
+      <c r="G91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="54" t="inlineStr">
@@ -34205,11 +34501,12 @@
         <v>17</v>
       </c>
       <c r="E92" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3286</v>
       </c>
       <c r="F92" s="54" t="n">
-        <v>-5.34</v>
-      </c>
+        <v>-5.59</v>
+      </c>
+      <c r="G92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="54" t="inlineStr">
@@ -34231,11 +34528,12 @@
         <v>8</v>
       </c>
       <c r="E93" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3286</v>
       </c>
       <c r="F93" s="54" t="n">
-        <v>-2.51</v>
-      </c>
+        <v>-2.63</v>
+      </c>
+      <c r="G93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="54" t="inlineStr">
@@ -34257,11 +34555,12 @@
         <v>10</v>
       </c>
       <c r="E94" s="54" t="n">
-        <v>1.5</v>
+        <v>1.6429</v>
       </c>
       <c r="F94" s="54" t="n">
-        <v>-15.71</v>
-      </c>
+        <v>-16.43</v>
+      </c>
+      <c r="G94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="54" t="inlineStr">
@@ -34283,11 +34582,12 @@
         <v>43</v>
       </c>
       <c r="E95" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3286</v>
       </c>
       <c r="F95" s="54" t="n">
-        <v>-13.51</v>
-      </c>
+        <v>-14.13</v>
+      </c>
+      <c r="G95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="53" t="inlineStr">
@@ -34314,6 +34614,7 @@
       <c r="F96" s="53" t="n">
         <v>12</v>
       </c>
+      <c r="G96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="54" t="inlineStr">
@@ -34340,6 +34641,7 @@
       <c r="F97" s="54" t="n">
         <v>-3.5</v>
       </c>
+      <c r="G97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="54" t="inlineStr">
@@ -34361,11 +34663,12 @@
         <v>13</v>
       </c>
       <c r="E98" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3316</v>
       </c>
       <c r="F98" s="54" t="n">
-        <v>-4.52</v>
-      </c>
+        <v>-4.31</v>
+      </c>
+      <c r="G98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="54" t="inlineStr">
@@ -34387,11 +34690,12 @@
         <v>15</v>
       </c>
       <c r="E99" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3316</v>
       </c>
       <c r="F99" s="54" t="n">
-        <v>-5.21</v>
-      </c>
+        <v>-4.97</v>
+      </c>
+      <c r="G99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="54" t="inlineStr">
@@ -34413,11 +34717,12 @@
         <v>15</v>
       </c>
       <c r="E100" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3316</v>
       </c>
       <c r="F100" s="54" t="n">
-        <v>-5.21</v>
-      </c>
+        <v>-4.97</v>
+      </c>
+      <c r="G100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="54" t="inlineStr">
@@ -34439,11 +34744,12 @@
         <v>4</v>
       </c>
       <c r="E101" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3316</v>
       </c>
       <c r="F101" s="54" t="n">
-        <v>-1.39</v>
-      </c>
+        <v>-1.33</v>
+      </c>
+      <c r="G101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="54" t="inlineStr">
@@ -34465,11 +34771,12 @@
         <v>10</v>
       </c>
       <c r="E102" s="54" t="n">
-        <v>1.5</v>
+        <v>1.6579</v>
       </c>
       <c r="F102" s="54" t="n">
-        <v>-17.37</v>
-      </c>
+        <v>-16.58</v>
+      </c>
+      <c r="G102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="54" t="inlineStr">
@@ -34491,11 +34798,12 @@
         <v>1</v>
       </c>
       <c r="E103" s="54" t="n">
-        <v>0.5</v>
+        <v>0.5526</v>
       </c>
       <c r="F103" s="54" t="n">
-        <v>-0.58</v>
-      </c>
+        <v>-0.55</v>
+      </c>
+      <c r="G103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="54" t="inlineStr">
@@ -34517,11 +34825,12 @@
         <v>187</v>
       </c>
       <c r="E104" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3316</v>
       </c>
       <c r="F104" s="54" t="n">
-        <v>-64.95999999999999</v>
-      </c>
+        <v>-62.01</v>
+      </c>
+      <c r="G104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="53" t="inlineStr">
@@ -34548,6 +34857,7 @@
       <c r="F105" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="53" t="inlineStr">
@@ -34574,6 +34884,7 @@
       <c r="F106" s="53" t="n">
         <v>1</v>
       </c>
+      <c r="G106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="54" t="inlineStr">
@@ -34600,6 +34911,7 @@
       <c r="F107" s="54" t="n">
         <v>-1</v>
       </c>
+      <c r="G107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="54" t="inlineStr">
@@ -34621,11 +34933,12 @@
         <v>2</v>
       </c>
       <c r="E108" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F108" s="54" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="54" t="inlineStr">
@@ -34647,11 +34960,12 @@
         <v>2</v>
       </c>
       <c r="E109" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F109" s="54" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="54" t="inlineStr">
@@ -34673,11 +34987,12 @@
         <v>3</v>
       </c>
       <c r="E110" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F110" s="54" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="54" t="inlineStr">
@@ -34699,11 +35014,12 @@
         <v>13</v>
       </c>
       <c r="E111" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F111" s="54" t="n">
         <v>-7.8</v>
       </c>
+      <c r="G111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="53" t="inlineStr">
@@ -34730,6 +35046,7 @@
       <c r="F112" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="53" t="inlineStr">
@@ -34756,6 +35073,7 @@
       <c r="F113" s="53" t="n">
         <v>15</v>
       </c>
+      <c r="G113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="54" t="inlineStr">
@@ -34782,6 +35100,7 @@
       <c r="F114" s="54" t="n">
         <v>-2.5</v>
       </c>
+      <c r="G114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="54" t="inlineStr">
@@ -34803,11 +35122,12 @@
         <v>1</v>
       </c>
       <c r="E115" s="54" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="F115" s="54" t="n">
         <v>-0.33</v>
       </c>
+      <c r="G115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="54" t="inlineStr">
@@ -34829,11 +35149,12 @@
         <v>12</v>
       </c>
       <c r="E116" s="54" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="F116" s="54" t="n">
         <v>-3.96</v>
       </c>
+      <c r="G116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="54" t="inlineStr">
@@ -34855,11 +35176,12 @@
         <v>8</v>
       </c>
       <c r="E117" s="54" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="F117" s="54" t="n">
         <v>-2.64</v>
       </c>
+      <c r="G117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="54" t="inlineStr">
@@ -34881,11 +35203,12 @@
         <v>7</v>
       </c>
       <c r="E118" s="54" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="F118" s="54" t="n">
         <v>-11.55</v>
       </c>
+      <c r="G118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="54" t="inlineStr">
@@ -34907,11 +35230,12 @@
         <v>2</v>
       </c>
       <c r="E119" s="54" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F119" s="54" t="n">
         <v>-2.2</v>
       </c>
+      <c r="G119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="54" t="inlineStr">
@@ -34933,11 +35257,12 @@
         <v>3</v>
       </c>
       <c r="E120" s="54" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="F120" s="54" t="n">
         <v>-1.65</v>
       </c>
+      <c r="G120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="54" t="inlineStr">
@@ -34959,11 +35284,12 @@
         <v>1</v>
       </c>
       <c r="E121" s="54" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="F121" s="54" t="n">
         <v>-0.55</v>
       </c>
+      <c r="G121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="53" t="inlineStr">
@@ -34990,6 +35316,7 @@
       <c r="F122" s="53" t="n">
         <v>13</v>
       </c>
+      <c r="G122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="54" t="inlineStr">
@@ -35016,6 +35343,7 @@
       <c r="F123" s="54" t="n">
         <v>-2.5</v>
       </c>
+      <c r="G123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="54" t="inlineStr">
@@ -35037,11 +35365,12 @@
         <v>2</v>
       </c>
       <c r="E124" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3667</v>
       </c>
       <c r="F124" s="54" t="n">
         <v>-0.73</v>
       </c>
+      <c r="G124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="54" t="inlineStr">
@@ -35063,11 +35392,12 @@
         <v>8</v>
       </c>
       <c r="E125" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3667</v>
       </c>
       <c r="F125" s="54" t="n">
         <v>-2.93</v>
       </c>
+      <c r="G125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="54" t="inlineStr">
@@ -35089,11 +35419,12 @@
         <v>10</v>
       </c>
       <c r="E126" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3667</v>
       </c>
       <c r="F126" s="54" t="n">
         <v>-3.67</v>
       </c>
+      <c r="G126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="54" t="inlineStr">
@@ -35115,11 +35446,12 @@
         <v>3</v>
       </c>
       <c r="E127" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3667</v>
       </c>
       <c r="F127" s="54" t="n">
         <v>-1.1</v>
       </c>
+      <c r="G127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="54" t="inlineStr">
@@ -35141,11 +35473,12 @@
         <v>12</v>
       </c>
       <c r="E128" s="54" t="n">
-        <v>1.5</v>
+        <v>1.8333</v>
       </c>
       <c r="F128" s="54" t="n">
         <v>-22</v>
       </c>
+      <c r="G128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="54" t="inlineStr">
@@ -35167,11 +35500,12 @@
         <v>3</v>
       </c>
       <c r="E129" s="54" t="n">
-        <v>0.5</v>
+        <v>0.6111</v>
       </c>
       <c r="F129" s="54" t="n">
         <v>-1.83</v>
       </c>
+      <c r="G129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="54" t="inlineStr">
@@ -35193,11 +35527,12 @@
         <v>40</v>
       </c>
       <c r="E130" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3667</v>
       </c>
       <c r="F130" s="54" t="n">
         <v>-14.67</v>
       </c>
+      <c r="G130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="53" t="inlineStr">
@@ -35224,6 +35559,7 @@
       <c r="F131" s="53" t="n">
         <v>12</v>
       </c>
+      <c r="G131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="54" t="inlineStr">
@@ -35250,6 +35586,7 @@
       <c r="F132" s="54" t="n">
         <v>-5</v>
       </c>
+      <c r="G132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="54" t="inlineStr">
@@ -35271,11 +35608,12 @@
         <v>3</v>
       </c>
       <c r="E133" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3136</v>
       </c>
       <c r="F133" s="54" t="n">
-        <v>-0.9</v>
-      </c>
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="G133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="54" t="inlineStr">
@@ -35297,11 +35635,12 @@
         <v>6</v>
       </c>
       <c r="E134" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3136</v>
       </c>
       <c r="F134" s="54" t="n">
-        <v>-1.8</v>
-      </c>
+        <v>-1.88</v>
+      </c>
+      <c r="G134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="54" t="inlineStr">
@@ -35323,11 +35662,12 @@
         <v>9</v>
       </c>
       <c r="E135" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3136</v>
       </c>
       <c r="F135" s="54" t="n">
-        <v>-2.7</v>
-      </c>
+        <v>-2.82</v>
+      </c>
+      <c r="G135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="54" t="inlineStr">
@@ -35349,11 +35689,12 @@
         <v>9</v>
       </c>
       <c r="E136" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3136</v>
       </c>
       <c r="F136" s="54" t="n">
-        <v>-2.7</v>
-      </c>
+        <v>-2.82</v>
+      </c>
+      <c r="G136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="54" t="inlineStr">
@@ -35375,11 +35716,12 @@
         <v>7</v>
       </c>
       <c r="E137" s="54" t="n">
-        <v>1.5</v>
+        <v>1.5682</v>
       </c>
       <c r="F137" s="54" t="n">
-        <v>-10.5</v>
-      </c>
+        <v>-10.98</v>
+      </c>
+      <c r="G137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="54" t="inlineStr">
@@ -35401,11 +35743,12 @@
         <v>2</v>
       </c>
       <c r="E138" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3136</v>
       </c>
       <c r="F138" s="54" t="n">
-        <v>-0.6</v>
-      </c>
+        <v>-0.63</v>
+      </c>
+      <c r="G138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="54" t="inlineStr">
@@ -35427,11 +35770,12 @@
         <v>2</v>
       </c>
       <c r="E139" s="54" t="n">
-        <v>1</v>
+        <v>1.0455</v>
       </c>
       <c r="F139" s="54" t="n">
-        <v>-2</v>
-      </c>
+        <v>-2.09</v>
+      </c>
+      <c r="G139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="54" t="inlineStr">
@@ -35453,11 +35797,12 @@
         <v>10</v>
       </c>
       <c r="E140" s="54" t="n">
-        <v>0.5</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="F140" s="54" t="n">
-        <v>-5</v>
-      </c>
+        <v>-5.23</v>
+      </c>
+      <c r="G140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="54" t="inlineStr">
@@ -35479,11 +35824,12 @@
         <v>189</v>
       </c>
       <c r="E141" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3136</v>
       </c>
       <c r="F141" s="54" t="n">
-        <v>-56.7</v>
-      </c>
+        <v>-59.28</v>
+      </c>
+      <c r="G141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="53" t="inlineStr">
@@ -35510,6 +35856,7 @@
       <c r="F142" s="53" t="n">
         <v>17</v>
       </c>
+      <c r="G142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="54" t="inlineStr">
@@ -35536,6 +35883,7 @@
       <c r="F143" s="54" t="n">
         <v>-3</v>
       </c>
+      <c r="G143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="54" t="inlineStr">
@@ -35557,11 +35905,12 @@
         <v>3</v>
       </c>
       <c r="E144" s="54" t="n">
-        <v>0.3</v>
+        <v>0.287</v>
       </c>
       <c r="F144" s="54" t="n">
         <v>-0.86</v>
       </c>
+      <c r="G144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="54" t="inlineStr">
@@ -35583,11 +35932,12 @@
         <v>3</v>
       </c>
       <c r="E145" s="54" t="n">
-        <v>0.3</v>
+        <v>0.287</v>
       </c>
       <c r="F145" s="54" t="n">
         <v>-0.86</v>
       </c>
+      <c r="G145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="54" t="inlineStr">
@@ -35609,11 +35959,12 @@
         <v>6</v>
       </c>
       <c r="E146" s="54" t="n">
-        <v>1.5</v>
+        <v>1.4348</v>
       </c>
       <c r="F146" s="54" t="n">
         <v>-8.609999999999999</v>
       </c>
+      <c r="G146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="54" t="inlineStr">
@@ -35635,11 +35986,12 @@
         <v>3</v>
       </c>
       <c r="E147" s="54" t="n">
-        <v>1</v>
+        <v>0.9565</v>
       </c>
       <c r="F147" s="54" t="n">
         <v>-2.87</v>
       </c>
+      <c r="G147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="54" t="inlineStr">
@@ -35661,11 +36013,12 @@
         <v>24</v>
       </c>
       <c r="E148" s="54" t="n">
-        <v>0.5</v>
+        <v>0.4783</v>
       </c>
       <c r="F148" s="54" t="n">
         <v>-11.48</v>
       </c>
+      <c r="G148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="54" t="inlineStr">
@@ -35687,11 +36040,12 @@
         <v>21</v>
       </c>
       <c r="E149" s="54" t="n">
-        <v>0.3</v>
+        <v>0.287</v>
       </c>
       <c r="F149" s="54" t="n">
         <v>-6.03</v>
       </c>
+      <c r="G149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="53" t="inlineStr">
@@ -35718,6 +36072,7 @@
       <c r="F150" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="53" t="inlineStr">
@@ -35744,6 +36099,7 @@
       <c r="F151" s="53" t="n">
         <v>15</v>
       </c>
+      <c r="G151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="54" t="inlineStr">
@@ -35770,6 +36126,7 @@
       <c r="F152" s="54" t="n">
         <v>-2.5</v>
       </c>
+      <c r="G152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="54" t="inlineStr">
@@ -35791,11 +36148,12 @@
         <v>1</v>
       </c>
       <c r="E153" s="54" t="n">
-        <v>0.3</v>
+        <v>0.315</v>
       </c>
       <c r="F153" s="54" t="n">
-        <v>-0.33</v>
-      </c>
+        <v>-0.32</v>
+      </c>
+      <c r="G153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="54" t="inlineStr">
@@ -35817,11 +36175,12 @@
         <v>10</v>
       </c>
       <c r="E154" s="54" t="n">
-        <v>0.3</v>
+        <v>0.315</v>
       </c>
       <c r="F154" s="54" t="n">
-        <v>-3.3</v>
-      </c>
+        <v>-3.15</v>
+      </c>
+      <c r="G154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="54" t="inlineStr">
@@ -35843,11 +36202,12 @@
         <v>17</v>
       </c>
       <c r="E155" s="54" t="n">
-        <v>0.3</v>
+        <v>0.315</v>
       </c>
       <c r="F155" s="54" t="n">
-        <v>-5.61</v>
-      </c>
+        <v>-5.36</v>
+      </c>
+      <c r="G155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="54" t="inlineStr">
@@ -35869,11 +36229,12 @@
         <v>1</v>
       </c>
       <c r="E156" s="54" t="n">
-        <v>0.3</v>
+        <v>0.315</v>
       </c>
       <c r="F156" s="54" t="n">
-        <v>-0.33</v>
-      </c>
+        <v>-0.32</v>
+      </c>
+      <c r="G156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="54" t="inlineStr">
@@ -35895,11 +36256,12 @@
         <v>10</v>
       </c>
       <c r="E157" s="54" t="n">
-        <v>1.5</v>
+        <v>1.575</v>
       </c>
       <c r="F157" s="54" t="n">
-        <v>-16.5</v>
-      </c>
+        <v>-15.75</v>
+      </c>
+      <c r="G157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="54" t="inlineStr">
@@ -35921,11 +36283,12 @@
         <v>2</v>
       </c>
       <c r="E158" s="54" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="F158" s="54" t="n">
-        <v>-2.2</v>
-      </c>
+        <v>-2.1</v>
+      </c>
+      <c r="G158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="54" t="inlineStr">
@@ -35947,11 +36310,12 @@
         <v>1</v>
       </c>
       <c r="E159" s="54" t="n">
-        <v>0.5</v>
+        <v>0.525</v>
       </c>
       <c r="F159" s="54" t="n">
-        <v>-0.55</v>
-      </c>
+        <v>-0.53</v>
+      </c>
+      <c r="G159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="53" t="inlineStr">
@@ -35978,6 +36342,7 @@
       <c r="F160" s="53" t="n">
         <v>13</v>
       </c>
+      <c r="G160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="54" t="inlineStr">
@@ -36004,6 +36369,7 @@
       <c r="F161" s="54" t="n">
         <v>-4</v>
       </c>
+      <c r="G161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="54" t="inlineStr">
@@ -36025,11 +36391,12 @@
         <v>1</v>
       </c>
       <c r="E162" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3286</v>
       </c>
       <c r="F162" s="54" t="n">
-        <v>-0.31</v>
-      </c>
+        <v>-0.33</v>
+      </c>
+      <c r="G162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="54" t="inlineStr">
@@ -36051,11 +36418,12 @@
         <v>6</v>
       </c>
       <c r="E163" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3286</v>
       </c>
       <c r="F163" s="54" t="n">
-        <v>-1.89</v>
-      </c>
+        <v>-1.97</v>
+      </c>
+      <c r="G163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="54" t="inlineStr">
@@ -36077,11 +36445,12 @@
         <v>5</v>
       </c>
       <c r="E164" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3286</v>
       </c>
       <c r="F164" s="54" t="n">
-        <v>-1.57</v>
-      </c>
+        <v>-1.64</v>
+      </c>
+      <c r="G164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="54" t="inlineStr">
@@ -36103,11 +36472,12 @@
         <v>2</v>
       </c>
       <c r="E165" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3286</v>
       </c>
       <c r="F165" s="54" t="n">
-        <v>-0.63</v>
-      </c>
+        <v>-0.66</v>
+      </c>
+      <c r="G165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="54" t="inlineStr">
@@ -36129,11 +36499,12 @@
         <v>12</v>
       </c>
       <c r="E166" s="54" t="n">
-        <v>1.5</v>
+        <v>1.6429</v>
       </c>
       <c r="F166" s="54" t="n">
-        <v>-18.86</v>
-      </c>
+        <v>-19.71</v>
+      </c>
+      <c r="G166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="54" t="inlineStr">
@@ -36155,11 +36526,12 @@
         <v>6</v>
       </c>
       <c r="E167" s="54" t="n">
-        <v>1</v>
+        <v>1.0952</v>
       </c>
       <c r="F167" s="54" t="n">
-        <v>-6.29</v>
-      </c>
+        <v>-6.57</v>
+      </c>
+      <c r="G167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="54" t="inlineStr">
@@ -36181,11 +36553,12 @@
         <v>10</v>
       </c>
       <c r="E168" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3286</v>
       </c>
       <c r="F168" s="54" t="n">
-        <v>-3.14</v>
-      </c>
+        <v>-3.29</v>
+      </c>
+      <c r="G168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="53" t="inlineStr">
@@ -36212,6 +36585,7 @@
       <c r="F169" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="53" t="inlineStr">
@@ -36238,6 +36612,7 @@
       <c r="F170" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="53" t="inlineStr">
@@ -36264,6 +36639,7 @@
       <c r="F171" s="53" t="n">
         <v>2</v>
       </c>
+      <c r="G171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="54" t="inlineStr">
@@ -36290,6 +36666,7 @@
       <c r="F172" s="54" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="54" t="inlineStr">
@@ -36311,11 +36688,12 @@
         <v>1</v>
       </c>
       <c r="E173" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F173" s="54" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="54" t="inlineStr">
@@ -36337,11 +36715,12 @@
         <v>3</v>
       </c>
       <c r="E174" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F174" s="54" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="53" t="inlineStr">
@@ -36368,6 +36747,7 @@
       <c r="F175" s="53" t="n">
         <v>13</v>
       </c>
+      <c r="G175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="54" t="inlineStr">
@@ -36394,6 +36774,7 @@
       <c r="F176" s="54" t="n">
         <v>-5</v>
       </c>
+      <c r="G176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="54" t="inlineStr">
@@ -36415,11 +36796,12 @@
         <v>3</v>
       </c>
       <c r="E177" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2739</v>
       </c>
       <c r="F177" s="54" t="n">
-        <v>-0.86</v>
-      </c>
+        <v>-0.82</v>
+      </c>
+      <c r="G177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="54" t="inlineStr">
@@ -36441,11 +36823,12 @@
         <v>7</v>
       </c>
       <c r="E178" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2739</v>
       </c>
       <c r="F178" s="54" t="n">
-        <v>-2.01</v>
-      </c>
+        <v>-1.92</v>
+      </c>
+      <c r="G178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="54" t="inlineStr">
@@ -36467,11 +36850,12 @@
         <v>15</v>
       </c>
       <c r="E179" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2739</v>
       </c>
       <c r="F179" s="54" t="n">
-        <v>-4.3</v>
-      </c>
+        <v>-4.11</v>
+      </c>
+      <c r="G179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="54" t="inlineStr">
@@ -36493,11 +36877,12 @@
         <v>7</v>
       </c>
       <c r="E180" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2739</v>
       </c>
       <c r="F180" s="54" t="n">
-        <v>-2.01</v>
-      </c>
+        <v>-1.92</v>
+      </c>
+      <c r="G180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="54" t="inlineStr">
@@ -36519,11 +36904,12 @@
         <v>7</v>
       </c>
       <c r="E181" s="54" t="n">
-        <v>1.5</v>
+        <v>1.3696</v>
       </c>
       <c r="F181" s="54" t="n">
-        <v>-10.04</v>
-      </c>
+        <v>-9.59</v>
+      </c>
+      <c r="G181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="54" t="inlineStr">
@@ -36545,11 +36931,12 @@
         <v>4</v>
       </c>
       <c r="E182" s="54" t="n">
-        <v>1</v>
+        <v>0.913</v>
       </c>
       <c r="F182" s="54" t="n">
-        <v>-3.83</v>
-      </c>
+        <v>-3.65</v>
+      </c>
+      <c r="G182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="54" t="inlineStr">
@@ -36571,11 +36958,12 @@
         <v>94</v>
       </c>
       <c r="E183" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2739</v>
       </c>
       <c r="F183" s="54" t="n">
-        <v>-26.97</v>
-      </c>
+        <v>-25.75</v>
+      </c>
+      <c r="G183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="53" t="inlineStr">
@@ -36602,6 +36990,7 @@
       <c r="F184" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="53" t="inlineStr">
@@ -36628,6 +37017,7 @@
       <c r="F185" s="53" t="n">
         <v>12</v>
       </c>
+      <c r="G185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="54" t="inlineStr">
@@ -36654,6 +37044,7 @@
       <c r="F186" s="54" t="n">
         <v>-5</v>
       </c>
+      <c r="G186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="54" t="inlineStr">
@@ -36675,11 +37066,12 @@
         <v>6</v>
       </c>
       <c r="E187" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3136</v>
       </c>
       <c r="F187" s="54" t="n">
-        <v>-1.8</v>
-      </c>
+        <v>-1.88</v>
+      </c>
+      <c r="G187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="54" t="inlineStr">
@@ -36701,11 +37093,12 @@
         <v>15</v>
       </c>
       <c r="E188" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3136</v>
       </c>
       <c r="F188" s="54" t="n">
-        <v>-4.5</v>
-      </c>
+        <v>-4.7</v>
+      </c>
+      <c r="G188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="54" t="inlineStr">
@@ -36727,11 +37120,12 @@
         <v>8</v>
       </c>
       <c r="E189" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3136</v>
       </c>
       <c r="F189" s="54" t="n">
-        <v>-2.4</v>
-      </c>
+        <v>-2.51</v>
+      </c>
+      <c r="G189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="54" t="inlineStr">
@@ -36753,11 +37147,12 @@
         <v>7</v>
       </c>
       <c r="E190" s="54" t="n">
-        <v>1.5</v>
+        <v>1.5682</v>
       </c>
       <c r="F190" s="54" t="n">
-        <v>-10.5</v>
-      </c>
+        <v>-10.98</v>
+      </c>
+      <c r="G190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="54" t="inlineStr">
@@ -36779,11 +37174,12 @@
         <v>3</v>
       </c>
       <c r="E191" s="54" t="n">
-        <v>0.5</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="F191" s="54" t="n">
-        <v>-1.5</v>
-      </c>
+        <v>-1.57</v>
+      </c>
+      <c r="G191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="54" t="inlineStr">
@@ -36805,11 +37201,12 @@
         <v>1</v>
       </c>
       <c r="E192" s="54" t="n">
-        <v>0.5</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="F192" s="54" t="n">
-        <v>-0.5</v>
-      </c>
+        <v>-0.52</v>
+      </c>
+      <c r="G192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="53" t="inlineStr">
@@ -36836,6 +37233,7 @@
       <c r="F193" s="53" t="n">
         <v>17</v>
       </c>
+      <c r="G193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="54" t="inlineStr">
@@ -36862,6 +37260,7 @@
       <c r="F194" s="54" t="n">
         <v>-1.5</v>
       </c>
+      <c r="G194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="54" t="inlineStr">
@@ -36883,11 +37282,12 @@
         <v>7</v>
       </c>
       <c r="E195" s="54" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="F195" s="54" t="n">
         <v>-2.31</v>
       </c>
+      <c r="G195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="54" t="inlineStr">
@@ -36909,11 +37309,12 @@
         <v>17</v>
       </c>
       <c r="E196" s="54" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="F196" s="54" t="n">
         <v>-5.61</v>
       </c>
+      <c r="G196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="54" t="inlineStr">
@@ -36935,11 +37336,12 @@
         <v>1</v>
       </c>
       <c r="E197" s="54" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="F197" s="54" t="n">
         <v>-0.33</v>
       </c>
+      <c r="G197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="54" t="inlineStr">
@@ -36961,11 +37363,12 @@
         <v>8</v>
       </c>
       <c r="E198" s="54" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="F198" s="54" t="n">
         <v>-13.2</v>
       </c>
+      <c r="G198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="54" t="inlineStr">
@@ -36987,11 +37390,12 @@
         <v>2</v>
       </c>
       <c r="E199" s="54" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="F199" s="54" t="n">
         <v>-0.66</v>
       </c>
+      <c r="G199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="53" t="inlineStr">
@@ -37018,6 +37422,7 @@
       <c r="F200" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="53" t="inlineStr">
@@ -37044,6 +37449,7 @@
       <c r="F201" s="53" t="n">
         <v>2</v>
       </c>
+      <c r="G201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="54" t="inlineStr">
@@ -37070,6 +37476,7 @@
       <c r="F202" s="54" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="54" t="inlineStr">
@@ -37091,11 +37498,12 @@
         <v>2</v>
       </c>
       <c r="E203" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F203" s="54" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="54" t="inlineStr">
@@ -37117,11 +37525,12 @@
         <v>2</v>
       </c>
       <c r="E204" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F204" s="54" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="54" t="inlineStr">
@@ -37143,11 +37552,12 @@
         <v>2</v>
       </c>
       <c r="E205" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F205" s="54" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="54" t="inlineStr">
@@ -37169,11 +37579,12 @@
         <v>14</v>
       </c>
       <c r="E206" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F206" s="54" t="n">
         <v>-8.4</v>
       </c>
+      <c r="G206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="53" t="inlineStr">
@@ -37200,6 +37611,7 @@
       <c r="F207" s="53" t="n">
         <v>12</v>
       </c>
+      <c r="G207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="54" t="inlineStr">
@@ -37226,6 +37638,7 @@
       <c r="F208" s="54" t="n">
         <v>-4.5</v>
       </c>
+      <c r="G208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="54" t="inlineStr">
@@ -37247,11 +37660,12 @@
         <v>1</v>
       </c>
       <c r="E209" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3286</v>
       </c>
       <c r="F209" s="54" t="n">
-        <v>-0.31</v>
-      </c>
+        <v>-0.33</v>
+      </c>
+      <c r="G209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="54" t="inlineStr">
@@ -37273,11 +37687,12 @@
         <v>17</v>
       </c>
       <c r="E210" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3286</v>
       </c>
       <c r="F210" s="54" t="n">
-        <v>-5.34</v>
-      </c>
+        <v>-5.59</v>
+      </c>
+      <c r="G210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="54" t="inlineStr">
@@ -37299,11 +37714,12 @@
         <v>10</v>
       </c>
       <c r="E211" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3286</v>
       </c>
       <c r="F211" s="54" t="n">
-        <v>-3.14</v>
-      </c>
+        <v>-3.29</v>
+      </c>
+      <c r="G211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="54" t="inlineStr">
@@ -37325,11 +37741,12 @@
         <v>11</v>
       </c>
       <c r="E212" s="54" t="n">
-        <v>1.5</v>
+        <v>1.6429</v>
       </c>
       <c r="F212" s="54" t="n">
-        <v>-17.29</v>
-      </c>
+        <v>-18.07</v>
+      </c>
+      <c r="G212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="54" t="inlineStr">
@@ -37351,11 +37768,12 @@
         <v>4</v>
       </c>
       <c r="E213" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3286</v>
       </c>
       <c r="F213" s="54" t="n">
-        <v>-1.26</v>
-      </c>
+        <v>-1.31</v>
+      </c>
+      <c r="G213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="53" t="inlineStr">
@@ -37382,6 +37800,7 @@
       <c r="F214" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="54" t="inlineStr">
@@ -37408,6 +37827,7 @@
       <c r="F215" s="54" t="n">
         <v>-1</v>
       </c>
+      <c r="G215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="54" t="inlineStr">
@@ -37429,11 +37849,12 @@
         <v>1</v>
       </c>
       <c r="E216" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F216" s="54" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="54" t="inlineStr">
@@ -37455,11 +37876,12 @@
         <v>1</v>
       </c>
       <c r="E217" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F217" s="54" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="54" t="inlineStr">
@@ -37481,11 +37903,12 @@
         <v>2</v>
       </c>
       <c r="E218" s="54" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F218" s="54" t="n">
         <v>-6</v>
       </c>
+      <c r="G218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="53" t="inlineStr">
@@ -37512,6 +37935,7 @@
       <c r="F219" s="53" t="n">
         <v>14</v>
       </c>
+      <c r="G219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="54" t="inlineStr">
@@ -37538,6 +37962,7 @@
       <c r="F220" s="54" t="n">
         <v>-3.5</v>
       </c>
+      <c r="G220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="54" t="inlineStr">
@@ -37559,11 +37984,12 @@
         <v>3</v>
       </c>
       <c r="E221" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3143</v>
       </c>
       <c r="F221" s="54" t="n">
         <v>-0.9399999999999999</v>
       </c>
+      <c r="G221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="54" t="inlineStr">
@@ -37585,11 +38011,12 @@
         <v>2</v>
       </c>
       <c r="E222" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3143</v>
       </c>
       <c r="F222" s="54" t="n">
         <v>-0.63</v>
       </c>
+      <c r="G222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="54" t="inlineStr">
@@ -37611,11 +38038,12 @@
         <v>6</v>
       </c>
       <c r="E223" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3143</v>
       </c>
       <c r="F223" s="54" t="n">
         <v>-1.89</v>
       </c>
+      <c r="G223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="54" t="inlineStr">
@@ -37637,11 +38065,12 @@
         <v>2</v>
       </c>
       <c r="E224" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3143</v>
       </c>
       <c r="F224" s="54" t="n">
         <v>-0.63</v>
       </c>
+      <c r="G224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="54" t="inlineStr">
@@ -37663,11 +38092,12 @@
         <v>5</v>
       </c>
       <c r="E225" s="54" t="n">
-        <v>1.5</v>
+        <v>1.5714</v>
       </c>
       <c r="F225" s="54" t="n">
         <v>-7.86</v>
       </c>
+      <c r="G225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="54" t="inlineStr">
@@ -37689,11 +38119,12 @@
         <v>2</v>
       </c>
       <c r="E226" s="54" t="n">
-        <v>1</v>
+        <v>1.0476</v>
       </c>
       <c r="F226" s="54" t="n">
         <v>-2.1</v>
       </c>
+      <c r="G226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="54" t="inlineStr">
@@ -37715,11 +38146,12 @@
         <v>3</v>
       </c>
       <c r="E227" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3143</v>
       </c>
       <c r="F227" s="54" t="n">
         <v>-0.9399999999999999</v>
       </c>
+      <c r="G227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="53" t="inlineStr">
@@ -37746,6 +38178,7 @@
       <c r="F228" s="53" t="n">
         <v>17</v>
       </c>
+      <c r="G228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="54" t="inlineStr">
@@ -37772,6 +38205,7 @@
       <c r="F229" s="54" t="n">
         <v>-3</v>
       </c>
+      <c r="G229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="54" t="inlineStr">
@@ -37793,11 +38227,12 @@
         <v>9</v>
       </c>
       <c r="E230" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2739</v>
       </c>
       <c r="F230" s="54" t="n">
-        <v>-2.58</v>
-      </c>
+        <v>-2.47</v>
+      </c>
+      <c r="G230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="54" t="inlineStr">
@@ -37819,11 +38254,12 @@
         <v>15</v>
       </c>
       <c r="E231" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2739</v>
       </c>
       <c r="F231" s="54" t="n">
-        <v>-4.3</v>
-      </c>
+        <v>-4.11</v>
+      </c>
+      <c r="G231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="54" t="inlineStr">
@@ -37845,11 +38281,12 @@
         <v>16</v>
       </c>
       <c r="E232" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2739</v>
       </c>
       <c r="F232" s="54" t="n">
-        <v>-4.59</v>
-      </c>
+        <v>-4.38</v>
+      </c>
+      <c r="G232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="54" t="inlineStr">
@@ -37871,11 +38308,12 @@
         <v>2</v>
       </c>
       <c r="E233" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2739</v>
       </c>
       <c r="F233" s="54" t="n">
-        <v>-0.57</v>
-      </c>
+        <v>-0.55</v>
+      </c>
+      <c r="G233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="54" t="inlineStr">
@@ -37897,11 +38335,12 @@
         <v>5</v>
       </c>
       <c r="E234" s="54" t="n">
-        <v>1.5</v>
+        <v>1.3696</v>
       </c>
       <c r="F234" s="54" t="n">
-        <v>-7.17</v>
-      </c>
+        <v>-6.85</v>
+      </c>
+      <c r="G234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="54" t="inlineStr">
@@ -37923,11 +38362,12 @@
         <v>9</v>
       </c>
       <c r="E235" s="54" t="n">
-        <v>0.5</v>
+        <v>0.4565</v>
       </c>
       <c r="F235" s="54" t="n">
-        <v>-4.3</v>
-      </c>
+        <v>-4.11</v>
+      </c>
+      <c r="G235" s="2" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="54" t="inlineStr">
@@ -37949,11 +38389,12 @@
         <v>7</v>
       </c>
       <c r="E236" s="54" t="n">
-        <v>0.5</v>
+        <v>0.4565</v>
       </c>
       <c r="F236" s="54" t="n">
-        <v>-3.35</v>
-      </c>
+        <v>-3.2</v>
+      </c>
+      <c r="G236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="54" t="inlineStr">
@@ -37975,11 +38416,12 @@
         <v>4</v>
       </c>
       <c r="E237" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2739</v>
       </c>
       <c r="F237" s="54" t="n">
-        <v>-1.15</v>
-      </c>
+        <v>-1.1</v>
+      </c>
+      <c r="G237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="53" t="inlineStr">
@@ -38006,6 +38448,7 @@
       <c r="F238" s="53" t="n">
         <v>12</v>
       </c>
+      <c r="G238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="54" t="inlineStr">
@@ -38032,6 +38475,7 @@
       <c r="F239" s="54" t="n">
         <v>-2.5</v>
       </c>
+      <c r="G239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="54" t="inlineStr">
@@ -38053,11 +38497,12 @@
         <v>2</v>
       </c>
       <c r="E240" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3882</v>
       </c>
       <c r="F240" s="54" t="n">
         <v>-0.78</v>
       </c>
+      <c r="G240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="54" t="inlineStr">
@@ -38079,11 +38524,12 @@
         <v>16</v>
       </c>
       <c r="E241" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3882</v>
       </c>
       <c r="F241" s="54" t="n">
         <v>-6.21</v>
       </c>
+      <c r="G241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="54" t="inlineStr">
@@ -38105,11 +38551,12 @@
         <v>2</v>
       </c>
       <c r="E242" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3882</v>
       </c>
       <c r="F242" s="54" t="n">
         <v>-0.78</v>
       </c>
+      <c r="G242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="54" t="inlineStr">
@@ -38131,11 +38578,12 @@
         <v>15</v>
       </c>
       <c r="E243" s="54" t="n">
-        <v>1.5</v>
+        <v>1.9412</v>
       </c>
       <c r="F243" s="54" t="n">
         <v>-29.12</v>
       </c>
+      <c r="G243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="54" t="inlineStr">
@@ -38157,11 +38605,12 @@
         <v>180</v>
       </c>
       <c r="E244" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3882</v>
       </c>
       <c r="F244" s="54" t="n">
         <v>-69.88</v>
       </c>
+      <c r="G244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="53" t="inlineStr">
@@ -38188,6 +38637,7 @@
       <c r="F245" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="53" t="inlineStr">
@@ -38214,6 +38664,7 @@
       <c r="F246" s="53" t="n">
         <v>1</v>
       </c>
+      <c r="G246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="54" t="inlineStr">
@@ -38240,6 +38691,7 @@
       <c r="F247" s="54" t="n">
         <v>-1</v>
       </c>
+      <c r="G247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="54" t="inlineStr">
@@ -38261,11 +38713,12 @@
         <v>1</v>
       </c>
       <c r="E248" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F248" s="54" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="54" t="inlineStr">
@@ -38287,11 +38740,12 @@
         <v>2</v>
       </c>
       <c r="E249" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F249" s="54" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="54" t="inlineStr">
@@ -38313,11 +38767,12 @@
         <v>2</v>
       </c>
       <c r="E250" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F250" s="54" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="54" t="inlineStr">
@@ -38339,11 +38794,12 @@
         <v>1</v>
       </c>
       <c r="E251" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F251" s="54" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="53" t="inlineStr">
@@ -38370,6 +38826,7 @@
       <c r="F252" s="53" t="n">
         <v>13</v>
       </c>
+      <c r="G252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="54" t="inlineStr">
@@ -38396,6 +38853,7 @@
       <c r="F253" s="54" t="n">
         <v>-1</v>
       </c>
+      <c r="G253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="54" t="inlineStr">
@@ -38417,11 +38875,12 @@
         <v>1</v>
       </c>
       <c r="E254" s="54" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="F254" s="54" t="n">
-        <v>-0.44</v>
-      </c>
+        <v>-0.42</v>
+      </c>
+      <c r="G254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="54" t="inlineStr">
@@ -38443,11 +38902,12 @@
         <v>3</v>
       </c>
       <c r="E255" s="54" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="F255" s="54" t="n">
-        <v>-1.32</v>
-      </c>
+        <v>-1.26</v>
+      </c>
+      <c r="G255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="54" t="inlineStr">
@@ -38469,11 +38929,12 @@
         <v>9</v>
       </c>
       <c r="E256" s="54" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="F256" s="54" t="n">
-        <v>-3.96</v>
-      </c>
+        <v>-3.78</v>
+      </c>
+      <c r="G256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="54" t="inlineStr">
@@ -38495,11 +38956,12 @@
         <v>5</v>
       </c>
       <c r="E257" s="54" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="F257" s="54" t="n">
-        <v>-2.2</v>
-      </c>
+        <v>-2.1</v>
+      </c>
+      <c r="G257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="54" t="inlineStr">
@@ -38521,11 +38983,12 @@
         <v>16</v>
       </c>
       <c r="E258" s="54" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="F258" s="54" t="n">
-        <v>-35.2</v>
-      </c>
+        <v>-33.6</v>
+      </c>
+      <c r="G258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="54" t="inlineStr">
@@ -38547,11 +39010,12 @@
         <v>194</v>
       </c>
       <c r="E259" s="54" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="F259" s="54" t="n">
-        <v>-85.36</v>
-      </c>
+        <v>-81.48</v>
+      </c>
+      <c r="G259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="53" t="inlineStr">
@@ -38578,6 +39042,7 @@
       <c r="F260" s="53" t="n">
         <v>15</v>
       </c>
+      <c r="G260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="54" t="inlineStr">
@@ -38604,6 +39069,7 @@
       <c r="F261" s="54" t="n">
         <v>-2.5</v>
       </c>
+      <c r="G261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="54" t="inlineStr">
@@ -38625,11 +39091,12 @@
         <v>5</v>
       </c>
       <c r="E262" s="54" t="n">
-        <v>0.3</v>
+        <v>0.315</v>
       </c>
       <c r="F262" s="54" t="n">
-        <v>-1.65</v>
-      </c>
+        <v>-1.57</v>
+      </c>
+      <c r="G262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="54" t="inlineStr">
@@ -38651,11 +39118,12 @@
         <v>14</v>
       </c>
       <c r="E263" s="54" t="n">
-        <v>0.3</v>
+        <v>0.315</v>
       </c>
       <c r="F263" s="54" t="n">
-        <v>-4.62</v>
-      </c>
+        <v>-4.41</v>
+      </c>
+      <c r="G263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="54" t="inlineStr">
@@ -38677,11 +39145,12 @@
         <v>16</v>
       </c>
       <c r="E264" s="54" t="n">
-        <v>0.3</v>
+        <v>0.315</v>
       </c>
       <c r="F264" s="54" t="n">
-        <v>-5.28</v>
-      </c>
+        <v>-5.04</v>
+      </c>
+      <c r="G264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="54" t="inlineStr">
@@ -38703,11 +39172,12 @@
         <v>10</v>
       </c>
       <c r="E265" s="54" t="n">
-        <v>0.3</v>
+        <v>0.315</v>
       </c>
       <c r="F265" s="54" t="n">
-        <v>-3.3</v>
-      </c>
+        <v>-3.15</v>
+      </c>
+      <c r="G265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="54" t="inlineStr">
@@ -38729,11 +39199,12 @@
         <v>10</v>
       </c>
       <c r="E266" s="54" t="n">
-        <v>1.5</v>
+        <v>1.575</v>
       </c>
       <c r="F266" s="54" t="n">
-        <v>-16.5</v>
-      </c>
+        <v>-15.75</v>
+      </c>
+      <c r="G266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="54" t="inlineStr">
@@ -38755,11 +39226,12 @@
         <v>210</v>
       </c>
       <c r="E267" s="54" t="n">
-        <v>0.3</v>
+        <v>0.315</v>
       </c>
       <c r="F267" s="54" t="n">
-        <v>-69.3</v>
-      </c>
+        <v>-66.15000000000001</v>
+      </c>
+      <c r="G267" s="2" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="53" t="inlineStr">
@@ -38786,6 +39258,7 @@
       <c r="F268" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G268" s="2" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="53" t="inlineStr">
@@ -38812,6 +39285,7 @@
       <c r="F269" s="53" t="n">
         <v>1</v>
       </c>
+      <c r="G269" s="2" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="54" t="inlineStr">
@@ -38838,6 +39312,7 @@
       <c r="F270" s="54" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="54" t="inlineStr">
@@ -38859,11 +39334,12 @@
         <v>2</v>
       </c>
       <c r="E271" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F271" s="54" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G271" s="2" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="54" t="inlineStr">
@@ -38885,11 +39361,12 @@
         <v>2</v>
       </c>
       <c r="E272" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F272" s="54" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="54" t="inlineStr">
@@ -38911,11 +39388,12 @@
         <v>9</v>
       </c>
       <c r="E273" s="54" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F273" s="54" t="n">
         <v>-9</v>
       </c>
+      <c r="G273" s="2" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="54" t="inlineStr">
@@ -38937,11 +39415,12 @@
         <v>4</v>
       </c>
       <c r="E274" s="54" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F274" s="54" t="n">
         <v>-4</v>
       </c>
+      <c r="G274" s="2" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="54" t="inlineStr">
@@ -38963,11 +39442,12 @@
         <v>6</v>
       </c>
       <c r="E275" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F275" s="54" t="n">
         <v>-3.6</v>
       </c>
+      <c r="G275" s="2" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="53" t="inlineStr">
@@ -38994,6 +39474,7 @@
       <c r="F276" s="53" t="n">
         <v>9</v>
       </c>
+      <c r="G276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="54" t="inlineStr">
@@ -39020,6 +39501,7 @@
       <c r="F277" s="54" t="n">
         <v>-3</v>
       </c>
+      <c r="G277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="54" t="inlineStr">
@@ -39041,11 +39523,12 @@
         <v>2</v>
       </c>
       <c r="E278" s="54" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="F278" s="54" t="n">
-        <v>-0.88</v>
-      </c>
+        <v>-0.84</v>
+      </c>
+      <c r="G278" s="2" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="54" t="inlineStr">
@@ -39067,11 +39550,12 @@
         <v>6</v>
       </c>
       <c r="E279" s="54" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="F279" s="54" t="n">
-        <v>-2.64</v>
-      </c>
+        <v>-2.52</v>
+      </c>
+      <c r="G279" s="2" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="54" t="inlineStr">
@@ -39093,11 +39577,12 @@
         <v>5</v>
       </c>
       <c r="E280" s="54" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="F280" s="54" t="n">
-        <v>-2.2</v>
-      </c>
+        <v>-2.1</v>
+      </c>
+      <c r="G280" s="2" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="54" t="inlineStr">
@@ -39119,11 +39604,12 @@
         <v>20</v>
       </c>
       <c r="E281" s="54" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="F281" s="54" t="n">
-        <v>-44</v>
-      </c>
+        <v>-42</v>
+      </c>
+      <c r="G281" s="2" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="54" t="inlineStr">
@@ -39145,11 +39631,12 @@
         <v>21</v>
       </c>
       <c r="E282" s="54" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="F282" s="54" t="n">
-        <v>-9.24</v>
-      </c>
+        <v>-8.82</v>
+      </c>
+      <c r="G282" s="2" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="53" t="inlineStr">
@@ -39176,6 +39663,7 @@
       <c r="F283" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G283" s="2" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="54" t="inlineStr">
@@ -39202,6 +39690,7 @@
       <c r="F284" s="54" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G284" s="2" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="54" t="inlineStr">
@@ -39223,11 +39712,12 @@
         <v>1</v>
       </c>
       <c r="E285" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F285" s="54" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G285" s="2" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="54" t="inlineStr">
@@ -39249,11 +39739,12 @@
         <v>1</v>
       </c>
       <c r="E286" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F286" s="54" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="54" t="inlineStr">
@@ -39275,11 +39766,12 @@
         <v>4</v>
       </c>
       <c r="E287" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F287" s="54" t="n">
         <v>-2.4</v>
       </c>
+      <c r="G287" s="2" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="53" t="inlineStr">
@@ -39306,6 +39798,7 @@
       <c r="F288" s="53" t="n">
         <v>15</v>
       </c>
+      <c r="G288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="54" t="inlineStr">
@@ -39332,6 +39825,7 @@
       <c r="F289" s="54" t="n">
         <v>-3</v>
       </c>
+      <c r="G289" s="2" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="54" t="inlineStr">
@@ -39353,11 +39847,12 @@
         <v>4</v>
       </c>
       <c r="E290" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3143</v>
       </c>
       <c r="F290" s="54" t="n">
         <v>-1.26</v>
       </c>
+      <c r="G290" s="2" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="54" t="inlineStr">
@@ -39379,11 +39874,12 @@
         <v>8</v>
       </c>
       <c r="E291" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3143</v>
       </c>
       <c r="F291" s="54" t="n">
         <v>-2.51</v>
       </c>
+      <c r="G291" s="2" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="54" t="inlineStr">
@@ -39405,11 +39901,12 @@
         <v>10</v>
       </c>
       <c r="E292" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3143</v>
       </c>
       <c r="F292" s="54" t="n">
         <v>-3.14</v>
       </c>
+      <c r="G292" s="2" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="54" t="inlineStr">
@@ -39431,11 +39928,12 @@
         <v>13</v>
       </c>
       <c r="E293" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3143</v>
       </c>
       <c r="F293" s="54" t="n">
         <v>-4.09</v>
       </c>
+      <c r="G293" s="2" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="54" t="inlineStr">
@@ -39457,11 +39955,12 @@
         <v>8</v>
       </c>
       <c r="E294" s="54" t="n">
-        <v>1.5</v>
+        <v>1.5714</v>
       </c>
       <c r="F294" s="54" t="n">
         <v>-12.57</v>
       </c>
+      <c r="G294" s="2" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="54" t="inlineStr">
@@ -39483,11 +39982,12 @@
         <v>3</v>
       </c>
       <c r="E295" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3143</v>
       </c>
       <c r="F295" s="54" t="n">
         <v>-0.9399999999999999</v>
       </c>
+      <c r="G295" s="2" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="54" t="inlineStr">
@@ -39509,11 +40009,12 @@
         <v>15</v>
       </c>
       <c r="E296" s="54" t="n">
-        <v>1</v>
+        <v>1.0476</v>
       </c>
       <c r="F296" s="54" t="n">
         <v>-15.71</v>
       </c>
+      <c r="G296" s="2" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="54" t="inlineStr">
@@ -39535,11 +40036,12 @@
         <v>1</v>
       </c>
       <c r="E297" s="54" t="n">
-        <v>0.5</v>
+        <v>0.5238</v>
       </c>
       <c r="F297" s="54" t="n">
         <v>-0.52</v>
       </c>
+      <c r="G297" s="2" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="54" t="inlineStr">
@@ -39561,11 +40063,12 @@
         <v>1</v>
       </c>
       <c r="E298" s="54" t="n">
-        <v>0.5</v>
+        <v>0.5238</v>
       </c>
       <c r="F298" s="54" t="n">
         <v>-0.52</v>
       </c>
+      <c r="G298" s="2" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="54" t="inlineStr">
@@ -39587,11 +40090,12 @@
         <v>221</v>
       </c>
       <c r="E299" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3143</v>
       </c>
       <c r="F299" s="54" t="n">
         <v>-69.45999999999999</v>
       </c>
+      <c r="G299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="53" t="inlineStr">
@@ -39618,6 +40122,7 @@
       <c r="F300" s="53" t="n">
         <v>1</v>
       </c>
+      <c r="G300" s="2" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="54" t="inlineStr">
@@ -39644,6 +40149,7 @@
       <c r="F301" s="54" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G301" s="2" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="54" t="inlineStr">
@@ -39665,11 +40171,12 @@
         <v>1</v>
       </c>
       <c r="E302" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F302" s="54" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G302" s="2" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="54" t="inlineStr">
@@ -39691,11 +40198,12 @@
         <v>1</v>
       </c>
       <c r="E303" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F303" s="54" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G303" s="2" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="54" t="inlineStr">
@@ -39717,11 +40225,12 @@
         <v>2</v>
       </c>
       <c r="E304" s="54" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F304" s="54" t="n">
         <v>-6</v>
       </c>
+      <c r="G304" s="2" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="54" t="inlineStr">
@@ -39743,11 +40252,12 @@
         <v>12</v>
       </c>
       <c r="E305" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F305" s="54" t="n">
         <v>-7.2</v>
       </c>
+      <c r="G305" s="2" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="53" t="inlineStr">
@@ -39774,6 +40284,7 @@
       <c r="F306" s="53" t="n">
         <v>13</v>
       </c>
+      <c r="G306" s="2" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="54" t="inlineStr">
@@ -39800,6 +40311,7 @@
       <c r="F307" s="54" t="n">
         <v>-4.5</v>
       </c>
+      <c r="G307" s="2" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="54" t="inlineStr">
@@ -39821,11 +40333,12 @@
         <v>3</v>
       </c>
       <c r="E308" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2864</v>
       </c>
       <c r="F308" s="54" t="n">
-        <v>-0.9</v>
-      </c>
+        <v>-0.86</v>
+      </c>
+      <c r="G308" s="2" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="54" t="inlineStr">
@@ -39847,11 +40360,12 @@
         <v>2</v>
       </c>
       <c r="E309" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2864</v>
       </c>
       <c r="F309" s="54" t="n">
-        <v>-0.6</v>
-      </c>
+        <v>-0.57</v>
+      </c>
+      <c r="G309" s="2" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="54" t="inlineStr">
@@ -39873,11 +40387,12 @@
         <v>4</v>
       </c>
       <c r="E310" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2864</v>
       </c>
       <c r="F310" s="54" t="n">
-        <v>-1.2</v>
-      </c>
+        <v>-1.15</v>
+      </c>
+      <c r="G310" s="2" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="54" t="inlineStr">
@@ -39899,11 +40414,12 @@
         <v>9</v>
       </c>
       <c r="E311" s="54" t="n">
-        <v>1.5</v>
+        <v>1.4318</v>
       </c>
       <c r="F311" s="54" t="n">
-        <v>-13.5</v>
-      </c>
+        <v>-12.89</v>
+      </c>
+      <c r="G311" s="2" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="54" t="inlineStr">
@@ -39925,11 +40441,12 @@
         <v>15</v>
       </c>
       <c r="E312" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2864</v>
       </c>
       <c r="F312" s="54" t="n">
-        <v>-4.5</v>
-      </c>
+        <v>-4.3</v>
+      </c>
+      <c r="G312" s="2" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="53" t="inlineStr">
@@ -39956,6 +40473,7 @@
       <c r="F313" s="53" t="n">
         <v>11</v>
       </c>
+      <c r="G313" s="2" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="54" t="inlineStr">
@@ -39982,6 +40500,7 @@
       <c r="F314" s="54" t="n">
         <v>-1</v>
       </c>
+      <c r="G314" s="2" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="54" t="inlineStr">
@@ -40003,11 +40522,12 @@
         <v>1</v>
       </c>
       <c r="E315" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4846</v>
       </c>
       <c r="F315" s="54" t="n">
-        <v>-0.51</v>
-      </c>
+        <v>-0.48</v>
+      </c>
+      <c r="G315" s="2" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="54" t="inlineStr">
@@ -40029,11 +40549,12 @@
         <v>8</v>
       </c>
       <c r="E316" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4846</v>
       </c>
       <c r="F316" s="54" t="n">
-        <v>-4.06</v>
-      </c>
+        <v>-3.88</v>
+      </c>
+      <c r="G316" s="2" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="54" t="inlineStr">
@@ -40055,11 +40576,12 @@
         <v>10</v>
       </c>
       <c r="E317" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4846</v>
       </c>
       <c r="F317" s="54" t="n">
-        <v>-5.08</v>
-      </c>
+        <v>-4.85</v>
+      </c>
+      <c r="G317" s="2" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="54" t="inlineStr">
@@ -40081,11 +40603,12 @@
         <v>6</v>
       </c>
       <c r="E318" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4846</v>
       </c>
       <c r="F318" s="54" t="n">
-        <v>-3.05</v>
-      </c>
+        <v>-2.91</v>
+      </c>
+      <c r="G318" s="2" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="54" t="inlineStr">
@@ -40107,11 +40630,12 @@
         <v>4</v>
       </c>
       <c r="E319" s="54" t="n">
-        <v>1.5</v>
+        <v>2.4231</v>
       </c>
       <c r="F319" s="54" t="n">
-        <v>-10.15</v>
-      </c>
+        <v>-9.69</v>
+      </c>
+      <c r="G319" s="2" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="54" t="inlineStr">
@@ -40133,11 +40657,12 @@
         <v>1</v>
       </c>
       <c r="E320" s="54" t="n">
-        <v>0.5</v>
+        <v>0.8077</v>
       </c>
       <c r="F320" s="54" t="n">
-        <v>-0.85</v>
-      </c>
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="G320" s="2" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="54" t="inlineStr">
@@ -40159,11 +40684,12 @@
         <v>225</v>
       </c>
       <c r="E321" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4846</v>
       </c>
       <c r="F321" s="54" t="n">
-        <v>-114.23</v>
-      </c>
+        <v>-109.04</v>
+      </c>
+      <c r="G321" s="2" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="53" t="inlineStr">
@@ -40190,6 +40716,7 @@
       <c r="F322" s="53" t="n">
         <v>15</v>
       </c>
+      <c r="G322" s="2" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="54" t="inlineStr">
@@ -40216,6 +40743,7 @@
       <c r="F323" s="54" t="n">
         <v>-3</v>
       </c>
+      <c r="G323" s="2" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="54" t="inlineStr">
@@ -40240,8 +40768,9 @@
         <v>0.3</v>
       </c>
       <c r="F324" s="54" t="n">
-        <v>-0.63</v>
-      </c>
+        <v>-0.6</v>
+      </c>
+      <c r="G324" s="2" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="54" t="inlineStr">
@@ -40266,8 +40795,9 @@
         <v>0.3</v>
       </c>
       <c r="F325" s="54" t="n">
-        <v>-1.26</v>
-      </c>
+        <v>-1.2</v>
+      </c>
+      <c r="G325" s="2" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="54" t="inlineStr">
@@ -40292,8 +40822,9 @@
         <v>0.3</v>
       </c>
       <c r="F326" s="54" t="n">
-        <v>-4.71</v>
-      </c>
+        <v>-4.5</v>
+      </c>
+      <c r="G326" s="2" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="54" t="inlineStr">
@@ -40318,8 +40849,9 @@
         <v>0.3</v>
       </c>
       <c r="F327" s="54" t="n">
-        <v>-1.26</v>
-      </c>
+        <v>-1.2</v>
+      </c>
+      <c r="G327" s="2" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="54" t="inlineStr">
@@ -40344,8 +40876,9 @@
         <v>1.5</v>
       </c>
       <c r="F328" s="54" t="n">
-        <v>-9.43</v>
-      </c>
+        <v>-9</v>
+      </c>
+      <c r="G328" s="2" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="54" t="inlineStr">
@@ -40370,8 +40903,9 @@
         <v>0.5</v>
       </c>
       <c r="F329" s="54" t="n">
-        <v>-1.57</v>
-      </c>
+        <v>-1.5</v>
+      </c>
+      <c r="G329" s="2" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="54" t="inlineStr">
@@ -40396,8 +40930,9 @@
         <v>0.5</v>
       </c>
       <c r="F330" s="54" t="n">
-        <v>-0.52</v>
-      </c>
+        <v>-0.5</v>
+      </c>
+      <c r="G330" s="2" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="54" t="inlineStr">
@@ -40422,8 +40957,9 @@
         <v>0.3</v>
       </c>
       <c r="F331" s="54" t="n">
-        <v>-8.49</v>
-      </c>
+        <v>-8.1</v>
+      </c>
+      <c r="G331" s="2" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="53" t="inlineStr">
@@ -40450,6 +40986,7 @@
       <c r="F332" s="53" t="n">
         <v>13</v>
       </c>
+      <c r="G332" s="2" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="54" t="inlineStr">
@@ -40476,6 +41013,7 @@
       <c r="F333" s="54" t="n">
         <v>-2</v>
       </c>
+      <c r="G333" s="2" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="54" t="inlineStr">
@@ -40497,11 +41035,12 @@
         <v>1</v>
       </c>
       <c r="E334" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4059</v>
       </c>
       <c r="F334" s="54" t="n">
-        <v>-0.39</v>
-      </c>
+        <v>-0.41</v>
+      </c>
+      <c r="G334" s="2" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="54" t="inlineStr">
@@ -40523,11 +41062,12 @@
         <v>2</v>
       </c>
       <c r="E335" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4059</v>
       </c>
       <c r="F335" s="54" t="n">
-        <v>-0.78</v>
-      </c>
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="G335" s="2" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="54" t="inlineStr">
@@ -40549,11 +41089,12 @@
         <v>15</v>
       </c>
       <c r="E336" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4059</v>
       </c>
       <c r="F336" s="54" t="n">
-        <v>-5.82</v>
-      </c>
+        <v>-6.09</v>
+      </c>
+      <c r="G336" s="2" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="54" t="inlineStr">
@@ -40575,11 +41116,12 @@
         <v>10</v>
       </c>
       <c r="E337" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4059</v>
       </c>
       <c r="F337" s="54" t="n">
-        <v>-3.88</v>
-      </c>
+        <v>-4.06</v>
+      </c>
+      <c r="G337" s="2" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="54" t="inlineStr">
@@ -40601,11 +41143,12 @@
         <v>14</v>
       </c>
       <c r="E338" s="54" t="n">
-        <v>1.5</v>
+        <v>2.0294</v>
       </c>
       <c r="F338" s="54" t="n">
-        <v>-27.18</v>
-      </c>
+        <v>-28.41</v>
+      </c>
+      <c r="G338" s="2" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="54" t="inlineStr">
@@ -40627,11 +41170,12 @@
         <v>105</v>
       </c>
       <c r="E339" s="54" t="n">
-        <v>0.3</v>
+        <v>0.4059</v>
       </c>
       <c r="F339" s="54" t="n">
-        <v>-40.76</v>
-      </c>
+        <v>-42.62</v>
+      </c>
+      <c r="G339" s="2" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="53" t="inlineStr">
@@ -40658,6 +41202,7 @@
       <c r="F340" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G340" s="2" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="53" t="inlineStr">
@@ -40684,6 +41229,7 @@
       <c r="F341" s="53" t="n">
         <v>2</v>
       </c>
+      <c r="G341" s="2" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="54" t="inlineStr">
@@ -40710,6 +41256,7 @@
       <c r="F342" s="54" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G342" s="2" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="54" t="inlineStr">
@@ -40731,11 +41278,12 @@
         <v>2</v>
       </c>
       <c r="E343" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F343" s="54" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G343" s="2" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="54" t="inlineStr">
@@ -40757,11 +41305,12 @@
         <v>1</v>
       </c>
       <c r="E344" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F344" s="54" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G344" s="2" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="54" t="inlineStr">
@@ -40783,11 +41332,12 @@
         <v>2</v>
       </c>
       <c r="E345" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F345" s="54" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G345" s="2" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="54" t="inlineStr">
@@ -40809,11 +41359,12 @@
         <v>3</v>
       </c>
       <c r="E346" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F346" s="54" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G346" s="2" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="53" t="inlineStr">
@@ -40840,6 +41391,7 @@
       <c r="F347" s="53" t="n">
         <v>14</v>
       </c>
+      <c r="G347" s="2" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="54" t="inlineStr">
@@ -40866,6 +41418,7 @@
       <c r="F348" s="54" t="n">
         <v>-4</v>
       </c>
+      <c r="G348" s="2" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="54" t="inlineStr">
@@ -40887,11 +41440,12 @@
         <v>1</v>
       </c>
       <c r="E349" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2864</v>
       </c>
       <c r="F349" s="54" t="n">
-        <v>-0.3</v>
-      </c>
+        <v>-0.29</v>
+      </c>
+      <c r="G349" s="2" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="54" t="inlineStr">
@@ -40913,11 +41467,12 @@
         <v>18</v>
       </c>
       <c r="E350" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2864</v>
       </c>
       <c r="F350" s="54" t="n">
-        <v>-5.4</v>
-      </c>
+        <v>-5.15</v>
+      </c>
+      <c r="G350" s="2" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="54" t="inlineStr">
@@ -40939,11 +41494,12 @@
         <v>2</v>
       </c>
       <c r="E351" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2864</v>
       </c>
       <c r="F351" s="54" t="n">
-        <v>-0.6</v>
-      </c>
+        <v>-0.57</v>
+      </c>
+      <c r="G351" s="2" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="54" t="inlineStr">
@@ -40965,11 +41521,12 @@
         <v>7</v>
       </c>
       <c r="E352" s="54" t="n">
-        <v>1.5</v>
+        <v>1.4318</v>
       </c>
       <c r="F352" s="54" t="n">
-        <v>-10.5</v>
-      </c>
+        <v>-10.02</v>
+      </c>
+      <c r="G352" s="2" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="54" t="inlineStr">
@@ -40991,11 +41548,12 @@
         <v>10</v>
       </c>
       <c r="E353" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2864</v>
       </c>
       <c r="F353" s="54" t="n">
-        <v>-3</v>
-      </c>
+        <v>-2.86</v>
+      </c>
+      <c r="G353" s="2" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="53" t="inlineStr">
@@ -41022,6 +41580,7 @@
       <c r="F354" s="53" t="n">
         <v>12</v>
       </c>
+      <c r="G354" s="2" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="54" t="inlineStr">
@@ -41048,6 +41607,7 @@
       <c r="F355" s="54" t="n">
         <v>-3.5</v>
       </c>
+      <c r="G355" s="2" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="54" t="inlineStr">
@@ -41069,11 +41629,12 @@
         <v>7</v>
       </c>
       <c r="E356" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3316</v>
       </c>
       <c r="F356" s="54" t="n">
-        <v>-2.43</v>
-      </c>
+        <v>-2.32</v>
+      </c>
+      <c r="G356" s="2" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="54" t="inlineStr">
@@ -41095,11 +41656,12 @@
         <v>15</v>
       </c>
       <c r="E357" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3316</v>
       </c>
       <c r="F357" s="54" t="n">
-        <v>-5.21</v>
-      </c>
+        <v>-4.97</v>
+      </c>
+      <c r="G357" s="2" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="54" t="inlineStr">
@@ -41121,11 +41683,12 @@
         <v>14</v>
       </c>
       <c r="E358" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3316</v>
       </c>
       <c r="F358" s="54" t="n">
-        <v>-4.86</v>
-      </c>
+        <v>-4.64</v>
+      </c>
+      <c r="G358" s="2" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="54" t="inlineStr">
@@ -41147,11 +41710,12 @@
         <v>4</v>
       </c>
       <c r="E359" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3316</v>
       </c>
       <c r="F359" s="54" t="n">
-        <v>-1.39</v>
-      </c>
+        <v>-1.33</v>
+      </c>
+      <c r="G359" s="2" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="54" t="inlineStr">
@@ -41173,11 +41737,12 @@
         <v>10</v>
       </c>
       <c r="E360" s="54" t="n">
-        <v>1.5</v>
+        <v>1.6579</v>
       </c>
       <c r="F360" s="54" t="n">
-        <v>-17.37</v>
-      </c>
+        <v>-16.58</v>
+      </c>
+      <c r="G360" s="2" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="54" t="inlineStr">
@@ -41199,11 +41764,12 @@
         <v>91</v>
       </c>
       <c r="E361" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3316</v>
       </c>
       <c r="F361" s="54" t="n">
-        <v>-31.61</v>
-      </c>
+        <v>-30.17</v>
+      </c>
+      <c r="G361" s="2" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="53" t="inlineStr">
@@ -41230,6 +41796,7 @@
       <c r="F362" s="53" t="n">
         <v>10</v>
       </c>
+      <c r="G362" s="2" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="54" t="inlineStr">
@@ -41256,6 +41823,7 @@
       <c r="F363" s="54" t="n">
         <v>-5</v>
       </c>
+      <c r="G363" s="2" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="54" t="inlineStr">
@@ -41277,11 +41845,12 @@
         <v>5</v>
       </c>
       <c r="E364" s="54" t="n">
-        <v>0.3</v>
+        <v>0.345</v>
       </c>
       <c r="F364" s="54" t="n">
-        <v>-1.65</v>
-      </c>
+        <v>-1.72</v>
+      </c>
+      <c r="G364" s="2" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="54" t="inlineStr">
@@ -41303,11 +41872,12 @@
         <v>7</v>
       </c>
       <c r="E365" s="54" t="n">
-        <v>0.3</v>
+        <v>0.345</v>
       </c>
       <c r="F365" s="54" t="n">
-        <v>-2.31</v>
-      </c>
+        <v>-2.41</v>
+      </c>
+      <c r="G365" s="2" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="54" t="inlineStr">
@@ -41329,11 +41899,12 @@
         <v>10</v>
       </c>
       <c r="E366" s="54" t="n">
-        <v>0.3</v>
+        <v>0.345</v>
       </c>
       <c r="F366" s="54" t="n">
-        <v>-3.3</v>
-      </c>
+        <v>-3.45</v>
+      </c>
+      <c r="G366" s="2" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="54" t="inlineStr">
@@ -41355,11 +41926,12 @@
         <v>5</v>
       </c>
       <c r="E367" s="54" t="n">
-        <v>0.3</v>
+        <v>0.345</v>
       </c>
       <c r="F367" s="54" t="n">
-        <v>-1.65</v>
-      </c>
+        <v>-1.72</v>
+      </c>
+      <c r="G367" s="2" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="54" t="inlineStr">
@@ -41381,11 +41953,12 @@
         <v>12</v>
       </c>
       <c r="E368" s="54" t="n">
-        <v>1.5</v>
+        <v>1.725</v>
       </c>
       <c r="F368" s="54" t="n">
-        <v>-19.8</v>
-      </c>
+        <v>-20.7</v>
+      </c>
+      <c r="G368" s="2" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="54" t="inlineStr">
@@ -41407,11 +41980,12 @@
         <v>1</v>
       </c>
       <c r="E369" s="54" t="n">
-        <v>0.5</v>
+        <v>0.575</v>
       </c>
       <c r="F369" s="54" t="n">
-        <v>-0.55</v>
-      </c>
+        <v>-0.57</v>
+      </c>
+      <c r="G369" s="2" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="54" t="inlineStr">
@@ -41433,11 +42007,12 @@
         <v>1</v>
       </c>
       <c r="E370" s="54" t="n">
-        <v>0.3</v>
+        <v>0.345</v>
       </c>
       <c r="F370" s="54" t="n">
-        <v>-0.33</v>
-      </c>
+        <v>-0.34</v>
+      </c>
+      <c r="G370" s="2" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="53" t="inlineStr">
@@ -41464,6 +42039,7 @@
       <c r="F371" s="53" t="n">
         <v>13</v>
       </c>
+      <c r="G371" s="2" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="54" t="inlineStr">
@@ -41490,6 +42066,7 @@
       <c r="F372" s="54" t="n">
         <v>-4.5</v>
       </c>
+      <c r="G372" s="2" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="54" t="inlineStr">
@@ -41511,11 +42088,12 @@
         <v>5</v>
       </c>
       <c r="E373" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2864</v>
       </c>
       <c r="F373" s="54" t="n">
-        <v>-1.5</v>
-      </c>
+        <v>-1.43</v>
+      </c>
+      <c r="G373" s="2" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="54" t="inlineStr">
@@ -41537,11 +42115,12 @@
         <v>12</v>
       </c>
       <c r="E374" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2864</v>
       </c>
       <c r="F374" s="54" t="n">
-        <v>-3.6</v>
-      </c>
+        <v>-3.44</v>
+      </c>
+      <c r="G374" s="2" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="54" t="inlineStr">
@@ -41563,11 +42142,12 @@
         <v>9</v>
       </c>
       <c r="E375" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2864</v>
       </c>
       <c r="F375" s="54" t="n">
-        <v>-2.7</v>
-      </c>
+        <v>-2.58</v>
+      </c>
+      <c r="G375" s="2" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="54" t="inlineStr">
@@ -41589,11 +42169,12 @@
         <v>9</v>
       </c>
       <c r="E376" s="54" t="n">
-        <v>1.5</v>
+        <v>1.4318</v>
       </c>
       <c r="F376" s="54" t="n">
-        <v>-13.5</v>
-      </c>
+        <v>-12.89</v>
+      </c>
+      <c r="G376" s="2" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="54" t="inlineStr">
@@ -41615,11 +42196,12 @@
         <v>4</v>
       </c>
       <c r="E377" s="54" t="n">
-        <v>1</v>
+        <v>0.9545</v>
       </c>
       <c r="F377" s="54" t="n">
-        <v>-4</v>
-      </c>
+        <v>-3.82</v>
+      </c>
+      <c r="G377" s="2" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="54" t="inlineStr">
@@ -41641,11 +42223,12 @@
         <v>1</v>
       </c>
       <c r="E378" s="54" t="n">
-        <v>0.5</v>
+        <v>0.4773</v>
       </c>
       <c r="F378" s="54" t="n">
-        <v>-0.5</v>
-      </c>
+        <v>-0.48</v>
+      </c>
+      <c r="G378" s="2" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="54" t="inlineStr">
@@ -41667,11 +42250,12 @@
         <v>40</v>
       </c>
       <c r="E379" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2864</v>
       </c>
       <c r="F379" s="54" t="n">
-        <v>-12</v>
-      </c>
+        <v>-11.45</v>
+      </c>
+      <c r="G379" s="2" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="53" t="inlineStr">
@@ -41698,6 +42282,7 @@
       <c r="F380" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G380" s="2" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="53" t="inlineStr">
@@ -41724,6 +42309,7 @@
       <c r="F381" s="53" t="n">
         <v>10</v>
       </c>
+      <c r="G381" s="2" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="54" t="inlineStr">
@@ -41750,6 +42336,7 @@
       <c r="F382" s="54" t="n">
         <v>-1</v>
       </c>
+      <c r="G382" s="2" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="54" t="inlineStr">
@@ -41771,11 +42358,12 @@
         <v>1</v>
       </c>
       <c r="E383" s="54" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="F383" s="54" t="n">
         <v>-0.55</v>
       </c>
+      <c r="G383" s="2" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="54" t="inlineStr">
@@ -41797,11 +42385,12 @@
         <v>7</v>
       </c>
       <c r="E384" s="54" t="n">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="F384" s="54" t="n">
         <v>-19.25</v>
       </c>
+      <c r="G384" s="2" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="54" t="inlineStr">
@@ -41823,11 +42412,12 @@
         <v>4</v>
       </c>
       <c r="E385" s="54" t="n">
-        <v>0.5</v>
+        <v>0.9167</v>
       </c>
       <c r="F385" s="54" t="n">
         <v>-3.67</v>
       </c>
+      <c r="G385" s="2" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="54" t="inlineStr">
@@ -41849,11 +42439,12 @@
         <v>3</v>
       </c>
       <c r="E386" s="54" t="n">
-        <v>0.5</v>
+        <v>0.9167</v>
       </c>
       <c r="F386" s="54" t="n">
         <v>-2.75</v>
       </c>
+      <c r="G386" s="2" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="53" t="inlineStr">
@@ -41880,6 +42471,7 @@
       <c r="F387" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G387" s="2" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="53" t="inlineStr">
@@ -41906,6 +42498,7 @@
       <c r="F388" s="53" t="n">
         <v>2</v>
       </c>
+      <c r="G388" s="2" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="54" t="inlineStr">
@@ -41932,6 +42525,7 @@
       <c r="F389" s="54" t="n">
         <v>-1</v>
       </c>
+      <c r="G389" s="2" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="54" t="inlineStr">
@@ -41953,11 +42547,12 @@
         <v>1</v>
       </c>
       <c r="E390" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F390" s="54" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G390" s="2" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="54" t="inlineStr">
@@ -41979,11 +42574,12 @@
         <v>2</v>
       </c>
       <c r="E391" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F391" s="54" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G391" s="2" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="54" t="inlineStr">
@@ -42005,11 +42601,12 @@
         <v>3</v>
       </c>
       <c r="E392" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F392" s="54" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G392" s="2" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="54" t="inlineStr">
@@ -42031,11 +42628,12 @@
         <v>3</v>
       </c>
       <c r="E393" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F393" s="54" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G393" s="2" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="53" t="inlineStr">
@@ -42062,6 +42660,7 @@
       <c r="F394" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G394" s="2" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="53" t="inlineStr">
@@ -42088,6 +42687,7 @@
       <c r="F395" s="53" t="n">
         <v>14</v>
       </c>
+      <c r="G395" s="2" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="54" t="inlineStr">
@@ -42114,6 +42714,7 @@
       <c r="F396" s="54" t="n">
         <v>-4</v>
       </c>
+      <c r="G396" s="2" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="54" t="inlineStr">
@@ -42140,6 +42741,7 @@
       <c r="F397" s="54" t="n">
         <v>-0.9</v>
       </c>
+      <c r="G397" s="2" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="54" t="inlineStr">
@@ -42166,6 +42768,7 @@
       <c r="F398" s="54" t="n">
         <v>-2.4</v>
       </c>
+      <c r="G398" s="2" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="54" t="inlineStr">
@@ -42192,6 +42795,7 @@
       <c r="F399" s="54" t="n">
         <v>-0.9</v>
       </c>
+      <c r="G399" s="2" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="54" t="inlineStr">
@@ -42218,6 +42822,7 @@
       <c r="F400" s="54" t="n">
         <v>-4.5</v>
       </c>
+      <c r="G400" s="2" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="53" t="inlineStr">
@@ -42244,6 +42849,7 @@
       <c r="F401" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G401" s="2" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="53" t="inlineStr">
@@ -42270,6 +42876,7 @@
       <c r="F402" s="53" t="n">
         <v>15</v>
       </c>
+      <c r="G402" s="2" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="54" t="inlineStr">
@@ -42296,6 +42903,7 @@
       <c r="F403" s="54" t="n">
         <v>-1</v>
       </c>
+      <c r="G403" s="2" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="54" t="inlineStr">
@@ -42317,11 +42925,12 @@
         <v>4</v>
       </c>
       <c r="E404" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3882</v>
       </c>
       <c r="F404" s="54" t="n">
         <v>-1.55</v>
       </c>
+      <c r="G404" s="2" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="54" t="inlineStr">
@@ -42343,11 +42952,12 @@
         <v>15</v>
       </c>
       <c r="E405" s="54" t="n">
-        <v>1.5</v>
+        <v>1.9412</v>
       </c>
       <c r="F405" s="54" t="n">
         <v>-29.12</v>
       </c>
+      <c r="G405" s="2" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="54" t="inlineStr">
@@ -42369,11 +42979,12 @@
         <v>14</v>
       </c>
       <c r="E406" s="54" t="n">
-        <v>1</v>
+        <v>1.2941</v>
       </c>
       <c r="F406" s="54" t="n">
         <v>-18.12</v>
       </c>
+      <c r="G406" s="2" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="53" t="inlineStr">
@@ -42400,6 +43011,7 @@
       <c r="F407" s="53" t="n">
         <v>7</v>
       </c>
+      <c r="G407" s="2" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="54" t="inlineStr">
@@ -42426,6 +43038,7 @@
       <c r="F408" s="54" t="n">
         <v>-2</v>
       </c>
+      <c r="G408" s="2" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="54" t="inlineStr">
@@ -42447,11 +43060,12 @@
         <v>3</v>
       </c>
       <c r="E409" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F409" s="54" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G409" s="2" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="54" t="inlineStr">
@@ -42473,11 +43087,12 @@
         <v>7</v>
       </c>
       <c r="E410" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F410" s="54" t="n">
         <v>-4.2</v>
       </c>
+      <c r="G410" s="2" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="54" t="inlineStr">
@@ -42499,11 +43114,12 @@
         <v>5</v>
       </c>
       <c r="E411" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F411" s="54" t="n">
         <v>-3</v>
       </c>
+      <c r="G411" s="2" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="54" t="inlineStr">
@@ -42525,11 +43141,12 @@
         <v>12</v>
       </c>
       <c r="E412" s="54" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F412" s="54" t="n">
         <v>-36</v>
       </c>
+      <c r="G412" s="2" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="54" t="inlineStr">
@@ -42551,11 +43168,12 @@
         <v>18</v>
       </c>
       <c r="E413" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F413" s="54" t="n">
         <v>-10.8</v>
       </c>
+      <c r="G413" s="2" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="53" t="inlineStr">
@@ -42582,6 +43200,7 @@
       <c r="F414" s="53" t="n">
         <v>9</v>
       </c>
+      <c r="G414" s="2" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="54" t="inlineStr">
@@ -42608,6 +43227,7 @@
       <c r="F415" s="54" t="n">
         <v>-1</v>
       </c>
+      <c r="G415" s="2" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="54" t="inlineStr">
@@ -42629,11 +43249,12 @@
         <v>4</v>
       </c>
       <c r="E416" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F416" s="54" t="n">
         <v>-2.4</v>
       </c>
+      <c r="G416" s="2" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="54" t="inlineStr">
@@ -42655,11 +43276,12 @@
         <v>7</v>
       </c>
       <c r="E417" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F417" s="54" t="n">
         <v>-4.2</v>
       </c>
+      <c r="G417" s="2" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="54" t="inlineStr">
@@ -42681,11 +43303,12 @@
         <v>3</v>
       </c>
       <c r="E418" s="54" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F418" s="54" t="n">
         <v>-9</v>
       </c>
+      <c r="G418" s="2" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="54" t="inlineStr">
@@ -42707,11 +43330,12 @@
         <v>77</v>
       </c>
       <c r="E419" s="54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F419" s="54" t="n">
         <v>-46.2</v>
       </c>
+      <c r="G419" s="2" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="53" t="inlineStr">
@@ -42738,6 +43362,7 @@
       <c r="F420" s="53" t="n">
         <v>11</v>
       </c>
+      <c r="G420" s="2" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="54" t="inlineStr">
@@ -42764,6 +43389,7 @@
       <c r="F421" s="54" t="n">
         <v>-5</v>
       </c>
+      <c r="G421" s="2" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="54" t="inlineStr">
@@ -42788,8 +43414,9 @@
         <v>0.3</v>
       </c>
       <c r="F422" s="54" t="n">
-        <v>-1.89</v>
-      </c>
+        <v>-1.8</v>
+      </c>
+      <c r="G422" s="2" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="54" t="inlineStr">
@@ -42814,8 +43441,9 @@
         <v>0.3</v>
       </c>
       <c r="F423" s="54" t="n">
-        <v>-4.09</v>
-      </c>
+        <v>-3.9</v>
+      </c>
+      <c r="G423" s="2" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="54" t="inlineStr">
@@ -42840,8 +43468,9 @@
         <v>0.3</v>
       </c>
       <c r="F424" s="54" t="n">
-        <v>-4.71</v>
-      </c>
+        <v>-4.5</v>
+      </c>
+      <c r="G424" s="2" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="54" t="inlineStr">
@@ -42866,8 +43495,9 @@
         <v>0.3</v>
       </c>
       <c r="F425" s="54" t="n">
-        <v>-0.63</v>
-      </c>
+        <v>-0.6</v>
+      </c>
+      <c r="G425" s="2" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="54" t="inlineStr">
@@ -42892,8 +43522,9 @@
         <v>1.5</v>
       </c>
       <c r="F426" s="54" t="n">
-        <v>-17.29</v>
-      </c>
+        <v>-16.5</v>
+      </c>
+      <c r="G426" s="2" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="54" t="inlineStr">
@@ -42918,8 +43549,9 @@
         <v>0.3</v>
       </c>
       <c r="F427" s="54" t="n">
-        <v>-33.63</v>
-      </c>
+        <v>-32.1</v>
+      </c>
+      <c r="G427" s="2" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="53" t="inlineStr">
@@ -42946,6 +43578,7 @@
       <c r="F428" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G428" s="2" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="53" t="inlineStr">
@@ -42972,6 +43605,7 @@
       <c r="F429" s="53" t="n">
         <v>14</v>
       </c>
+      <c r="G429" s="2" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="54" t="inlineStr">
@@ -42998,6 +43632,7 @@
       <c r="F430" s="54" t="n">
         <v>-3.5</v>
       </c>
+      <c r="G430" s="2" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="54" t="inlineStr">
@@ -43019,11 +43654,12 @@
         <v>4</v>
       </c>
       <c r="E431" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3143</v>
       </c>
       <c r="F431" s="54" t="n">
         <v>-1.26</v>
       </c>
+      <c r="G431" s="2" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="54" t="inlineStr">
@@ -43045,11 +43681,12 @@
         <v>16</v>
       </c>
       <c r="E432" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3143</v>
       </c>
       <c r="F432" s="54" t="n">
         <v>-5.03</v>
       </c>
+      <c r="G432" s="2" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="54" t="inlineStr">
@@ -43071,11 +43708,12 @@
         <v>5</v>
       </c>
       <c r="E433" s="54" t="n">
-        <v>0.3</v>
+        <v>0.3143</v>
       </c>
       <c r="F433" s="54" t="n">
         <v>-1.57</v>
       </c>
+      <c r="G433" s="2" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="54" t="inlineStr">
@@ -43097,11 +43735,12 @@
         <v>8</v>
       </c>
       <c r="E434" s="54" t="n">
-        <v>1.5</v>
+        <v>1.5714</v>
       </c>
       <c r="F434" s="54" t="n">
         <v>-12.57</v>
       </c>
+      <c r="G434" s="2" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="53" t="inlineStr">
@@ -43128,6 +43767,7 @@
       <c r="F435" s="53" t="n">
         <v>5</v>
       </c>
+      <c r="G435" s="2" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="53" t="inlineStr">
@@ -43154,6 +43794,7 @@
       <c r="F436" s="53" t="n">
         <v>15</v>
       </c>
+      <c r="G436" s="2" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="54" t="inlineStr">
@@ -43180,6 +43821,7 @@
       <c r="F437" s="54" t="n">
         <v>-2.5</v>
       </c>
+      <c r="G437" s="2" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="54" t="inlineStr">
@@ -43201,11 +43843,12 @@
         <v>1</v>
       </c>
       <c r="E438" s="54" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="F438" s="54" t="n">
         <v>-0.33</v>
       </c>
+      <c r="G438" s="2" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="54" t="inlineStr">
@@ -43227,11 +43870,12 @@
         <v>7</v>
       </c>
       <c r="E439" s="54" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="F439" s="54" t="n">
         <v>-2.31</v>
       </c>
+      <c r="G439" s="2" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="54" t="inlineStr">
@@ -43253,11 +43897,12 @@
         <v>16</v>
       </c>
       <c r="E440" s="54" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="F440" s="54" t="n">
         <v>-5.28</v>
       </c>
+      <c r="G440" s="2" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="54" t="inlineStr">
@@ -43279,11 +43924,12 @@
         <v>1</v>
       </c>
       <c r="E441" s="54" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="F441" s="54" t="n">
         <v>-0.33</v>
       </c>
+      <c r="G441" s="2" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="54" t="inlineStr">
@@ -43305,17 +43951,18 @@
         <v>11</v>
       </c>
       <c r="E442" s="54" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="F442" s="54" t="n">
         <v>-18.15</v>
       </c>
+      <c r="G442" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E51"/>
+  <autoFilter ref="A2:G51"/>
   <mergeCells count="2">
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/historico/semanas_313-317.xlsx
+++ b/data/historico/semanas_313-317.xlsx
@@ -35,7 +35,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Resumo Semanal'!$A$2:$AE$195</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Ranking'!$A$2:$G$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Ranking'!$A$2:$H$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31962,16 +31962,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G442"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -31986,6 +31987,7 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -32015,10 +32017,15 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>Turnos Sem Trabalhar</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Pontuação Final</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
@@ -32045,9 +32052,12 @@
         <v>22</v>
       </c>
       <c r="F3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32059,7 +32069,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Emerson de Carvalho Miranda</t>
+          <t>Alvaro Delgado Brandao</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -32074,9 +32084,12 @@
         <v>23</v>
       </c>
       <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32088,7 +32101,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Josoé de Oliveira</t>
+          <t>Emerson de Carvalho Miranda</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -32103,9 +32116,12 @@
         <v>23</v>
       </c>
       <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32117,7 +32133,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Marcos Alcindo Insalbralde</t>
+          <t>Josoé de Oliveira</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -32126,15 +32142,18 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>23</v>
       </c>
       <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32146,7 +32165,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Robson Pavão Montania</t>
+          <t>Marcos Alcindo Insalbralde</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -32155,15 +32174,18 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>23</v>
       </c>
       <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32175,7 +32197,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Silvio de Aquino</t>
+          <t>Robson Pavão Montania</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -32184,15 +32206,18 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>23</v>
       </c>
       <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32204,7 +32229,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Alvaro Delgado Brandao</t>
+          <t>Silvio de Aquino</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -32213,15 +32238,18 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>23</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32233,24 +32261,27 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Fabio Teodoro Alves Alexo</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe Bloqueio</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>23</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32262,24 +32293,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>95.52</v>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32291,7 +32325,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -32306,9 +32340,12 @@
         <v>22</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>95.06999999999999</v>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32320,24 +32357,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Anderson Salabarrieto</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe Bloqueio</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>94.62</v>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32349,24 +32389,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Fabio Teodoro Alves Alexo</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Equipe Bloqueio</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32378,7 +32421,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -32393,9 +32436,12 @@
         <v>22</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>93.39</v>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>94.62</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32407,24 +32453,27 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Anderson Salabarrieto</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Equipe Bloqueio</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32436,24 +32485,27 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -32465,55 +32517,61 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Naime Cristina Freitas</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D19" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E19" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="F18" s="4" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>90.17</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
         </is>
       </c>
     </row>
@@ -32523,24 +32581,27 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>89.84</v>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -32552,24 +32613,27 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>22</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>88.73999999999999</v>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>89.84</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -32581,7 +32645,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -32590,15 +32654,18 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>87.78</v>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -32610,7 +32677,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -32619,15 +32686,18 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>21</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>87.25</v>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -32639,24 +32709,27 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>87.78</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -32668,12 +32741,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -32683,9 +32756,12 @@
         <v>23</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -32697,7 +32773,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Ramona dos Santos Oliveira</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -32706,15 +32782,18 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>21</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>87.61</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -32741,9 +32820,12 @@
         <v>22</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -32770,9 +32852,12 @@
         <v>23</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>78.91</v>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -32799,69 +32884,78 @@
         <v>23</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>75.67</v>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>76.52</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="41" t="n">
+      <c r="A30" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="41" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>76.23999999999999</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
-      <c r="C30" s="41" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D30" s="41" t="n">
+      <c r="D31" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="E30" s="41" t="n">
+      <c r="E31" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="F30" s="41" t="n">
-        <v>74.83</v>
-      </c>
-      <c r="G30" s="41" t="inlineStr">
-        <is>
-          <t>🟠 ATENÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="41" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="41" t="inlineStr">
-        <is>
-          <t>Rozentina Matos de Oliveira</t>
-        </is>
-      </c>
-      <c r="C31" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="D31" s="41" t="n">
-        <v>20</v>
-      </c>
-      <c r="E31" s="41" t="n">
-        <v>23</v>
-      </c>
-      <c r="F31" s="41" t="n">
-        <v>74.06</v>
-      </c>
-      <c r="G31" s="41" t="inlineStr">
-        <is>
-          <t>🟠 ATENÇÃO</t>
+      <c r="F31" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
     </row>
@@ -32871,24 +32965,27 @@
       </c>
       <c r="B32" s="41" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="C32" s="41" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D32" s="41" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E32" s="41" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F32" s="41" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="G32" s="41" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="G32" s="41" t="n">
+        <v>74.18000000000001</v>
+      </c>
+      <c r="H32" s="41" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
         </is>
@@ -32915,9 +33012,12 @@
         <v>22</v>
       </c>
       <c r="F33" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="G33" s="41" t="n">
         <v>70.20999999999999</v>
       </c>
-      <c r="G33" s="41" t="inlineStr">
+      <c r="H33" s="41" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
         </is>
@@ -32929,24 +33029,27 @@
       </c>
       <c r="B34" s="41" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C34" s="41" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D34" s="41" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E34" s="41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F34" s="41" t="n">
-        <v>63.57</v>
-      </c>
-      <c r="G34" s="41" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="G34" s="41" t="n">
+        <v>68.83</v>
+      </c>
+      <c r="H34" s="41" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
         </is>
@@ -32958,24 +33061,27 @@
       </c>
       <c r="B35" s="41" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C35" s="41" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D35" s="41" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E35" s="41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F35" s="41" t="n">
-        <v>62.63</v>
-      </c>
-      <c r="G35" s="41" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="G35" s="41" t="n">
+        <v>68.45999999999999</v>
+      </c>
+      <c r="H35" s="41" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
         </is>
@@ -32987,55 +33093,61 @@
       </c>
       <c r="B36" s="41" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="C36" s="41" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D36" s="41" t="n">
+        <v>21</v>
+      </c>
+      <c r="E36" s="41" t="n">
         <v>23</v>
       </c>
-      <c r="E36" s="41" t="n">
-        <v>21</v>
-      </c>
       <c r="F36" s="41" t="n">
-        <v>60.25</v>
-      </c>
-      <c r="G36" s="41" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="G36" s="41" t="n">
+        <v>67.34</v>
+      </c>
+      <c r="H36" s="41" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="41" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="E37" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>49.72</v>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="C37" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D37" s="41" t="n">
+        <v>11</v>
+      </c>
+      <c r="E37" s="41" t="n">
+        <v>23</v>
+      </c>
+      <c r="F37" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" s="41" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="H37" s="41" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
         </is>
       </c>
     </row>
@@ -33045,24 +33157,27 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>49.58</v>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -33074,24 +33189,27 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F39" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="E39" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G39" s="6" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -33103,24 +33221,27 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>48.48</v>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -33132,24 +33253,27 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -33161,24 +33285,27 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>52.66</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -33205,9 +33332,12 @@
         <v>23</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>28.61</v>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
+        <v>14</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>42.81</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -33219,24 +33349,27 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Carlos Alberto Albiero</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -33248,24 +33381,27 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Carlos Alberto Albiero</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>20.33</v>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>38.47</v>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -33277,7 +33413,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -33286,15 +33422,18 @@
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>21</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>16.42</v>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -33306,24 +33445,27 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>13.78</v>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -33335,7 +33477,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -33344,15 +33486,18 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>22</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -33364,24 +33509,27 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="E49" s="6" t="n">
-        <v>22</v>
-      </c>
       <c r="F49" s="6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -33408,9 +33556,12 @@
         <v>21</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -33437,9 +33588,12 @@
         <v>21</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -33453,6 +33607,7 @@
       <c r="E52" s="2" t="n"/>
       <c r="F52" s="2" t="n"/>
       <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -33462,6 +33617,7 @@
       <c r="E53" s="2" t="n"/>
       <c r="F53" s="2" t="n"/>
       <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="52" t="inlineStr">
@@ -33475,6 +33631,7 @@
       <c r="E54" s="2" t="n"/>
       <c r="F54" s="2" t="n"/>
       <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -33499,15 +33656,24 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Peso (pontos/ocorrência)</t>
+          <t>Peso Nominal (tabela de critérios)</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
+          <t>Fator de Normalização</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Peso Efetivo (nominal × fator)</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
           <t>Pontos Aplicados</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="53" t="inlineStr">
@@ -33532,9 +33698,14 @@
         <v>1</v>
       </c>
       <c r="F56" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="53" t="n">
         <v>14</v>
       </c>
-      <c r="G56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="54" t="inlineStr">
@@ -33559,9 +33730,14 @@
         <v>0.5</v>
       </c>
       <c r="F57" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H57" s="54" t="n">
         <v>-2.5</v>
       </c>
-      <c r="G57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="54" t="inlineStr">
@@ -33583,12 +33759,17 @@
         <v>3</v>
       </c>
       <c r="E58" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F58" s="54" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="G58" s="54" t="n">
         <v>0.3632</v>
       </c>
-      <c r="F58" s="54" t="n">
+      <c r="H58" s="54" t="n">
         <v>-1.09</v>
       </c>
-      <c r="G58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="54" t="inlineStr">
@@ -33610,12 +33791,17 @@
         <v>9</v>
       </c>
       <c r="E59" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F59" s="54" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="G59" s="54" t="n">
         <v>0.3632</v>
       </c>
-      <c r="F59" s="54" t="n">
+      <c r="H59" s="54" t="n">
         <v>-3.27</v>
       </c>
-      <c r="G59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="54" t="inlineStr">
@@ -33637,12 +33823,17 @@
         <v>15</v>
       </c>
       <c r="E60" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F60" s="54" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="G60" s="54" t="n">
         <v>0.3632</v>
       </c>
-      <c r="F60" s="54" t="n">
+      <c r="H60" s="54" t="n">
         <v>-5.45</v>
       </c>
-      <c r="G60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="54" t="inlineStr">
@@ -33664,12 +33855,17 @@
         <v>8</v>
       </c>
       <c r="E61" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F61" s="54" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="G61" s="54" t="n">
         <v>0.3632</v>
       </c>
-      <c r="F61" s="54" t="n">
+      <c r="H61" s="54" t="n">
         <v>-2.91</v>
       </c>
-      <c r="G61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="54" t="inlineStr">
@@ -33691,12 +33887,17 @@
         <v>11</v>
       </c>
       <c r="E62" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F62" s="54" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="G62" s="54" t="n">
         <v>1.8158</v>
       </c>
-      <c r="F62" s="54" t="n">
+      <c r="H62" s="54" t="n">
         <v>-19.97</v>
       </c>
-      <c r="G62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="54" t="inlineStr">
@@ -33718,12 +33919,17 @@
         <v>1</v>
       </c>
       <c r="E63" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F63" s="54" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="G63" s="54" t="n">
         <v>0.6052999999999999</v>
       </c>
-      <c r="F63" s="54" t="n">
+      <c r="H63" s="54" t="n">
         <v>-0.61</v>
       </c>
-      <c r="G63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="54" t="inlineStr">
@@ -33745,12 +33951,17 @@
         <v>7</v>
       </c>
       <c r="E64" s="54" t="n">
-        <v>0.3632</v>
+        <v>0.2</v>
       </c>
       <c r="F64" s="54" t="n">
-        <v>-2.54</v>
-      </c>
-      <c r="G64" s="2" t="n"/>
+        <v>1.211</v>
+      </c>
+      <c r="G64" s="54" t="n">
+        <v>0.2421</v>
+      </c>
+      <c r="H64" s="54" t="n">
+        <v>-1.69</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="53" t="inlineStr">
@@ -33775,9 +33986,14 @@
         <v>1</v>
       </c>
       <c r="F65" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="53" t="n">
         <v>13</v>
       </c>
-      <c r="G65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="54" t="inlineStr">
@@ -33802,9 +34018,14 @@
         <v>0.5</v>
       </c>
       <c r="F66" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H66" s="54" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="54" t="inlineStr">
@@ -33826,12 +34047,17 @@
         <v>4</v>
       </c>
       <c r="E67" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F67" s="54" t="n">
+        <v>1.643</v>
+      </c>
+      <c r="G67" s="54" t="n">
         <v>0.4929</v>
       </c>
-      <c r="F67" s="54" t="n">
+      <c r="H67" s="54" t="n">
         <v>-1.97</v>
       </c>
-      <c r="G67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="54" t="inlineStr">
@@ -33853,12 +34079,17 @@
         <v>6</v>
       </c>
       <c r="E68" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F68" s="54" t="n">
+        <v>1.643</v>
+      </c>
+      <c r="G68" s="54" t="n">
         <v>0.4929</v>
       </c>
-      <c r="F68" s="54" t="n">
+      <c r="H68" s="54" t="n">
         <v>-2.96</v>
       </c>
-      <c r="G68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="54" t="inlineStr">
@@ -33880,12 +34111,17 @@
         <v>13</v>
       </c>
       <c r="E69" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F69" s="54" t="n">
+        <v>1.643</v>
+      </c>
+      <c r="G69" s="54" t="n">
         <v>0.4929</v>
       </c>
-      <c r="F69" s="54" t="n">
+      <c r="H69" s="54" t="n">
         <v>-6.41</v>
       </c>
-      <c r="G69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="54" t="inlineStr">
@@ -33907,12 +34143,17 @@
         <v>7</v>
       </c>
       <c r="E70" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F70" s="54" t="n">
+        <v>1.643</v>
+      </c>
+      <c r="G70" s="54" t="n">
         <v>0.4929</v>
       </c>
-      <c r="F70" s="54" t="n">
+      <c r="H70" s="54" t="n">
         <v>-3.45</v>
       </c>
-      <c r="G70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="54" t="inlineStr">
@@ -33934,12 +34175,17 @@
         <v>10</v>
       </c>
       <c r="E71" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F71" s="54" t="n">
+        <v>1.643</v>
+      </c>
+      <c r="G71" s="54" t="n">
         <v>2.4643</v>
       </c>
-      <c r="F71" s="54" t="n">
+      <c r="H71" s="54" t="n">
         <v>-24.64</v>
       </c>
-      <c r="G71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="54" t="inlineStr">
@@ -33961,12 +34207,17 @@
         <v>1</v>
       </c>
       <c r="E72" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F72" s="54" t="n">
+        <v>1.643</v>
+      </c>
+      <c r="G72" s="54" t="n">
         <v>0.8214</v>
       </c>
-      <c r="F72" s="54" t="n">
+      <c r="H72" s="54" t="n">
         <v>-0.82</v>
       </c>
-      <c r="G72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="54" t="inlineStr">
@@ -33988,12 +34239,17 @@
         <v>46</v>
       </c>
       <c r="E73" s="54" t="n">
-        <v>0.4929</v>
+        <v>0.2</v>
       </c>
       <c r="F73" s="54" t="n">
-        <v>-22.67</v>
-      </c>
-      <c r="G73" s="2" t="n"/>
+        <v>1.643</v>
+      </c>
+      <c r="G73" s="54" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="H73" s="54" t="n">
+        <v>-15.11</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="53" t="inlineStr">
@@ -34018,9 +34274,14 @@
         <v>1</v>
       </c>
       <c r="F74" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="53" t="n">
         <v>9</v>
       </c>
-      <c r="G74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="54" t="inlineStr">
@@ -34045,9 +34306,14 @@
         <v>0.5</v>
       </c>
       <c r="F75" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H75" s="54" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="54" t="inlineStr">
@@ -34069,12 +34335,17 @@
         <v>1</v>
       </c>
       <c r="E76" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F76" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F76" s="54" t="n">
+      <c r="H76" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="54" t="inlineStr">
@@ -34096,12 +34367,17 @@
         <v>2</v>
       </c>
       <c r="E77" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F77" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F77" s="54" t="n">
+      <c r="H77" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="54" t="inlineStr">
@@ -34123,12 +34399,17 @@
         <v>1</v>
       </c>
       <c r="E78" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F78" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F78" s="54" t="n">
+      <c r="H78" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="54" t="inlineStr">
@@ -34150,12 +34431,17 @@
         <v>26</v>
       </c>
       <c r="E79" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F79" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="F79" s="54" t="n">
+      <c r="H79" s="54" t="n">
         <v>-78</v>
       </c>
-      <c r="G79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="54" t="inlineStr">
@@ -34177,12 +34463,17 @@
         <v>5</v>
       </c>
       <c r="E80" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F80" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="F80" s="54" t="n">
+      <c r="H80" s="54" t="n">
         <v>-5</v>
       </c>
-      <c r="G80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="54" t="inlineStr">
@@ -34204,12 +34495,17 @@
         <v>2</v>
       </c>
       <c r="E81" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F81" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="F81" s="54" t="n">
+      <c r="H81" s="54" t="n">
         <v>-2</v>
       </c>
-      <c r="G81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="54" t="inlineStr">
@@ -34231,12 +34527,17 @@
         <v>1</v>
       </c>
       <c r="E82" s="54" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F82" s="54" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G82" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G82" s="54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H82" s="54" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="53" t="inlineStr">
@@ -34261,9 +34562,14 @@
         <v>5</v>
       </c>
       <c r="F83" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G83" s="2" t="n"/>
+      <c r="H83" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="53" t="inlineStr">
@@ -34290,7 +34596,12 @@
       <c r="F84" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="G84" s="2" t="n"/>
+      <c r="G84" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="54" t="inlineStr">
@@ -34315,9 +34626,14 @@
         <v>0.5</v>
       </c>
       <c r="F85" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H85" s="54" t="n">
         <v>-1</v>
       </c>
-      <c r="G85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="54" t="inlineStr">
@@ -34339,12 +34655,17 @@
         <v>3</v>
       </c>
       <c r="E86" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F86" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F86" s="54" t="n">
+      <c r="H86" s="54" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="54" t="inlineStr">
@@ -34366,12 +34687,17 @@
         <v>6</v>
       </c>
       <c r="E87" s="54" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F87" s="54" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="G87" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G87" s="54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H87" s="54" t="n">
+        <v>-2.4</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="53" t="inlineStr">
@@ -34396,9 +34722,14 @@
         <v>1</v>
       </c>
       <c r="F88" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="53" t="n">
         <v>11</v>
       </c>
-      <c r="G88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="54" t="inlineStr">
@@ -34423,9 +34754,14 @@
         <v>0.5</v>
       </c>
       <c r="F89" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H89" s="54" t="n">
         <v>-5</v>
       </c>
-      <c r="G89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="54" t="inlineStr">
@@ -34447,12 +34783,17 @@
         <v>4</v>
       </c>
       <c r="E90" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F90" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G90" s="54" t="n">
         <v>0.3286</v>
       </c>
-      <c r="F90" s="54" t="n">
+      <c r="H90" s="54" t="n">
         <v>-1.31</v>
       </c>
-      <c r="G90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="54" t="inlineStr">
@@ -34474,12 +34815,17 @@
         <v>10</v>
       </c>
       <c r="E91" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F91" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G91" s="54" t="n">
         <v>0.3286</v>
       </c>
-      <c r="F91" s="54" t="n">
+      <c r="H91" s="54" t="n">
         <v>-3.29</v>
       </c>
-      <c r="G91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="54" t="inlineStr">
@@ -34501,12 +34847,17 @@
         <v>17</v>
       </c>
       <c r="E92" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F92" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G92" s="54" t="n">
         <v>0.3286</v>
       </c>
-      <c r="F92" s="54" t="n">
+      <c r="H92" s="54" t="n">
         <v>-5.59</v>
       </c>
-      <c r="G92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="54" t="inlineStr">
@@ -34528,12 +34879,17 @@
         <v>8</v>
       </c>
       <c r="E93" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F93" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G93" s="54" t="n">
         <v>0.3286</v>
       </c>
-      <c r="F93" s="54" t="n">
+      <c r="H93" s="54" t="n">
         <v>-2.63</v>
       </c>
-      <c r="G93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="54" t="inlineStr">
@@ -34555,12 +34911,17 @@
         <v>10</v>
       </c>
       <c r="E94" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F94" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G94" s="54" t="n">
         <v>1.6429</v>
       </c>
-      <c r="F94" s="54" t="n">
+      <c r="H94" s="54" t="n">
         <v>-16.43</v>
       </c>
-      <c r="G94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="54" t="inlineStr">
@@ -34582,12 +34943,17 @@
         <v>43</v>
       </c>
       <c r="E95" s="54" t="n">
-        <v>0.3286</v>
+        <v>0.2</v>
       </c>
       <c r="F95" s="54" t="n">
-        <v>-14.13</v>
-      </c>
-      <c r="G95" s="2" t="n"/>
+        <v>1.095</v>
+      </c>
+      <c r="G95" s="54" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="H95" s="54" t="n">
+        <v>-9.42</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="53" t="inlineStr">
@@ -34612,9 +34978,14 @@
         <v>1</v>
       </c>
       <c r="F96" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="G96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="54" t="inlineStr">
@@ -34639,9 +35010,14 @@
         <v>0.5</v>
       </c>
       <c r="F97" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H97" s="54" t="n">
         <v>-3.5</v>
       </c>
-      <c r="G97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="54" t="inlineStr">
@@ -34663,12 +35039,17 @@
         <v>13</v>
       </c>
       <c r="E98" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F98" s="54" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="G98" s="54" t="n">
         <v>0.3316</v>
       </c>
-      <c r="F98" s="54" t="n">
+      <c r="H98" s="54" t="n">
         <v>-4.31</v>
       </c>
-      <c r="G98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="54" t="inlineStr">
@@ -34690,12 +35071,17 @@
         <v>15</v>
       </c>
       <c r="E99" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F99" s="54" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="G99" s="54" t="n">
         <v>0.3316</v>
       </c>
-      <c r="F99" s="54" t="n">
+      <c r="H99" s="54" t="n">
         <v>-4.97</v>
       </c>
-      <c r="G99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="54" t="inlineStr">
@@ -34717,12 +35103,17 @@
         <v>15</v>
       </c>
       <c r="E100" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F100" s="54" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="G100" s="54" t="n">
         <v>0.3316</v>
       </c>
-      <c r="F100" s="54" t="n">
+      <c r="H100" s="54" t="n">
         <v>-4.97</v>
       </c>
-      <c r="G100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="54" t="inlineStr">
@@ -34744,12 +35135,17 @@
         <v>4</v>
       </c>
       <c r="E101" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F101" s="54" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="G101" s="54" t="n">
         <v>0.3316</v>
       </c>
-      <c r="F101" s="54" t="n">
+      <c r="H101" s="54" t="n">
         <v>-1.33</v>
       </c>
-      <c r="G101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="54" t="inlineStr">
@@ -34771,12 +35167,17 @@
         <v>10</v>
       </c>
       <c r="E102" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F102" s="54" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="G102" s="54" t="n">
         <v>1.6579</v>
       </c>
-      <c r="F102" s="54" t="n">
+      <c r="H102" s="54" t="n">
         <v>-16.58</v>
       </c>
-      <c r="G102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="54" t="inlineStr">
@@ -34798,12 +35199,17 @@
         <v>1</v>
       </c>
       <c r="E103" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F103" s="54" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="G103" s="54" t="n">
         <v>0.5526</v>
       </c>
-      <c r="F103" s="54" t="n">
+      <c r="H103" s="54" t="n">
         <v>-0.55</v>
       </c>
-      <c r="G103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="54" t="inlineStr">
@@ -34825,12 +35231,17 @@
         <v>187</v>
       </c>
       <c r="E104" s="54" t="n">
-        <v>0.3316</v>
+        <v>0.2</v>
       </c>
       <c r="F104" s="54" t="n">
-        <v>-62.01</v>
-      </c>
-      <c r="G104" s="2" t="n"/>
+        <v>1.105</v>
+      </c>
+      <c r="G104" s="54" t="n">
+        <v>0.2211</v>
+      </c>
+      <c r="H104" s="54" t="n">
+        <v>-41.34</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="53" t="inlineStr">
@@ -34855,9 +35266,14 @@
         <v>5</v>
       </c>
       <c r="F105" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G105" s="2" t="n"/>
+      <c r="H105" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="53" t="inlineStr">
@@ -34884,7 +35300,12 @@
       <c r="F106" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="G106" s="2" t="n"/>
+      <c r="G106" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="54" t="inlineStr">
@@ -34909,9 +35330,14 @@
         <v>0.5</v>
       </c>
       <c r="F107" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H107" s="54" t="n">
         <v>-1</v>
       </c>
-      <c r="G107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="54" t="inlineStr">
@@ -34933,12 +35359,17 @@
         <v>2</v>
       </c>
       <c r="E108" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F108" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G108" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F108" s="54" t="n">
+      <c r="H108" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="54" t="inlineStr">
@@ -34960,12 +35391,17 @@
         <v>2</v>
       </c>
       <c r="E109" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F109" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G109" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F109" s="54" t="n">
+      <c r="H109" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="54" t="inlineStr">
@@ -34987,12 +35423,17 @@
         <v>3</v>
       </c>
       <c r="E110" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F110" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G110" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F110" s="54" t="n">
+      <c r="H110" s="54" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="54" t="inlineStr">
@@ -35014,12 +35455,17 @@
         <v>13</v>
       </c>
       <c r="E111" s="54" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F111" s="54" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="G111" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G111" s="54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H111" s="54" t="n">
+        <v>-5.2</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="53" t="inlineStr">
@@ -35044,9 +35490,14 @@
         <v>5</v>
       </c>
       <c r="F112" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="53" t="inlineStr">
@@ -35071,9 +35522,14 @@
         <v>1</v>
       </c>
       <c r="F113" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="53" t="n">
         <v>15</v>
       </c>
-      <c r="G113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="54" t="inlineStr">
@@ -35098,9 +35554,14 @@
         <v>0.5</v>
       </c>
       <c r="F114" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H114" s="54" t="n">
         <v>-2.5</v>
       </c>
-      <c r="G114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="54" t="inlineStr">
@@ -35122,12 +35583,17 @@
         <v>1</v>
       </c>
       <c r="E115" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F115" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G115" s="54" t="n">
         <v>0.33</v>
       </c>
-      <c r="F115" s="54" t="n">
+      <c r="H115" s="54" t="n">
         <v>-0.33</v>
       </c>
-      <c r="G115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="54" t="inlineStr">
@@ -35149,12 +35615,17 @@
         <v>12</v>
       </c>
       <c r="E116" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F116" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G116" s="54" t="n">
         <v>0.33</v>
       </c>
-      <c r="F116" s="54" t="n">
+      <c r="H116" s="54" t="n">
         <v>-3.96</v>
       </c>
-      <c r="G116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="54" t="inlineStr">
@@ -35176,12 +35647,17 @@
         <v>8</v>
       </c>
       <c r="E117" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F117" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G117" s="54" t="n">
         <v>0.33</v>
       </c>
-      <c r="F117" s="54" t="n">
+      <c r="H117" s="54" t="n">
         <v>-2.64</v>
       </c>
-      <c r="G117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="54" t="inlineStr">
@@ -35203,12 +35679,17 @@
         <v>7</v>
       </c>
       <c r="E118" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F118" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G118" s="54" t="n">
         <v>1.65</v>
       </c>
-      <c r="F118" s="54" t="n">
+      <c r="H118" s="54" t="n">
         <v>-11.55</v>
       </c>
-      <c r="G118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="54" t="inlineStr">
@@ -35230,12 +35711,17 @@
         <v>2</v>
       </c>
       <c r="E119" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="54" t="n">
         <v>1.1</v>
       </c>
-      <c r="F119" s="54" t="n">
+      <c r="G119" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H119" s="54" t="n">
         <v>-2.2</v>
       </c>
-      <c r="G119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="54" t="inlineStr">
@@ -35257,12 +35743,17 @@
         <v>3</v>
       </c>
       <c r="E120" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F120" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G120" s="54" t="n">
         <v>0.55</v>
       </c>
-      <c r="F120" s="54" t="n">
+      <c r="H120" s="54" t="n">
         <v>-1.65</v>
       </c>
-      <c r="G120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="54" t="inlineStr">
@@ -35284,12 +35775,17 @@
         <v>1</v>
       </c>
       <c r="E121" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F121" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G121" s="54" t="n">
         <v>0.55</v>
       </c>
-      <c r="F121" s="54" t="n">
+      <c r="H121" s="54" t="n">
         <v>-0.55</v>
       </c>
-      <c r="G121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="53" t="inlineStr">
@@ -35314,9 +35810,14 @@
         <v>1</v>
       </c>
       <c r="F122" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" s="53" t="n">
         <v>13</v>
       </c>
-      <c r="G122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="54" t="inlineStr">
@@ -35341,9 +35842,14 @@
         <v>0.5</v>
       </c>
       <c r="F123" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H123" s="54" t="n">
         <v>-2.5</v>
       </c>
-      <c r="G123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="54" t="inlineStr">
@@ -35365,12 +35871,17 @@
         <v>2</v>
       </c>
       <c r="E124" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F124" s="54" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="G124" s="54" t="n">
         <v>0.3667</v>
       </c>
-      <c r="F124" s="54" t="n">
+      <c r="H124" s="54" t="n">
         <v>-0.73</v>
       </c>
-      <c r="G124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="54" t="inlineStr">
@@ -35392,12 +35903,17 @@
         <v>8</v>
       </c>
       <c r="E125" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F125" s="54" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="G125" s="54" t="n">
         <v>0.3667</v>
       </c>
-      <c r="F125" s="54" t="n">
+      <c r="H125" s="54" t="n">
         <v>-2.93</v>
       </c>
-      <c r="G125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="54" t="inlineStr">
@@ -35419,12 +35935,17 @@
         <v>10</v>
       </c>
       <c r="E126" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F126" s="54" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="G126" s="54" t="n">
         <v>0.3667</v>
       </c>
-      <c r="F126" s="54" t="n">
+      <c r="H126" s="54" t="n">
         <v>-3.67</v>
       </c>
-      <c r="G126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="54" t="inlineStr">
@@ -35446,12 +35967,17 @@
         <v>3</v>
       </c>
       <c r="E127" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F127" s="54" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="G127" s="54" t="n">
         <v>0.3667</v>
       </c>
-      <c r="F127" s="54" t="n">
+      <c r="H127" s="54" t="n">
         <v>-1.1</v>
       </c>
-      <c r="G127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="54" t="inlineStr">
@@ -35473,12 +35999,17 @@
         <v>12</v>
       </c>
       <c r="E128" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F128" s="54" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="G128" s="54" t="n">
         <v>1.8333</v>
       </c>
-      <c r="F128" s="54" t="n">
+      <c r="H128" s="54" t="n">
         <v>-22</v>
       </c>
-      <c r="G128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="54" t="inlineStr">
@@ -35500,12 +36031,17 @@
         <v>3</v>
       </c>
       <c r="E129" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F129" s="54" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="G129" s="54" t="n">
         <v>0.6111</v>
       </c>
-      <c r="F129" s="54" t="n">
+      <c r="H129" s="54" t="n">
         <v>-1.83</v>
       </c>
-      <c r="G129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="54" t="inlineStr">
@@ -35527,12 +36063,17 @@
         <v>40</v>
       </c>
       <c r="E130" s="54" t="n">
-        <v>0.3667</v>
+        <v>0.2</v>
       </c>
       <c r="F130" s="54" t="n">
-        <v>-14.67</v>
-      </c>
-      <c r="G130" s="2" t="n"/>
+        <v>1.222</v>
+      </c>
+      <c r="G130" s="54" t="n">
+        <v>0.2444</v>
+      </c>
+      <c r="H130" s="54" t="n">
+        <v>-9.779999999999999</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="53" t="inlineStr">
@@ -35557,9 +36098,14 @@
         <v>1</v>
       </c>
       <c r="F131" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="G131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="54" t="inlineStr">
@@ -35584,9 +36130,14 @@
         <v>0.5</v>
       </c>
       <c r="F132" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H132" s="54" t="n">
         <v>-5</v>
       </c>
-      <c r="G132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="54" t="inlineStr">
@@ -35608,12 +36159,17 @@
         <v>3</v>
       </c>
       <c r="E133" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F133" s="54" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="G133" s="54" t="n">
         <v>0.3136</v>
       </c>
-      <c r="F133" s="54" t="n">
+      <c r="H133" s="54" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="G133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="54" t="inlineStr">
@@ -35635,12 +36191,17 @@
         <v>6</v>
       </c>
       <c r="E134" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F134" s="54" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="G134" s="54" t="n">
         <v>0.3136</v>
       </c>
-      <c r="F134" s="54" t="n">
+      <c r="H134" s="54" t="n">
         <v>-1.88</v>
       </c>
-      <c r="G134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="54" t="inlineStr">
@@ -35662,12 +36223,17 @@
         <v>9</v>
       </c>
       <c r="E135" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F135" s="54" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="G135" s="54" t="n">
         <v>0.3136</v>
       </c>
-      <c r="F135" s="54" t="n">
+      <c r="H135" s="54" t="n">
         <v>-2.82</v>
       </c>
-      <c r="G135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="54" t="inlineStr">
@@ -35689,12 +36255,17 @@
         <v>9</v>
       </c>
       <c r="E136" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F136" s="54" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="G136" s="54" t="n">
         <v>0.3136</v>
       </c>
-      <c r="F136" s="54" t="n">
+      <c r="H136" s="54" t="n">
         <v>-2.82</v>
       </c>
-      <c r="G136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="54" t="inlineStr">
@@ -35716,12 +36287,17 @@
         <v>7</v>
       </c>
       <c r="E137" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F137" s="54" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="G137" s="54" t="n">
         <v>1.5682</v>
       </c>
-      <c r="F137" s="54" t="n">
+      <c r="H137" s="54" t="n">
         <v>-10.98</v>
       </c>
-      <c r="G137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="54" t="inlineStr">
@@ -35743,12 +36319,17 @@
         <v>2</v>
       </c>
       <c r="E138" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F138" s="54" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="G138" s="54" t="n">
         <v>0.3136</v>
       </c>
-      <c r="F138" s="54" t="n">
+      <c r="H138" s="54" t="n">
         <v>-0.63</v>
       </c>
-      <c r="G138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="54" t="inlineStr">
@@ -35770,12 +36351,17 @@
         <v>2</v>
       </c>
       <c r="E139" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="54" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="G139" s="54" t="n">
         <v>1.0455</v>
       </c>
-      <c r="F139" s="54" t="n">
+      <c r="H139" s="54" t="n">
         <v>-2.09</v>
       </c>
-      <c r="G139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="54" t="inlineStr">
@@ -35797,12 +36383,17 @@
         <v>10</v>
       </c>
       <c r="E140" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F140" s="54" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="G140" s="54" t="n">
         <v>0.5227000000000001</v>
       </c>
-      <c r="F140" s="54" t="n">
+      <c r="H140" s="54" t="n">
         <v>-5.23</v>
       </c>
-      <c r="G140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="54" t="inlineStr">
@@ -35824,12 +36415,17 @@
         <v>189</v>
       </c>
       <c r="E141" s="54" t="n">
-        <v>0.3136</v>
+        <v>0.2</v>
       </c>
       <c r="F141" s="54" t="n">
-        <v>-59.28</v>
-      </c>
-      <c r="G141" s="2" t="n"/>
+        <v>1.045</v>
+      </c>
+      <c r="G141" s="54" t="n">
+        <v>0.2091</v>
+      </c>
+      <c r="H141" s="54" t="n">
+        <v>-39.52</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="53" t="inlineStr">
@@ -35854,9 +36450,14 @@
         <v>1</v>
       </c>
       <c r="F142" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" s="53" t="n">
         <v>17</v>
       </c>
-      <c r="G142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="54" t="inlineStr">
@@ -35881,9 +36482,14 @@
         <v>0.5</v>
       </c>
       <c r="F143" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H143" s="54" t="n">
         <v>-3</v>
       </c>
-      <c r="G143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="54" t="inlineStr">
@@ -35905,12 +36511,17 @@
         <v>3</v>
       </c>
       <c r="E144" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F144" s="54" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="G144" s="54" t="n">
         <v>0.287</v>
       </c>
-      <c r="F144" s="54" t="n">
+      <c r="H144" s="54" t="n">
         <v>-0.86</v>
       </c>
-      <c r="G144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="54" t="inlineStr">
@@ -35932,12 +36543,17 @@
         <v>3</v>
       </c>
       <c r="E145" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F145" s="54" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="G145" s="54" t="n">
         <v>0.287</v>
       </c>
-      <c r="F145" s="54" t="n">
+      <c r="H145" s="54" t="n">
         <v>-0.86</v>
       </c>
-      <c r="G145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="54" t="inlineStr">
@@ -35959,12 +36575,17 @@
         <v>6</v>
       </c>
       <c r="E146" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F146" s="54" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="G146" s="54" t="n">
         <v>1.4348</v>
       </c>
-      <c r="F146" s="54" t="n">
+      <c r="H146" s="54" t="n">
         <v>-8.609999999999999</v>
       </c>
-      <c r="G146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="54" t="inlineStr">
@@ -35986,12 +36607,17 @@
         <v>3</v>
       </c>
       <c r="E147" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" s="54" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="G147" s="54" t="n">
         <v>0.9565</v>
       </c>
-      <c r="F147" s="54" t="n">
+      <c r="H147" s="54" t="n">
         <v>-2.87</v>
       </c>
-      <c r="G147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="54" t="inlineStr">
@@ -36013,12 +36639,17 @@
         <v>24</v>
       </c>
       <c r="E148" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F148" s="54" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="G148" s="54" t="n">
         <v>0.4783</v>
       </c>
-      <c r="F148" s="54" t="n">
+      <c r="H148" s="54" t="n">
         <v>-11.48</v>
       </c>
-      <c r="G148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="54" t="inlineStr">
@@ -36040,12 +36671,17 @@
         <v>21</v>
       </c>
       <c r="E149" s="54" t="n">
-        <v>0.287</v>
+        <v>0.2</v>
       </c>
       <c r="F149" s="54" t="n">
-        <v>-6.03</v>
-      </c>
-      <c r="G149" s="2" t="n"/>
+        <v>0.957</v>
+      </c>
+      <c r="G149" s="54" t="n">
+        <v>0.1913</v>
+      </c>
+      <c r="H149" s="54" t="n">
+        <v>-4.02</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="53" t="inlineStr">
@@ -36070,9 +36706,14 @@
         <v>5</v>
       </c>
       <c r="F150" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G150" s="2" t="n"/>
+      <c r="H150" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="53" t="inlineStr">
@@ -36097,9 +36738,14 @@
         <v>1</v>
       </c>
       <c r="F151" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" s="53" t="n">
         <v>15</v>
       </c>
-      <c r="G151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="54" t="inlineStr">
@@ -36124,9 +36770,14 @@
         <v>0.5</v>
       </c>
       <c r="F152" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H152" s="54" t="n">
         <v>-2.5</v>
       </c>
-      <c r="G152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="54" t="inlineStr">
@@ -36148,12 +36799,17 @@
         <v>1</v>
       </c>
       <c r="E153" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F153" s="54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G153" s="54" t="n">
         <v>0.315</v>
       </c>
-      <c r="F153" s="54" t="n">
+      <c r="H153" s="54" t="n">
         <v>-0.32</v>
       </c>
-      <c r="G153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="54" t="inlineStr">
@@ -36175,12 +36831,17 @@
         <v>10</v>
       </c>
       <c r="E154" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F154" s="54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G154" s="54" t="n">
         <v>0.315</v>
       </c>
-      <c r="F154" s="54" t="n">
+      <c r="H154" s="54" t="n">
         <v>-3.15</v>
       </c>
-      <c r="G154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="54" t="inlineStr">
@@ -36202,12 +36863,17 @@
         <v>17</v>
       </c>
       <c r="E155" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F155" s="54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G155" s="54" t="n">
         <v>0.315</v>
       </c>
-      <c r="F155" s="54" t="n">
+      <c r="H155" s="54" t="n">
         <v>-5.36</v>
       </c>
-      <c r="G155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="54" t="inlineStr">
@@ -36229,12 +36895,17 @@
         <v>1</v>
       </c>
       <c r="E156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F156" s="54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G156" s="54" t="n">
         <v>0.315</v>
       </c>
-      <c r="F156" s="54" t="n">
+      <c r="H156" s="54" t="n">
         <v>-0.32</v>
       </c>
-      <c r="G156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="54" t="inlineStr">
@@ -36256,12 +36927,17 @@
         <v>10</v>
       </c>
       <c r="E157" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F157" s="54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G157" s="54" t="n">
         <v>1.575</v>
       </c>
-      <c r="F157" s="54" t="n">
+      <c r="H157" s="54" t="n">
         <v>-15.75</v>
       </c>
-      <c r="G157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="54" t="inlineStr">
@@ -36283,12 +36959,17 @@
         <v>2</v>
       </c>
       <c r="E158" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" s="54" t="n">
         <v>1.05</v>
       </c>
-      <c r="F158" s="54" t="n">
+      <c r="G158" s="54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H158" s="54" t="n">
         <v>-2.1</v>
       </c>
-      <c r="G158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="54" t="inlineStr">
@@ -36310,12 +36991,17 @@
         <v>1</v>
       </c>
       <c r="E159" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F159" s="54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G159" s="54" t="n">
         <v>0.525</v>
       </c>
-      <c r="F159" s="54" t="n">
+      <c r="H159" s="54" t="n">
         <v>-0.53</v>
       </c>
-      <c r="G159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="53" t="inlineStr">
@@ -36340,9 +37026,14 @@
         <v>1</v>
       </c>
       <c r="F160" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" s="53" t="n">
         <v>13</v>
       </c>
-      <c r="G160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="54" t="inlineStr">
@@ -36367,9 +37058,14 @@
         <v>0.5</v>
       </c>
       <c r="F161" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H161" s="54" t="n">
         <v>-4</v>
       </c>
-      <c r="G161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="54" t="inlineStr">
@@ -36391,12 +37087,17 @@
         <v>1</v>
       </c>
       <c r="E162" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F162" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G162" s="54" t="n">
         <v>0.3286</v>
       </c>
-      <c r="F162" s="54" t="n">
+      <c r="H162" s="54" t="n">
         <v>-0.33</v>
       </c>
-      <c r="G162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="54" t="inlineStr">
@@ -36418,12 +37119,17 @@
         <v>6</v>
       </c>
       <c r="E163" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F163" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G163" s="54" t="n">
         <v>0.3286</v>
       </c>
-      <c r="F163" s="54" t="n">
+      <c r="H163" s="54" t="n">
         <v>-1.97</v>
       </c>
-      <c r="G163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="54" t="inlineStr">
@@ -36445,12 +37151,17 @@
         <v>5</v>
       </c>
       <c r="E164" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F164" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G164" s="54" t="n">
         <v>0.3286</v>
       </c>
-      <c r="F164" s="54" t="n">
+      <c r="H164" s="54" t="n">
         <v>-1.64</v>
       </c>
-      <c r="G164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="54" t="inlineStr">
@@ -36472,12 +37183,17 @@
         <v>2</v>
       </c>
       <c r="E165" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F165" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G165" s="54" t="n">
         <v>0.3286</v>
       </c>
-      <c r="F165" s="54" t="n">
+      <c r="H165" s="54" t="n">
         <v>-0.66</v>
       </c>
-      <c r="G165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="54" t="inlineStr">
@@ -36499,12 +37215,17 @@
         <v>12</v>
       </c>
       <c r="E166" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F166" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G166" s="54" t="n">
         <v>1.6429</v>
       </c>
-      <c r="F166" s="54" t="n">
+      <c r="H166" s="54" t="n">
         <v>-19.71</v>
       </c>
-      <c r="G166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="54" t="inlineStr">
@@ -36526,12 +37247,17 @@
         <v>6</v>
       </c>
       <c r="E167" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G167" s="54" t="n">
         <v>1.0952</v>
       </c>
-      <c r="F167" s="54" t="n">
+      <c r="H167" s="54" t="n">
         <v>-6.57</v>
       </c>
-      <c r="G167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="54" t="inlineStr">
@@ -36553,12 +37279,17 @@
         <v>10</v>
       </c>
       <c r="E168" s="54" t="n">
-        <v>0.3286</v>
+        <v>0.2</v>
       </c>
       <c r="F168" s="54" t="n">
-        <v>-3.29</v>
-      </c>
-      <c r="G168" s="2" t="n"/>
+        <v>1.095</v>
+      </c>
+      <c r="G168" s="54" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="H168" s="54" t="n">
+        <v>-2.19</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="53" t="inlineStr">
@@ -36583,9 +37314,14 @@
         <v>5</v>
       </c>
       <c r="F169" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G169" s="2" t="n"/>
+      <c r="H169" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="53" t="inlineStr">
@@ -36610,9 +37346,14 @@
         <v>5</v>
       </c>
       <c r="F170" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G170" s="2" t="n"/>
+      <c r="H170" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="53" t="inlineStr">
@@ -36637,9 +37378,14 @@
         <v>1</v>
       </c>
       <c r="F171" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="G171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="54" t="inlineStr">
@@ -36664,9 +37410,14 @@
         <v>0.5</v>
       </c>
       <c r="F172" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H172" s="54" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="54" t="inlineStr">
@@ -36688,12 +37439,17 @@
         <v>1</v>
       </c>
       <c r="E173" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F173" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G173" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F173" s="54" t="n">
+      <c r="H173" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="54" t="inlineStr">
@@ -36715,12 +37471,17 @@
         <v>3</v>
       </c>
       <c r="E174" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F174" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G174" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F174" s="54" t="n">
+      <c r="H174" s="54" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="53" t="inlineStr">
@@ -36745,9 +37506,14 @@
         <v>1</v>
       </c>
       <c r="F175" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" s="53" t="n">
         <v>13</v>
       </c>
-      <c r="G175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="54" t="inlineStr">
@@ -36772,9 +37538,14 @@
         <v>0.5</v>
       </c>
       <c r="F176" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H176" s="54" t="n">
         <v>-5</v>
       </c>
-      <c r="G176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="54" t="inlineStr">
@@ -36796,12 +37567,17 @@
         <v>3</v>
       </c>
       <c r="E177" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F177" s="54" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="G177" s="54" t="n">
         <v>0.2739</v>
       </c>
-      <c r="F177" s="54" t="n">
+      <c r="H177" s="54" t="n">
         <v>-0.82</v>
       </c>
-      <c r="G177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="54" t="inlineStr">
@@ -36823,12 +37599,17 @@
         <v>7</v>
       </c>
       <c r="E178" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F178" s="54" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="G178" s="54" t="n">
         <v>0.2739</v>
       </c>
-      <c r="F178" s="54" t="n">
+      <c r="H178" s="54" t="n">
         <v>-1.92</v>
       </c>
-      <c r="G178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="54" t="inlineStr">
@@ -36850,12 +37631,17 @@
         <v>15</v>
       </c>
       <c r="E179" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F179" s="54" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="G179" s="54" t="n">
         <v>0.2739</v>
       </c>
-      <c r="F179" s="54" t="n">
+      <c r="H179" s="54" t="n">
         <v>-4.11</v>
       </c>
-      <c r="G179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="54" t="inlineStr">
@@ -36877,12 +37663,17 @@
         <v>7</v>
       </c>
       <c r="E180" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F180" s="54" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="G180" s="54" t="n">
         <v>0.2739</v>
       </c>
-      <c r="F180" s="54" t="n">
+      <c r="H180" s="54" t="n">
         <v>-1.92</v>
       </c>
-      <c r="G180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="54" t="inlineStr">
@@ -36904,12 +37695,17 @@
         <v>7</v>
       </c>
       <c r="E181" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F181" s="54" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="G181" s="54" t="n">
         <v>1.3696</v>
       </c>
-      <c r="F181" s="54" t="n">
+      <c r="H181" s="54" t="n">
         <v>-9.59</v>
       </c>
-      <c r="G181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="54" t="inlineStr">
@@ -36931,12 +37727,17 @@
         <v>4</v>
       </c>
       <c r="E182" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" s="54" t="n">
         <v>0.913</v>
       </c>
-      <c r="F182" s="54" t="n">
+      <c r="G182" s="54" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="H182" s="54" t="n">
         <v>-3.65</v>
       </c>
-      <c r="G182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="54" t="inlineStr">
@@ -36958,12 +37759,17 @@
         <v>94</v>
       </c>
       <c r="E183" s="54" t="n">
-        <v>0.2739</v>
+        <v>0.2</v>
       </c>
       <c r="F183" s="54" t="n">
-        <v>-25.75</v>
-      </c>
-      <c r="G183" s="2" t="n"/>
+        <v>0.913</v>
+      </c>
+      <c r="G183" s="54" t="n">
+        <v>0.1826</v>
+      </c>
+      <c r="H183" s="54" t="n">
+        <v>-17.17</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="53" t="inlineStr">
@@ -36988,9 +37794,14 @@
         <v>5</v>
       </c>
       <c r="F184" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G184" s="2" t="n"/>
+      <c r="H184" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="53" t="inlineStr">
@@ -37015,9 +37826,14 @@
         <v>1</v>
       </c>
       <c r="F185" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="G185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="54" t="inlineStr">
@@ -37042,9 +37858,14 @@
         <v>0.5</v>
       </c>
       <c r="F186" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H186" s="54" t="n">
         <v>-5</v>
       </c>
-      <c r="G186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="54" t="inlineStr">
@@ -37066,12 +37887,17 @@
         <v>6</v>
       </c>
       <c r="E187" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F187" s="54" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="G187" s="54" t="n">
         <v>0.3136</v>
       </c>
-      <c r="F187" s="54" t="n">
+      <c r="H187" s="54" t="n">
         <v>-1.88</v>
       </c>
-      <c r="G187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="54" t="inlineStr">
@@ -37093,12 +37919,17 @@
         <v>15</v>
       </c>
       <c r="E188" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F188" s="54" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="G188" s="54" t="n">
         <v>0.3136</v>
       </c>
-      <c r="F188" s="54" t="n">
+      <c r="H188" s="54" t="n">
         <v>-4.7</v>
       </c>
-      <c r="G188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="54" t="inlineStr">
@@ -37120,12 +37951,17 @@
         <v>8</v>
       </c>
       <c r="E189" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F189" s="54" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="G189" s="54" t="n">
         <v>0.3136</v>
       </c>
-      <c r="F189" s="54" t="n">
+      <c r="H189" s="54" t="n">
         <v>-2.51</v>
       </c>
-      <c r="G189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="54" t="inlineStr">
@@ -37147,12 +37983,17 @@
         <v>7</v>
       </c>
       <c r="E190" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F190" s="54" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="G190" s="54" t="n">
         <v>1.5682</v>
       </c>
-      <c r="F190" s="54" t="n">
+      <c r="H190" s="54" t="n">
         <v>-10.98</v>
       </c>
-      <c r="G190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="54" t="inlineStr">
@@ -37174,12 +38015,17 @@
         <v>3</v>
       </c>
       <c r="E191" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F191" s="54" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="G191" s="54" t="n">
         <v>0.5227000000000001</v>
       </c>
-      <c r="F191" s="54" t="n">
+      <c r="H191" s="54" t="n">
         <v>-1.57</v>
       </c>
-      <c r="G191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="54" t="inlineStr">
@@ -37201,12 +38047,17 @@
         <v>1</v>
       </c>
       <c r="E192" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F192" s="54" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="G192" s="54" t="n">
         <v>0.5227000000000001</v>
       </c>
-      <c r="F192" s="54" t="n">
+      <c r="H192" s="54" t="n">
         <v>-0.52</v>
       </c>
-      <c r="G192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="53" t="inlineStr">
@@ -37231,9 +38082,14 @@
         <v>1</v>
       </c>
       <c r="F193" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H193" s="53" t="n">
         <v>17</v>
       </c>
-      <c r="G193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="54" t="inlineStr">
@@ -37258,9 +38114,14 @@
         <v>0.5</v>
       </c>
       <c r="F194" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H194" s="54" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="54" t="inlineStr">
@@ -37282,12 +38143,17 @@
         <v>7</v>
       </c>
       <c r="E195" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F195" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G195" s="54" t="n">
         <v>0.33</v>
       </c>
-      <c r="F195" s="54" t="n">
+      <c r="H195" s="54" t="n">
         <v>-2.31</v>
       </c>
-      <c r="G195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="54" t="inlineStr">
@@ -37309,12 +38175,17 @@
         <v>17</v>
       </c>
       <c r="E196" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F196" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G196" s="54" t="n">
         <v>0.33</v>
       </c>
-      <c r="F196" s="54" t="n">
+      <c r="H196" s="54" t="n">
         <v>-5.61</v>
       </c>
-      <c r="G196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="54" t="inlineStr">
@@ -37336,12 +38207,17 @@
         <v>1</v>
       </c>
       <c r="E197" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F197" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G197" s="54" t="n">
         <v>0.33</v>
       </c>
-      <c r="F197" s="54" t="n">
+      <c r="H197" s="54" t="n">
         <v>-0.33</v>
       </c>
-      <c r="G197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="54" t="inlineStr">
@@ -37363,12 +38239,17 @@
         <v>8</v>
       </c>
       <c r="E198" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F198" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G198" s="54" t="n">
         <v>1.65</v>
       </c>
-      <c r="F198" s="54" t="n">
+      <c r="H198" s="54" t="n">
         <v>-13.2</v>
       </c>
-      <c r="G198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="54" t="inlineStr">
@@ -37390,12 +38271,17 @@
         <v>2</v>
       </c>
       <c r="E199" s="54" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="F199" s="54" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="G199" s="2" t="n"/>
+        <v>1.1</v>
+      </c>
+      <c r="G199" s="54" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H199" s="54" t="n">
+        <v>-0.44</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="53" t="inlineStr">
@@ -37420,9 +38306,14 @@
         <v>5</v>
       </c>
       <c r="F200" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G200" s="2" t="n"/>
+      <c r="H200" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="53" t="inlineStr">
@@ -37447,9 +38338,14 @@
         <v>1</v>
       </c>
       <c r="F201" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="G201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="54" t="inlineStr">
@@ -37474,9 +38370,14 @@
         <v>0.5</v>
       </c>
       <c r="F202" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H202" s="54" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="54" t="inlineStr">
@@ -37498,12 +38399,17 @@
         <v>2</v>
       </c>
       <c r="E203" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F203" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G203" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F203" s="54" t="n">
+      <c r="H203" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="54" t="inlineStr">
@@ -37525,12 +38431,17 @@
         <v>2</v>
       </c>
       <c r="E204" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F204" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F204" s="54" t="n">
+      <c r="H204" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="54" t="inlineStr">
@@ -37552,12 +38463,17 @@
         <v>2</v>
       </c>
       <c r="E205" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F205" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G205" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F205" s="54" t="n">
+      <c r="H205" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="54" t="inlineStr">
@@ -37579,12 +38495,17 @@
         <v>14</v>
       </c>
       <c r="E206" s="54" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F206" s="54" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="G206" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G206" s="54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H206" s="54" t="n">
+        <v>-5.6</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="53" t="inlineStr">
@@ -37609,9 +38530,14 @@
         <v>1</v>
       </c>
       <c r="F207" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H207" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="G207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="54" t="inlineStr">
@@ -37636,9 +38562,14 @@
         <v>0.5</v>
       </c>
       <c r="F208" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H208" s="54" t="n">
         <v>-4.5</v>
       </c>
-      <c r="G208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="54" t="inlineStr">
@@ -37660,12 +38591,17 @@
         <v>1</v>
       </c>
       <c r="E209" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F209" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G209" s="54" t="n">
         <v>0.3286</v>
       </c>
-      <c r="F209" s="54" t="n">
+      <c r="H209" s="54" t="n">
         <v>-0.33</v>
       </c>
-      <c r="G209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="54" t="inlineStr">
@@ -37687,12 +38623,17 @@
         <v>17</v>
       </c>
       <c r="E210" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F210" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G210" s="54" t="n">
         <v>0.3286</v>
       </c>
-      <c r="F210" s="54" t="n">
+      <c r="H210" s="54" t="n">
         <v>-5.59</v>
       </c>
-      <c r="G210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="54" t="inlineStr">
@@ -37714,12 +38655,17 @@
         <v>10</v>
       </c>
       <c r="E211" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F211" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G211" s="54" t="n">
         <v>0.3286</v>
       </c>
-      <c r="F211" s="54" t="n">
+      <c r="H211" s="54" t="n">
         <v>-3.29</v>
       </c>
-      <c r="G211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="54" t="inlineStr">
@@ -37741,12 +38687,17 @@
         <v>11</v>
       </c>
       <c r="E212" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F212" s="54" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="G212" s="54" t="n">
         <v>1.6429</v>
       </c>
-      <c r="F212" s="54" t="n">
+      <c r="H212" s="54" t="n">
         <v>-18.07</v>
       </c>
-      <c r="G212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="54" t="inlineStr">
@@ -37768,12 +38719,17 @@
         <v>4</v>
       </c>
       <c r="E213" s="54" t="n">
-        <v>0.3286</v>
+        <v>0.2</v>
       </c>
       <c r="F213" s="54" t="n">
-        <v>-1.31</v>
-      </c>
-      <c r="G213" s="2" t="n"/>
+        <v>1.095</v>
+      </c>
+      <c r="G213" s="54" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="H213" s="54" t="n">
+        <v>-0.88</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="53" t="inlineStr">
@@ -37798,9 +38754,14 @@
         <v>5</v>
       </c>
       <c r="F214" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G214" s="2" t="n"/>
+      <c r="H214" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="54" t="inlineStr">
@@ -37825,9 +38786,14 @@
         <v>0.5</v>
       </c>
       <c r="F215" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H215" s="54" t="n">
         <v>-1</v>
       </c>
-      <c r="G215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="54" t="inlineStr">
@@ -37849,12 +38815,17 @@
         <v>1</v>
       </c>
       <c r="E216" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F216" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G216" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F216" s="54" t="n">
+      <c r="H216" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="54" t="inlineStr">
@@ -37876,12 +38847,17 @@
         <v>1</v>
       </c>
       <c r="E217" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F217" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G217" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F217" s="54" t="n">
+      <c r="H217" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="54" t="inlineStr">
@@ -37903,12 +38879,17 @@
         <v>2</v>
       </c>
       <c r="E218" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F218" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G218" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="F218" s="54" t="n">
+      <c r="H218" s="54" t="n">
         <v>-6</v>
       </c>
-      <c r="G218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="53" t="inlineStr">
@@ -37933,9 +38914,14 @@
         <v>1</v>
       </c>
       <c r="F219" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H219" s="53" t="n">
         <v>14</v>
       </c>
-      <c r="G219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="54" t="inlineStr">
@@ -37960,9 +38946,14 @@
         <v>0.5</v>
       </c>
       <c r="F220" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H220" s="54" t="n">
         <v>-3.5</v>
       </c>
-      <c r="G220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="54" t="inlineStr">
@@ -37984,12 +38975,17 @@
         <v>3</v>
       </c>
       <c r="E221" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F221" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G221" s="54" t="n">
         <v>0.3143</v>
       </c>
-      <c r="F221" s="54" t="n">
+      <c r="H221" s="54" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="G221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="54" t="inlineStr">
@@ -38011,12 +39007,17 @@
         <v>2</v>
       </c>
       <c r="E222" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F222" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G222" s="54" t="n">
         <v>0.3143</v>
       </c>
-      <c r="F222" s="54" t="n">
+      <c r="H222" s="54" t="n">
         <v>-0.63</v>
       </c>
-      <c r="G222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="54" t="inlineStr">
@@ -38038,12 +39039,17 @@
         <v>6</v>
       </c>
       <c r="E223" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F223" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G223" s="54" t="n">
         <v>0.3143</v>
       </c>
-      <c r="F223" s="54" t="n">
+      <c r="H223" s="54" t="n">
         <v>-1.89</v>
       </c>
-      <c r="G223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="54" t="inlineStr">
@@ -38065,12 +39071,17 @@
         <v>2</v>
       </c>
       <c r="E224" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F224" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G224" s="54" t="n">
         <v>0.3143</v>
       </c>
-      <c r="F224" s="54" t="n">
+      <c r="H224" s="54" t="n">
         <v>-0.63</v>
       </c>
-      <c r="G224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="54" t="inlineStr">
@@ -38092,12 +39103,17 @@
         <v>5</v>
       </c>
       <c r="E225" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F225" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G225" s="54" t="n">
         <v>1.5714</v>
       </c>
-      <c r="F225" s="54" t="n">
+      <c r="H225" s="54" t="n">
         <v>-7.86</v>
       </c>
-      <c r="G225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="54" t="inlineStr">
@@ -38119,12 +39135,17 @@
         <v>2</v>
       </c>
       <c r="E226" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F226" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G226" s="54" t="n">
         <v>1.0476</v>
       </c>
-      <c r="F226" s="54" t="n">
+      <c r="H226" s="54" t="n">
         <v>-2.1</v>
       </c>
-      <c r="G226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="54" t="inlineStr">
@@ -38146,12 +39167,17 @@
         <v>3</v>
       </c>
       <c r="E227" s="54" t="n">
-        <v>0.3143</v>
+        <v>0.2</v>
       </c>
       <c r="F227" s="54" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="G227" s="2" t="n"/>
+        <v>1.048</v>
+      </c>
+      <c r="G227" s="54" t="n">
+        <v>0.2095</v>
+      </c>
+      <c r="H227" s="54" t="n">
+        <v>-0.63</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="53" t="inlineStr">
@@ -38176,9 +39202,14 @@
         <v>1</v>
       </c>
       <c r="F228" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H228" s="53" t="n">
         <v>17</v>
       </c>
-      <c r="G228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="54" t="inlineStr">
@@ -38203,9 +39234,14 @@
         <v>0.5</v>
       </c>
       <c r="F229" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H229" s="54" t="n">
         <v>-3</v>
       </c>
-      <c r="G229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="54" t="inlineStr">
@@ -38227,12 +39263,17 @@
         <v>9</v>
       </c>
       <c r="E230" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F230" s="54" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="G230" s="54" t="n">
         <v>0.2739</v>
       </c>
-      <c r="F230" s="54" t="n">
+      <c r="H230" s="54" t="n">
         <v>-2.47</v>
       </c>
-      <c r="G230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="54" t="inlineStr">
@@ -38254,12 +39295,17 @@
         <v>15</v>
       </c>
       <c r="E231" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F231" s="54" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="G231" s="54" t="n">
         <v>0.2739</v>
       </c>
-      <c r="F231" s="54" t="n">
+      <c r="H231" s="54" t="n">
         <v>-4.11</v>
       </c>
-      <c r="G231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="54" t="inlineStr">
@@ -38281,12 +39327,17 @@
         <v>16</v>
       </c>
       <c r="E232" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F232" s="54" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="G232" s="54" t="n">
         <v>0.2739</v>
       </c>
-      <c r="F232" s="54" t="n">
+      <c r="H232" s="54" t="n">
         <v>-4.38</v>
       </c>
-      <c r="G232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="54" t="inlineStr">
@@ -38308,12 +39359,17 @@
         <v>2</v>
       </c>
       <c r="E233" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F233" s="54" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="G233" s="54" t="n">
         <v>0.2739</v>
       </c>
-      <c r="F233" s="54" t="n">
+      <c r="H233" s="54" t="n">
         <v>-0.55</v>
       </c>
-      <c r="G233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="54" t="inlineStr">
@@ -38335,12 +39391,17 @@
         <v>5</v>
       </c>
       <c r="E234" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F234" s="54" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="G234" s="54" t="n">
         <v>1.3696</v>
       </c>
-      <c r="F234" s="54" t="n">
+      <c r="H234" s="54" t="n">
         <v>-6.85</v>
       </c>
-      <c r="G234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="54" t="inlineStr">
@@ -38362,12 +39423,17 @@
         <v>9</v>
       </c>
       <c r="E235" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F235" s="54" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="G235" s="54" t="n">
         <v>0.4565</v>
       </c>
-      <c r="F235" s="54" t="n">
+      <c r="H235" s="54" t="n">
         <v>-4.11</v>
       </c>
-      <c r="G235" s="2" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="54" t="inlineStr">
@@ -38389,12 +39455,17 @@
         <v>7</v>
       </c>
       <c r="E236" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F236" s="54" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="G236" s="54" t="n">
         <v>0.4565</v>
       </c>
-      <c r="F236" s="54" t="n">
+      <c r="H236" s="54" t="n">
         <v>-3.2</v>
       </c>
-      <c r="G236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="54" t="inlineStr">
@@ -38416,12 +39487,17 @@
         <v>4</v>
       </c>
       <c r="E237" s="54" t="n">
-        <v>0.2739</v>
+        <v>0.2</v>
       </c>
       <c r="F237" s="54" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="G237" s="2" t="n"/>
+        <v>0.913</v>
+      </c>
+      <c r="G237" s="54" t="n">
+        <v>0.1826</v>
+      </c>
+      <c r="H237" s="54" t="n">
+        <v>-0.73</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="53" t="inlineStr">
@@ -38446,9 +39522,14 @@
         <v>1</v>
       </c>
       <c r="F238" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G238" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H238" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="G238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="54" t="inlineStr">
@@ -38473,9 +39554,14 @@
         <v>0.5</v>
       </c>
       <c r="F239" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G239" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H239" s="54" t="n">
         <v>-2.5</v>
       </c>
-      <c r="G239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="54" t="inlineStr">
@@ -38497,12 +39583,17 @@
         <v>2</v>
       </c>
       <c r="E240" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F240" s="54" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="G240" s="54" t="n">
         <v>0.3882</v>
       </c>
-      <c r="F240" s="54" t="n">
+      <c r="H240" s="54" t="n">
         <v>-0.78</v>
       </c>
-      <c r="G240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="54" t="inlineStr">
@@ -38524,12 +39615,17 @@
         <v>16</v>
       </c>
       <c r="E241" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F241" s="54" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="G241" s="54" t="n">
         <v>0.3882</v>
       </c>
-      <c r="F241" s="54" t="n">
+      <c r="H241" s="54" t="n">
         <v>-6.21</v>
       </c>
-      <c r="G241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="54" t="inlineStr">
@@ -38551,12 +39647,17 @@
         <v>2</v>
       </c>
       <c r="E242" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F242" s="54" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="G242" s="54" t="n">
         <v>0.3882</v>
       </c>
-      <c r="F242" s="54" t="n">
+      <c r="H242" s="54" t="n">
         <v>-0.78</v>
       </c>
-      <c r="G242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="54" t="inlineStr">
@@ -38578,12 +39679,17 @@
         <v>15</v>
       </c>
       <c r="E243" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F243" s="54" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="G243" s="54" t="n">
         <v>1.9412</v>
       </c>
-      <c r="F243" s="54" t="n">
+      <c r="H243" s="54" t="n">
         <v>-29.12</v>
       </c>
-      <c r="G243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="54" t="inlineStr">
@@ -38605,12 +39711,17 @@
         <v>180</v>
       </c>
       <c r="E244" s="54" t="n">
-        <v>0.3882</v>
+        <v>0.2</v>
       </c>
       <c r="F244" s="54" t="n">
-        <v>-69.88</v>
-      </c>
-      <c r="G244" s="2" t="n"/>
+        <v>1.294</v>
+      </c>
+      <c r="G244" s="54" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="H244" s="54" t="n">
+        <v>-46.59</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="53" t="inlineStr">
@@ -38635,9 +39746,14 @@
         <v>5</v>
       </c>
       <c r="F245" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G245" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G245" s="2" t="n"/>
+      <c r="H245" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="53" t="inlineStr">
@@ -38664,7 +39780,12 @@
       <c r="F246" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="G246" s="2" t="n"/>
+      <c r="G246" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H246" s="53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="54" t="inlineStr">
@@ -38689,9 +39810,14 @@
         <v>0.5</v>
       </c>
       <c r="F247" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G247" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H247" s="54" t="n">
         <v>-1</v>
       </c>
-      <c r="G247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="54" t="inlineStr">
@@ -38713,12 +39839,17 @@
         <v>1</v>
       </c>
       <c r="E248" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F248" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G248" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F248" s="54" t="n">
+      <c r="H248" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="54" t="inlineStr">
@@ -38740,12 +39871,17 @@
         <v>2</v>
       </c>
       <c r="E249" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F249" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G249" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F249" s="54" t="n">
+      <c r="H249" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="54" t="inlineStr">
@@ -38767,12 +39903,17 @@
         <v>2</v>
       </c>
       <c r="E250" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F250" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G250" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F250" s="54" t="n">
+      <c r="H250" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="54" t="inlineStr">
@@ -38794,12 +39935,17 @@
         <v>1</v>
       </c>
       <c r="E251" s="54" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F251" s="54" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G251" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G251" s="54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H251" s="54" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="53" t="inlineStr">
@@ -38824,9 +39970,14 @@
         <v>1</v>
       </c>
       <c r="F252" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G252" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H252" s="53" t="n">
         <v>13</v>
       </c>
-      <c r="G252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="54" t="inlineStr">
@@ -38851,9 +40002,14 @@
         <v>0.5</v>
       </c>
       <c r="F253" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G253" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H253" s="54" t="n">
         <v>-1</v>
       </c>
-      <c r="G253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="54" t="inlineStr">
@@ -38875,12 +40031,17 @@
         <v>1</v>
       </c>
       <c r="E254" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F254" s="54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G254" s="54" t="n">
         <v>0.42</v>
       </c>
-      <c r="F254" s="54" t="n">
+      <c r="H254" s="54" t="n">
         <v>-0.42</v>
       </c>
-      <c r="G254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="54" t="inlineStr">
@@ -38902,12 +40063,17 @@
         <v>3</v>
       </c>
       <c r="E255" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F255" s="54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G255" s="54" t="n">
         <v>0.42</v>
       </c>
-      <c r="F255" s="54" t="n">
+      <c r="H255" s="54" t="n">
         <v>-1.26</v>
       </c>
-      <c r="G255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="54" t="inlineStr">
@@ -38929,12 +40095,17 @@
         <v>9</v>
       </c>
       <c r="E256" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F256" s="54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G256" s="54" t="n">
         <v>0.42</v>
       </c>
-      <c r="F256" s="54" t="n">
+      <c r="H256" s="54" t="n">
         <v>-3.78</v>
       </c>
-      <c r="G256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="54" t="inlineStr">
@@ -38956,12 +40127,17 @@
         <v>5</v>
       </c>
       <c r="E257" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F257" s="54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G257" s="54" t="n">
         <v>0.42</v>
       </c>
-      <c r="F257" s="54" t="n">
+      <c r="H257" s="54" t="n">
         <v>-2.1</v>
       </c>
-      <c r="G257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="54" t="inlineStr">
@@ -38983,12 +40159,17 @@
         <v>16</v>
       </c>
       <c r="E258" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F258" s="54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G258" s="54" t="n">
         <v>2.1</v>
       </c>
-      <c r="F258" s="54" t="n">
+      <c r="H258" s="54" t="n">
         <v>-33.6</v>
       </c>
-      <c r="G258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="54" t="inlineStr">
@@ -39010,12 +40191,17 @@
         <v>194</v>
       </c>
       <c r="E259" s="54" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="F259" s="54" t="n">
-        <v>-81.48</v>
-      </c>
-      <c r="G259" s="2" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="G259" s="54" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H259" s="54" t="n">
+        <v>-54.32</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="53" t="inlineStr">
@@ -39040,9 +40226,14 @@
         <v>1</v>
       </c>
       <c r="F260" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G260" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H260" s="53" t="n">
         <v>15</v>
       </c>
-      <c r="G260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="54" t="inlineStr">
@@ -39067,9 +40258,14 @@
         <v>0.5</v>
       </c>
       <c r="F261" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G261" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H261" s="54" t="n">
         <v>-2.5</v>
       </c>
-      <c r="G261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="54" t="inlineStr">
@@ -39091,12 +40287,17 @@
         <v>5</v>
       </c>
       <c r="E262" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F262" s="54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G262" s="54" t="n">
         <v>0.315</v>
       </c>
-      <c r="F262" s="54" t="n">
+      <c r="H262" s="54" t="n">
         <v>-1.57</v>
       </c>
-      <c r="G262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="54" t="inlineStr">
@@ -39118,12 +40319,17 @@
         <v>14</v>
       </c>
       <c r="E263" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F263" s="54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G263" s="54" t="n">
         <v>0.315</v>
       </c>
-      <c r="F263" s="54" t="n">
+      <c r="H263" s="54" t="n">
         <v>-4.41</v>
       </c>
-      <c r="G263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="54" t="inlineStr">
@@ -39145,12 +40351,17 @@
         <v>16</v>
       </c>
       <c r="E264" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F264" s="54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G264" s="54" t="n">
         <v>0.315</v>
       </c>
-      <c r="F264" s="54" t="n">
+      <c r="H264" s="54" t="n">
         <v>-5.04</v>
       </c>
-      <c r="G264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="54" t="inlineStr">
@@ -39172,12 +40383,17 @@
         <v>10</v>
       </c>
       <c r="E265" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F265" s="54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G265" s="54" t="n">
         <v>0.315</v>
       </c>
-      <c r="F265" s="54" t="n">
+      <c r="H265" s="54" t="n">
         <v>-3.15</v>
       </c>
-      <c r="G265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="54" t="inlineStr">
@@ -39199,12 +40415,17 @@
         <v>10</v>
       </c>
       <c r="E266" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F266" s="54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G266" s="54" t="n">
         <v>1.575</v>
       </c>
-      <c r="F266" s="54" t="n">
+      <c r="H266" s="54" t="n">
         <v>-15.75</v>
       </c>
-      <c r="G266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="54" t="inlineStr">
@@ -39226,12 +40447,17 @@
         <v>210</v>
       </c>
       <c r="E267" s="54" t="n">
-        <v>0.315</v>
+        <v>0.2</v>
       </c>
       <c r="F267" s="54" t="n">
-        <v>-66.15000000000001</v>
-      </c>
-      <c r="G267" s="2" t="n"/>
+        <v>1.05</v>
+      </c>
+      <c r="G267" s="54" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H267" s="54" t="n">
+        <v>-44.1</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="53" t="inlineStr">
@@ -39256,9 +40482,14 @@
         <v>5</v>
       </c>
       <c r="F268" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G268" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G268" s="2" t="n"/>
+      <c r="H268" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="53" t="inlineStr">
@@ -39285,7 +40516,12 @@
       <c r="F269" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="G269" s="2" t="n"/>
+      <c r="G269" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H269" s="53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="54" t="inlineStr">
@@ -39310,9 +40546,14 @@
         <v>0.5</v>
       </c>
       <c r="F270" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G270" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H270" s="54" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="54" t="inlineStr">
@@ -39334,12 +40575,17 @@
         <v>2</v>
       </c>
       <c r="E271" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F271" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G271" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F271" s="54" t="n">
+      <c r="H271" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G271" s="2" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="54" t="inlineStr">
@@ -39361,12 +40607,17 @@
         <v>2</v>
       </c>
       <c r="E272" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F272" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G272" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F272" s="54" t="n">
+      <c r="H272" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="54" t="inlineStr">
@@ -39388,12 +40639,17 @@
         <v>9</v>
       </c>
       <c r="E273" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F273" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G273" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="F273" s="54" t="n">
+      <c r="H273" s="54" t="n">
         <v>-9</v>
       </c>
-      <c r="G273" s="2" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="54" t="inlineStr">
@@ -39415,12 +40671,17 @@
         <v>4</v>
       </c>
       <c r="E274" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F274" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G274" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="F274" s="54" t="n">
+      <c r="H274" s="54" t="n">
         <v>-4</v>
       </c>
-      <c r="G274" s="2" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="54" t="inlineStr">
@@ -39442,12 +40703,17 @@
         <v>6</v>
       </c>
       <c r="E275" s="54" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F275" s="54" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="G275" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G275" s="54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H275" s="54" t="n">
+        <v>-2.4</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="53" t="inlineStr">
@@ -39472,9 +40738,14 @@
         <v>1</v>
       </c>
       <c r="F276" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G276" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H276" s="53" t="n">
         <v>9</v>
       </c>
-      <c r="G276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="54" t="inlineStr">
@@ -39499,9 +40770,14 @@
         <v>0.5</v>
       </c>
       <c r="F277" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G277" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H277" s="54" t="n">
         <v>-3</v>
       </c>
-      <c r="G277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="54" t="inlineStr">
@@ -39523,12 +40799,17 @@
         <v>2</v>
       </c>
       <c r="E278" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F278" s="54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G278" s="54" t="n">
         <v>0.42</v>
       </c>
-      <c r="F278" s="54" t="n">
+      <c r="H278" s="54" t="n">
         <v>-0.84</v>
       </c>
-      <c r="G278" s="2" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="54" t="inlineStr">
@@ -39550,12 +40831,17 @@
         <v>6</v>
       </c>
       <c r="E279" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F279" s="54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G279" s="54" t="n">
         <v>0.42</v>
       </c>
-      <c r="F279" s="54" t="n">
+      <c r="H279" s="54" t="n">
         <v>-2.52</v>
       </c>
-      <c r="G279" s="2" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="54" t="inlineStr">
@@ -39577,12 +40863,17 @@
         <v>5</v>
       </c>
       <c r="E280" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F280" s="54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G280" s="54" t="n">
         <v>0.42</v>
       </c>
-      <c r="F280" s="54" t="n">
+      <c r="H280" s="54" t="n">
         <v>-2.1</v>
       </c>
-      <c r="G280" s="2" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="54" t="inlineStr">
@@ -39604,12 +40895,17 @@
         <v>20</v>
       </c>
       <c r="E281" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F281" s="54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G281" s="54" t="n">
         <v>2.1</v>
       </c>
-      <c r="F281" s="54" t="n">
+      <c r="H281" s="54" t="n">
         <v>-42</v>
       </c>
-      <c r="G281" s="2" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="54" t="inlineStr">
@@ -39631,12 +40927,17 @@
         <v>21</v>
       </c>
       <c r="E282" s="54" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="F282" s="54" t="n">
-        <v>-8.82</v>
-      </c>
-      <c r="G282" s="2" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="G282" s="54" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H282" s="54" t="n">
+        <v>-5.88</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="53" t="inlineStr">
@@ -39661,9 +40962,14 @@
         <v>5</v>
       </c>
       <c r="F283" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G283" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G283" s="2" t="n"/>
+      <c r="H283" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="54" t="inlineStr">
@@ -39688,9 +40994,14 @@
         <v>0.5</v>
       </c>
       <c r="F284" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G284" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H284" s="54" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G284" s="2" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="54" t="inlineStr">
@@ -39712,12 +41023,17 @@
         <v>1</v>
       </c>
       <c r="E285" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F285" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G285" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F285" s="54" t="n">
+      <c r="H285" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G285" s="2" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="54" t="inlineStr">
@@ -39739,12 +41055,17 @@
         <v>1</v>
       </c>
       <c r="E286" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F286" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G286" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F286" s="54" t="n">
+      <c r="H286" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="54" t="inlineStr">
@@ -39766,12 +41087,17 @@
         <v>4</v>
       </c>
       <c r="E287" s="54" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F287" s="54" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="G287" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G287" s="54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H287" s="54" t="n">
+        <v>-1.6</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="53" t="inlineStr">
@@ -39796,9 +41122,14 @@
         <v>1</v>
       </c>
       <c r="F288" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G288" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H288" s="53" t="n">
         <v>15</v>
       </c>
-      <c r="G288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="54" t="inlineStr">
@@ -39823,9 +41154,14 @@
         <v>0.5</v>
       </c>
       <c r="F289" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G289" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H289" s="54" t="n">
         <v>-3</v>
       </c>
-      <c r="G289" s="2" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="54" t="inlineStr">
@@ -39847,12 +41183,17 @@
         <v>4</v>
       </c>
       <c r="E290" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F290" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G290" s="54" t="n">
         <v>0.3143</v>
       </c>
-      <c r="F290" s="54" t="n">
+      <c r="H290" s="54" t="n">
         <v>-1.26</v>
       </c>
-      <c r="G290" s="2" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="54" t="inlineStr">
@@ -39874,12 +41215,17 @@
         <v>8</v>
       </c>
       <c r="E291" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F291" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G291" s="54" t="n">
         <v>0.3143</v>
       </c>
-      <c r="F291" s="54" t="n">
+      <c r="H291" s="54" t="n">
         <v>-2.51</v>
       </c>
-      <c r="G291" s="2" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="54" t="inlineStr">
@@ -39901,12 +41247,17 @@
         <v>10</v>
       </c>
       <c r="E292" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F292" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G292" s="54" t="n">
         <v>0.3143</v>
       </c>
-      <c r="F292" s="54" t="n">
+      <c r="H292" s="54" t="n">
         <v>-3.14</v>
       </c>
-      <c r="G292" s="2" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="54" t="inlineStr">
@@ -39928,12 +41279,17 @@
         <v>13</v>
       </c>
       <c r="E293" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F293" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G293" s="54" t="n">
         <v>0.3143</v>
       </c>
-      <c r="F293" s="54" t="n">
+      <c r="H293" s="54" t="n">
         <v>-4.09</v>
       </c>
-      <c r="G293" s="2" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="54" t="inlineStr">
@@ -39955,12 +41311,17 @@
         <v>8</v>
       </c>
       <c r="E294" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F294" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G294" s="54" t="n">
         <v>1.5714</v>
       </c>
-      <c r="F294" s="54" t="n">
+      <c r="H294" s="54" t="n">
         <v>-12.57</v>
       </c>
-      <c r="G294" s="2" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="54" t="inlineStr">
@@ -39982,12 +41343,17 @@
         <v>3</v>
       </c>
       <c r="E295" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F295" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G295" s="54" t="n">
         <v>0.3143</v>
       </c>
-      <c r="F295" s="54" t="n">
+      <c r="H295" s="54" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="G295" s="2" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="54" t="inlineStr">
@@ -40009,12 +41375,17 @@
         <v>15</v>
       </c>
       <c r="E296" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F296" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G296" s="54" t="n">
         <v>1.0476</v>
       </c>
-      <c r="F296" s="54" t="n">
+      <c r="H296" s="54" t="n">
         <v>-15.71</v>
       </c>
-      <c r="G296" s="2" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="54" t="inlineStr">
@@ -40036,12 +41407,17 @@
         <v>1</v>
       </c>
       <c r="E297" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F297" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G297" s="54" t="n">
         <v>0.5238</v>
       </c>
-      <c r="F297" s="54" t="n">
+      <c r="H297" s="54" t="n">
         <v>-0.52</v>
       </c>
-      <c r="G297" s="2" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="54" t="inlineStr">
@@ -40063,12 +41439,17 @@
         <v>1</v>
       </c>
       <c r="E298" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F298" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G298" s="54" t="n">
         <v>0.5238</v>
       </c>
-      <c r="F298" s="54" t="n">
+      <c r="H298" s="54" t="n">
         <v>-0.52</v>
       </c>
-      <c r="G298" s="2" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="54" t="inlineStr">
@@ -40090,12 +41471,17 @@
         <v>221</v>
       </c>
       <c r="E299" s="54" t="n">
-        <v>0.3143</v>
+        <v>0.2</v>
       </c>
       <c r="F299" s="54" t="n">
-        <v>-69.45999999999999</v>
-      </c>
-      <c r="G299" s="2" t="n"/>
+        <v>1.048</v>
+      </c>
+      <c r="G299" s="54" t="n">
+        <v>0.2095</v>
+      </c>
+      <c r="H299" s="54" t="n">
+        <v>-46.3</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="53" t="inlineStr">
@@ -40122,7 +41508,12 @@
       <c r="F300" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="G300" s="2" t="n"/>
+      <c r="G300" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H300" s="53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="54" t="inlineStr">
@@ -40147,9 +41538,14 @@
         <v>0.5</v>
       </c>
       <c r="F301" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G301" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H301" s="54" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G301" s="2" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="54" t="inlineStr">
@@ -40171,12 +41567,17 @@
         <v>1</v>
       </c>
       <c r="E302" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F302" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G302" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F302" s="54" t="n">
+      <c r="H302" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G302" s="2" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="54" t="inlineStr">
@@ -40198,12 +41599,17 @@
         <v>1</v>
       </c>
       <c r="E303" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F303" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G303" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F303" s="54" t="n">
+      <c r="H303" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G303" s="2" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="54" t="inlineStr">
@@ -40225,12 +41631,17 @@
         <v>2</v>
       </c>
       <c r="E304" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F304" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G304" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="F304" s="54" t="n">
+      <c r="H304" s="54" t="n">
         <v>-6</v>
       </c>
-      <c r="G304" s="2" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="54" t="inlineStr">
@@ -40252,12 +41663,17 @@
         <v>12</v>
       </c>
       <c r="E305" s="54" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F305" s="54" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="G305" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G305" s="54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H305" s="54" t="n">
+        <v>-4.8</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="53" t="inlineStr">
@@ -40282,9 +41698,14 @@
         <v>1</v>
       </c>
       <c r="F306" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G306" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H306" s="53" t="n">
         <v>13</v>
       </c>
-      <c r="G306" s="2" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="54" t="inlineStr">
@@ -40309,9 +41730,14 @@
         <v>0.5</v>
       </c>
       <c r="F307" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G307" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H307" s="54" t="n">
         <v>-4.5</v>
       </c>
-      <c r="G307" s="2" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="54" t="inlineStr">
@@ -40333,12 +41759,17 @@
         <v>3</v>
       </c>
       <c r="E308" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F308" s="54" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G308" s="54" t="n">
         <v>0.2864</v>
       </c>
-      <c r="F308" s="54" t="n">
+      <c r="H308" s="54" t="n">
         <v>-0.86</v>
       </c>
-      <c r="G308" s="2" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="54" t="inlineStr">
@@ -40360,12 +41791,17 @@
         <v>2</v>
       </c>
       <c r="E309" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F309" s="54" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G309" s="54" t="n">
         <v>0.2864</v>
       </c>
-      <c r="F309" s="54" t="n">
+      <c r="H309" s="54" t="n">
         <v>-0.57</v>
       </c>
-      <c r="G309" s="2" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="54" t="inlineStr">
@@ -40387,12 +41823,17 @@
         <v>4</v>
       </c>
       <c r="E310" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F310" s="54" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G310" s="54" t="n">
         <v>0.2864</v>
       </c>
-      <c r="F310" s="54" t="n">
+      <c r="H310" s="54" t="n">
         <v>-1.15</v>
       </c>
-      <c r="G310" s="2" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="54" t="inlineStr">
@@ -40414,12 +41855,17 @@
         <v>9</v>
       </c>
       <c r="E311" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F311" s="54" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G311" s="54" t="n">
         <v>1.4318</v>
       </c>
-      <c r="F311" s="54" t="n">
+      <c r="H311" s="54" t="n">
         <v>-12.89</v>
       </c>
-      <c r="G311" s="2" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="54" t="inlineStr">
@@ -40441,12 +41887,17 @@
         <v>15</v>
       </c>
       <c r="E312" s="54" t="n">
-        <v>0.2864</v>
+        <v>0.2</v>
       </c>
       <c r="F312" s="54" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="G312" s="2" t="n"/>
+        <v>0.955</v>
+      </c>
+      <c r="G312" s="54" t="n">
+        <v>0.1909</v>
+      </c>
+      <c r="H312" s="54" t="n">
+        <v>-2.86</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="53" t="inlineStr">
@@ -40471,9 +41922,14 @@
         <v>1</v>
       </c>
       <c r="F313" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G313" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H313" s="53" t="n">
         <v>11</v>
       </c>
-      <c r="G313" s="2" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="54" t="inlineStr">
@@ -40498,9 +41954,14 @@
         <v>0.5</v>
       </c>
       <c r="F314" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G314" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H314" s="54" t="n">
         <v>-1</v>
       </c>
-      <c r="G314" s="2" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="54" t="inlineStr">
@@ -40522,12 +41983,17 @@
         <v>1</v>
       </c>
       <c r="E315" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F315" s="54" t="n">
+        <v>1.615</v>
+      </c>
+      <c r="G315" s="54" t="n">
         <v>0.4846</v>
       </c>
-      <c r="F315" s="54" t="n">
+      <c r="H315" s="54" t="n">
         <v>-0.48</v>
       </c>
-      <c r="G315" s="2" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="54" t="inlineStr">
@@ -40549,12 +42015,17 @@
         <v>8</v>
       </c>
       <c r="E316" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F316" s="54" t="n">
+        <v>1.615</v>
+      </c>
+      <c r="G316" s="54" t="n">
         <v>0.4846</v>
       </c>
-      <c r="F316" s="54" t="n">
+      <c r="H316" s="54" t="n">
         <v>-3.88</v>
       </c>
-      <c r="G316" s="2" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="54" t="inlineStr">
@@ -40576,12 +42047,17 @@
         <v>10</v>
       </c>
       <c r="E317" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F317" s="54" t="n">
+        <v>1.615</v>
+      </c>
+      <c r="G317" s="54" t="n">
         <v>0.4846</v>
       </c>
-      <c r="F317" s="54" t="n">
+      <c r="H317" s="54" t="n">
         <v>-4.85</v>
       </c>
-      <c r="G317" s="2" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="54" t="inlineStr">
@@ -40603,12 +42079,17 @@
         <v>6</v>
       </c>
       <c r="E318" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F318" s="54" t="n">
+        <v>1.615</v>
+      </c>
+      <c r="G318" s="54" t="n">
         <v>0.4846</v>
       </c>
-      <c r="F318" s="54" t="n">
+      <c r="H318" s="54" t="n">
         <v>-2.91</v>
       </c>
-      <c r="G318" s="2" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="54" t="inlineStr">
@@ -40630,12 +42111,17 @@
         <v>4</v>
       </c>
       <c r="E319" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F319" s="54" t="n">
+        <v>1.615</v>
+      </c>
+      <c r="G319" s="54" t="n">
         <v>2.4231</v>
       </c>
-      <c r="F319" s="54" t="n">
+      <c r="H319" s="54" t="n">
         <v>-9.69</v>
       </c>
-      <c r="G319" s="2" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="54" t="inlineStr">
@@ -40657,12 +42143,17 @@
         <v>1</v>
       </c>
       <c r="E320" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F320" s="54" t="n">
+        <v>1.615</v>
+      </c>
+      <c r="G320" s="54" t="n">
         <v>0.8077</v>
       </c>
-      <c r="F320" s="54" t="n">
+      <c r="H320" s="54" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="G320" s="2" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="54" t="inlineStr">
@@ -40684,12 +42175,17 @@
         <v>225</v>
       </c>
       <c r="E321" s="54" t="n">
-        <v>0.4846</v>
+        <v>0.2</v>
       </c>
       <c r="F321" s="54" t="n">
-        <v>-109.04</v>
-      </c>
-      <c r="G321" s="2" t="n"/>
+        <v>1.615</v>
+      </c>
+      <c r="G321" s="54" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="H321" s="54" t="n">
+        <v>-72.69</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="53" t="inlineStr">
@@ -40714,9 +42210,14 @@
         <v>1</v>
       </c>
       <c r="F322" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G322" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H322" s="53" t="n">
         <v>15</v>
       </c>
-      <c r="G322" s="2" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="54" t="inlineStr">
@@ -40741,9 +42242,14 @@
         <v>0.5</v>
       </c>
       <c r="F323" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G323" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H323" s="54" t="n">
         <v>-3</v>
       </c>
-      <c r="G323" s="2" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="54" t="inlineStr">
@@ -40768,9 +42274,14 @@
         <v>0.3</v>
       </c>
       <c r="F324" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G324" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H324" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G324" s="2" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="54" t="inlineStr">
@@ -40795,9 +42306,14 @@
         <v>0.3</v>
       </c>
       <c r="F325" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G325" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H325" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G325" s="2" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="54" t="inlineStr">
@@ -40822,9 +42338,14 @@
         <v>0.3</v>
       </c>
       <c r="F326" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G326" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H326" s="54" t="n">
         <v>-4.5</v>
       </c>
-      <c r="G326" s="2" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="54" t="inlineStr">
@@ -40849,9 +42370,14 @@
         <v>0.3</v>
       </c>
       <c r="F327" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G327" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H327" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G327" s="2" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="54" t="inlineStr">
@@ -40876,9 +42402,14 @@
         <v>1.5</v>
       </c>
       <c r="F328" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G328" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H328" s="54" t="n">
         <v>-9</v>
       </c>
-      <c r="G328" s="2" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="54" t="inlineStr">
@@ -40903,9 +42434,14 @@
         <v>0.5</v>
       </c>
       <c r="F329" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G329" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H329" s="54" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G329" s="2" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="54" t="inlineStr">
@@ -40930,9 +42466,14 @@
         <v>0.5</v>
       </c>
       <c r="F330" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G330" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H330" s="54" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G330" s="2" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="54" t="inlineStr">
@@ -40954,12 +42495,17 @@
         <v>27</v>
       </c>
       <c r="E331" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F331" s="54" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="G331" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G331" s="54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H331" s="54" t="n">
+        <v>-5.4</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="53" t="inlineStr">
@@ -40984,9 +42530,14 @@
         <v>1</v>
       </c>
       <c r="F332" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G332" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H332" s="53" t="n">
         <v>13</v>
       </c>
-      <c r="G332" s="2" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="54" t="inlineStr">
@@ -41011,9 +42562,14 @@
         <v>0.5</v>
       </c>
       <c r="F333" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G333" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H333" s="54" t="n">
         <v>-2</v>
       </c>
-      <c r="G333" s="2" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="54" t="inlineStr">
@@ -41035,12 +42591,17 @@
         <v>1</v>
       </c>
       <c r="E334" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F334" s="54" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="G334" s="54" t="n">
         <v>0.4059</v>
       </c>
-      <c r="F334" s="54" t="n">
+      <c r="H334" s="54" t="n">
         <v>-0.41</v>
       </c>
-      <c r="G334" s="2" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="54" t="inlineStr">
@@ -41062,12 +42623,17 @@
         <v>2</v>
       </c>
       <c r="E335" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F335" s="54" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="G335" s="54" t="n">
         <v>0.4059</v>
       </c>
-      <c r="F335" s="54" t="n">
+      <c r="H335" s="54" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="G335" s="2" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="54" t="inlineStr">
@@ -41089,12 +42655,17 @@
         <v>15</v>
       </c>
       <c r="E336" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F336" s="54" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="G336" s="54" t="n">
         <v>0.4059</v>
       </c>
-      <c r="F336" s="54" t="n">
+      <c r="H336" s="54" t="n">
         <v>-6.09</v>
       </c>
-      <c r="G336" s="2" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="54" t="inlineStr">
@@ -41116,12 +42687,17 @@
         <v>10</v>
       </c>
       <c r="E337" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F337" s="54" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="G337" s="54" t="n">
         <v>0.4059</v>
       </c>
-      <c r="F337" s="54" t="n">
+      <c r="H337" s="54" t="n">
         <v>-4.06</v>
       </c>
-      <c r="G337" s="2" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="54" t="inlineStr">
@@ -41143,12 +42719,17 @@
         <v>14</v>
       </c>
       <c r="E338" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F338" s="54" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="G338" s="54" t="n">
         <v>2.0294</v>
       </c>
-      <c r="F338" s="54" t="n">
+      <c r="H338" s="54" t="n">
         <v>-28.41</v>
       </c>
-      <c r="G338" s="2" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="54" t="inlineStr">
@@ -41170,12 +42751,17 @@
         <v>105</v>
       </c>
       <c r="E339" s="54" t="n">
-        <v>0.4059</v>
+        <v>0.2</v>
       </c>
       <c r="F339" s="54" t="n">
-        <v>-42.62</v>
-      </c>
-      <c r="G339" s="2" t="n"/>
+        <v>1.353</v>
+      </c>
+      <c r="G339" s="54" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="H339" s="54" t="n">
+        <v>-28.41</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="53" t="inlineStr">
@@ -41200,9 +42786,14 @@
         <v>5</v>
       </c>
       <c r="F340" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G340" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G340" s="2" t="n"/>
+      <c r="H340" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="53" t="inlineStr">
@@ -41227,9 +42818,14 @@
         <v>1</v>
       </c>
       <c r="F341" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G341" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H341" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="G341" s="2" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="54" t="inlineStr">
@@ -41254,9 +42850,14 @@
         <v>0.5</v>
       </c>
       <c r="F342" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G342" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H342" s="54" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G342" s="2" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="54" t="inlineStr">
@@ -41278,12 +42879,17 @@
         <v>2</v>
       </c>
       <c r="E343" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F343" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G343" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F343" s="54" t="n">
+      <c r="H343" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G343" s="2" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="54" t="inlineStr">
@@ -41305,12 +42911,17 @@
         <v>1</v>
       </c>
       <c r="E344" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F344" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G344" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F344" s="54" t="n">
+      <c r="H344" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G344" s="2" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="54" t="inlineStr">
@@ -41332,12 +42943,17 @@
         <v>2</v>
       </c>
       <c r="E345" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F345" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G345" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F345" s="54" t="n">
+      <c r="H345" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G345" s="2" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="54" t="inlineStr">
@@ -41359,12 +42975,17 @@
         <v>3</v>
       </c>
       <c r="E346" s="54" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F346" s="54" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G346" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G346" s="54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H346" s="54" t="n">
+        <v>-1.2</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="53" t="inlineStr">
@@ -41389,9 +43010,14 @@
         <v>1</v>
       </c>
       <c r="F347" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G347" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H347" s="53" t="n">
         <v>14</v>
       </c>
-      <c r="G347" s="2" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="54" t="inlineStr">
@@ -41416,9 +43042,14 @@
         <v>0.5</v>
       </c>
       <c r="F348" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G348" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H348" s="54" t="n">
         <v>-4</v>
       </c>
-      <c r="G348" s="2" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="54" t="inlineStr">
@@ -41440,12 +43071,17 @@
         <v>1</v>
       </c>
       <c r="E349" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F349" s="54" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G349" s="54" t="n">
         <v>0.2864</v>
       </c>
-      <c r="F349" s="54" t="n">
+      <c r="H349" s="54" t="n">
         <v>-0.29</v>
       </c>
-      <c r="G349" s="2" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="54" t="inlineStr">
@@ -41467,12 +43103,17 @@
         <v>18</v>
       </c>
       <c r="E350" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F350" s="54" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G350" s="54" t="n">
         <v>0.2864</v>
       </c>
-      <c r="F350" s="54" t="n">
+      <c r="H350" s="54" t="n">
         <v>-5.15</v>
       </c>
-      <c r="G350" s="2" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="54" t="inlineStr">
@@ -41494,12 +43135,17 @@
         <v>2</v>
       </c>
       <c r="E351" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F351" s="54" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G351" s="54" t="n">
         <v>0.2864</v>
       </c>
-      <c r="F351" s="54" t="n">
+      <c r="H351" s="54" t="n">
         <v>-0.57</v>
       </c>
-      <c r="G351" s="2" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="54" t="inlineStr">
@@ -41521,12 +43167,17 @@
         <v>7</v>
       </c>
       <c r="E352" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F352" s="54" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G352" s="54" t="n">
         <v>1.4318</v>
       </c>
-      <c r="F352" s="54" t="n">
+      <c r="H352" s="54" t="n">
         <v>-10.02</v>
       </c>
-      <c r="G352" s="2" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="54" t="inlineStr">
@@ -41548,12 +43199,17 @@
         <v>10</v>
       </c>
       <c r="E353" s="54" t="n">
-        <v>0.2864</v>
+        <v>0.2</v>
       </c>
       <c r="F353" s="54" t="n">
-        <v>-2.86</v>
-      </c>
-      <c r="G353" s="2" t="n"/>
+        <v>0.955</v>
+      </c>
+      <c r="G353" s="54" t="n">
+        <v>0.1909</v>
+      </c>
+      <c r="H353" s="54" t="n">
+        <v>-1.91</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="53" t="inlineStr">
@@ -41578,9 +43234,14 @@
         <v>1</v>
       </c>
       <c r="F354" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G354" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H354" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="G354" s="2" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="54" t="inlineStr">
@@ -41605,9 +43266,14 @@
         <v>0.5</v>
       </c>
       <c r="F355" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G355" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H355" s="54" t="n">
         <v>-3.5</v>
       </c>
-      <c r="G355" s="2" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="54" t="inlineStr">
@@ -41629,12 +43295,17 @@
         <v>7</v>
       </c>
       <c r="E356" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F356" s="54" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="G356" s="54" t="n">
         <v>0.3316</v>
       </c>
-      <c r="F356" s="54" t="n">
+      <c r="H356" s="54" t="n">
         <v>-2.32</v>
       </c>
-      <c r="G356" s="2" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="54" t="inlineStr">
@@ -41656,12 +43327,17 @@
         <v>15</v>
       </c>
       <c r="E357" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F357" s="54" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="G357" s="54" t="n">
         <v>0.3316</v>
       </c>
-      <c r="F357" s="54" t="n">
+      <c r="H357" s="54" t="n">
         <v>-4.97</v>
       </c>
-      <c r="G357" s="2" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="54" t="inlineStr">
@@ -41683,12 +43359,17 @@
         <v>14</v>
       </c>
       <c r="E358" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F358" s="54" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="G358" s="54" t="n">
         <v>0.3316</v>
       </c>
-      <c r="F358" s="54" t="n">
+      <c r="H358" s="54" t="n">
         <v>-4.64</v>
       </c>
-      <c r="G358" s="2" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="54" t="inlineStr">
@@ -41710,12 +43391,17 @@
         <v>4</v>
       </c>
       <c r="E359" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F359" s="54" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="G359" s="54" t="n">
         <v>0.3316</v>
       </c>
-      <c r="F359" s="54" t="n">
+      <c r="H359" s="54" t="n">
         <v>-1.33</v>
       </c>
-      <c r="G359" s="2" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="54" t="inlineStr">
@@ -41737,12 +43423,17 @@
         <v>10</v>
       </c>
       <c r="E360" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F360" s="54" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="G360" s="54" t="n">
         <v>1.6579</v>
       </c>
-      <c r="F360" s="54" t="n">
+      <c r="H360" s="54" t="n">
         <v>-16.58</v>
       </c>
-      <c r="G360" s="2" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="54" t="inlineStr">
@@ -41764,12 +43455,17 @@
         <v>91</v>
       </c>
       <c r="E361" s="54" t="n">
-        <v>0.3316</v>
+        <v>0.2</v>
       </c>
       <c r="F361" s="54" t="n">
-        <v>-30.17</v>
-      </c>
-      <c r="G361" s="2" t="n"/>
+        <v>1.105</v>
+      </c>
+      <c r="G361" s="54" t="n">
+        <v>0.2211</v>
+      </c>
+      <c r="H361" s="54" t="n">
+        <v>-20.12</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="53" t="inlineStr">
@@ -41794,9 +43490,14 @@
         <v>1</v>
       </c>
       <c r="F362" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G362" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H362" s="53" t="n">
         <v>10</v>
       </c>
-      <c r="G362" s="2" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="54" t="inlineStr">
@@ -41821,9 +43522,14 @@
         <v>0.5</v>
       </c>
       <c r="F363" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G363" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H363" s="54" t="n">
         <v>-5</v>
       </c>
-      <c r="G363" s="2" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="54" t="inlineStr">
@@ -41845,12 +43551,17 @@
         <v>5</v>
       </c>
       <c r="E364" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F364" s="54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G364" s="54" t="n">
         <v>0.345</v>
       </c>
-      <c r="F364" s="54" t="n">
+      <c r="H364" s="54" t="n">
         <v>-1.72</v>
       </c>
-      <c r="G364" s="2" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="54" t="inlineStr">
@@ -41872,12 +43583,17 @@
         <v>7</v>
       </c>
       <c r="E365" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F365" s="54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G365" s="54" t="n">
         <v>0.345</v>
       </c>
-      <c r="F365" s="54" t="n">
+      <c r="H365" s="54" t="n">
         <v>-2.41</v>
       </c>
-      <c r="G365" s="2" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="54" t="inlineStr">
@@ -41899,12 +43615,17 @@
         <v>10</v>
       </c>
       <c r="E366" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F366" s="54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G366" s="54" t="n">
         <v>0.345</v>
       </c>
-      <c r="F366" s="54" t="n">
+      <c r="H366" s="54" t="n">
         <v>-3.45</v>
       </c>
-      <c r="G366" s="2" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="54" t="inlineStr">
@@ -41926,12 +43647,17 @@
         <v>5</v>
       </c>
       <c r="E367" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F367" s="54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G367" s="54" t="n">
         <v>0.345</v>
       </c>
-      <c r="F367" s="54" t="n">
+      <c r="H367" s="54" t="n">
         <v>-1.72</v>
       </c>
-      <c r="G367" s="2" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="54" t="inlineStr">
@@ -41953,12 +43679,17 @@
         <v>12</v>
       </c>
       <c r="E368" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F368" s="54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G368" s="54" t="n">
         <v>1.725</v>
       </c>
-      <c r="F368" s="54" t="n">
+      <c r="H368" s="54" t="n">
         <v>-20.7</v>
       </c>
-      <c r="G368" s="2" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="54" t="inlineStr">
@@ -41980,12 +43711,17 @@
         <v>1</v>
       </c>
       <c r="E369" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F369" s="54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G369" s="54" t="n">
         <v>0.575</v>
       </c>
-      <c r="F369" s="54" t="n">
+      <c r="H369" s="54" t="n">
         <v>-0.57</v>
       </c>
-      <c r="G369" s="2" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="54" t="inlineStr">
@@ -42007,12 +43743,17 @@
         <v>1</v>
       </c>
       <c r="E370" s="54" t="n">
-        <v>0.345</v>
+        <v>0.2</v>
       </c>
       <c r="F370" s="54" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="G370" s="2" t="n"/>
+        <v>1.15</v>
+      </c>
+      <c r="G370" s="54" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H370" s="54" t="n">
+        <v>-0.23</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="53" t="inlineStr">
@@ -42037,9 +43778,14 @@
         <v>1</v>
       </c>
       <c r="F371" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G371" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H371" s="53" t="n">
         <v>13</v>
       </c>
-      <c r="G371" s="2" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="54" t="inlineStr">
@@ -42064,9 +43810,14 @@
         <v>0.5</v>
       </c>
       <c r="F372" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G372" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H372" s="54" t="n">
         <v>-4.5</v>
       </c>
-      <c r="G372" s="2" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="54" t="inlineStr">
@@ -42088,12 +43839,17 @@
         <v>5</v>
       </c>
       <c r="E373" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F373" s="54" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G373" s="54" t="n">
         <v>0.2864</v>
       </c>
-      <c r="F373" s="54" t="n">
+      <c r="H373" s="54" t="n">
         <v>-1.43</v>
       </c>
-      <c r="G373" s="2" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="54" t="inlineStr">
@@ -42115,12 +43871,17 @@
         <v>12</v>
       </c>
       <c r="E374" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F374" s="54" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G374" s="54" t="n">
         <v>0.2864</v>
       </c>
-      <c r="F374" s="54" t="n">
+      <c r="H374" s="54" t="n">
         <v>-3.44</v>
       </c>
-      <c r="G374" s="2" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="54" t="inlineStr">
@@ -42142,12 +43903,17 @@
         <v>9</v>
       </c>
       <c r="E375" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F375" s="54" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G375" s="54" t="n">
         <v>0.2864</v>
       </c>
-      <c r="F375" s="54" t="n">
+      <c r="H375" s="54" t="n">
         <v>-2.58</v>
       </c>
-      <c r="G375" s="2" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="54" t="inlineStr">
@@ -42169,12 +43935,17 @@
         <v>9</v>
       </c>
       <c r="E376" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F376" s="54" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G376" s="54" t="n">
         <v>1.4318</v>
       </c>
-      <c r="F376" s="54" t="n">
+      <c r="H376" s="54" t="n">
         <v>-12.89</v>
       </c>
-      <c r="G376" s="2" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="54" t="inlineStr">
@@ -42196,12 +43967,17 @@
         <v>4</v>
       </c>
       <c r="E377" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F377" s="54" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G377" s="54" t="n">
         <v>0.9545</v>
       </c>
-      <c r="F377" s="54" t="n">
+      <c r="H377" s="54" t="n">
         <v>-3.82</v>
       </c>
-      <c r="G377" s="2" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="54" t="inlineStr">
@@ -42223,12 +43999,17 @@
         <v>1</v>
       </c>
       <c r="E378" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F378" s="54" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G378" s="54" t="n">
         <v>0.4773</v>
       </c>
-      <c r="F378" s="54" t="n">
+      <c r="H378" s="54" t="n">
         <v>-0.48</v>
       </c>
-      <c r="G378" s="2" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="54" t="inlineStr">
@@ -42250,12 +44031,17 @@
         <v>40</v>
       </c>
       <c r="E379" s="54" t="n">
-        <v>0.2864</v>
+        <v>0.2</v>
       </c>
       <c r="F379" s="54" t="n">
-        <v>-11.45</v>
-      </c>
-      <c r="G379" s="2" t="n"/>
+        <v>0.955</v>
+      </c>
+      <c r="G379" s="54" t="n">
+        <v>0.1909</v>
+      </c>
+      <c r="H379" s="54" t="n">
+        <v>-7.64</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="53" t="inlineStr">
@@ -42280,9 +44066,14 @@
         <v>5</v>
       </c>
       <c r="F380" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G380" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G380" s="2" t="n"/>
+      <c r="H380" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="53" t="inlineStr">
@@ -42307,9 +44098,14 @@
         <v>1</v>
       </c>
       <c r="F381" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G381" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H381" s="53" t="n">
         <v>10</v>
       </c>
-      <c r="G381" s="2" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="54" t="inlineStr">
@@ -42334,9 +44130,14 @@
         <v>0.5</v>
       </c>
       <c r="F382" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G382" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H382" s="54" t="n">
         <v>-1</v>
       </c>
-      <c r="G382" s="2" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="54" t="inlineStr">
@@ -42358,12 +44159,17 @@
         <v>1</v>
       </c>
       <c r="E383" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F383" s="54" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="G383" s="54" t="n">
         <v>0.55</v>
       </c>
-      <c r="F383" s="54" t="n">
+      <c r="H383" s="54" t="n">
         <v>-0.55</v>
       </c>
-      <c r="G383" s="2" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="54" t="inlineStr">
@@ -42385,12 +44191,17 @@
         <v>7</v>
       </c>
       <c r="E384" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F384" s="54" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="G384" s="54" t="n">
         <v>2.75</v>
       </c>
-      <c r="F384" s="54" t="n">
+      <c r="H384" s="54" t="n">
         <v>-19.25</v>
       </c>
-      <c r="G384" s="2" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="54" t="inlineStr">
@@ -42412,12 +44223,17 @@
         <v>4</v>
       </c>
       <c r="E385" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F385" s="54" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="G385" s="54" t="n">
         <v>0.9167</v>
       </c>
-      <c r="F385" s="54" t="n">
+      <c r="H385" s="54" t="n">
         <v>-3.67</v>
       </c>
-      <c r="G385" s="2" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="54" t="inlineStr">
@@ -42439,12 +44255,17 @@
         <v>3</v>
       </c>
       <c r="E386" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F386" s="54" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="G386" s="54" t="n">
         <v>0.9167</v>
       </c>
-      <c r="F386" s="54" t="n">
+      <c r="H386" s="54" t="n">
         <v>-2.75</v>
       </c>
-      <c r="G386" s="2" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="53" t="inlineStr">
@@ -42469,9 +44290,14 @@
         <v>5</v>
       </c>
       <c r="F387" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G387" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G387" s="2" t="n"/>
+      <c r="H387" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="53" t="inlineStr">
@@ -42496,9 +44322,14 @@
         <v>1</v>
       </c>
       <c r="F388" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G388" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H388" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="G388" s="2" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="54" t="inlineStr">
@@ -42523,9 +44354,14 @@
         <v>0.5</v>
       </c>
       <c r="F389" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G389" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H389" s="54" t="n">
         <v>-1</v>
       </c>
-      <c r="G389" s="2" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="54" t="inlineStr">
@@ -42547,12 +44383,17 @@
         <v>1</v>
       </c>
       <c r="E390" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F390" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G390" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F390" s="54" t="n">
+      <c r="H390" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G390" s="2" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="54" t="inlineStr">
@@ -42574,12 +44415,17 @@
         <v>2</v>
       </c>
       <c r="E391" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F391" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G391" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F391" s="54" t="n">
+      <c r="H391" s="54" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G391" s="2" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="54" t="inlineStr">
@@ -42601,12 +44447,17 @@
         <v>3</v>
       </c>
       <c r="E392" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F392" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G392" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F392" s="54" t="n">
+      <c r="H392" s="54" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G392" s="2" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="54" t="inlineStr">
@@ -42628,12 +44479,17 @@
         <v>3</v>
       </c>
       <c r="E393" s="54" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F393" s="54" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G393" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G393" s="54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H393" s="54" t="n">
+        <v>-1.2</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="53" t="inlineStr">
@@ -42658,9 +44514,14 @@
         <v>5</v>
       </c>
       <c r="F394" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G394" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G394" s="2" t="n"/>
+      <c r="H394" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="53" t="inlineStr">
@@ -42685,9 +44546,14 @@
         <v>1</v>
       </c>
       <c r="F395" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G395" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H395" s="53" t="n">
         <v>14</v>
       </c>
-      <c r="G395" s="2" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="54" t="inlineStr">
@@ -42712,9 +44578,14 @@
         <v>0.5</v>
       </c>
       <c r="F396" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G396" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H396" s="54" t="n">
         <v>-4</v>
       </c>
-      <c r="G396" s="2" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="54" t="inlineStr">
@@ -42739,9 +44610,14 @@
         <v>0.3</v>
       </c>
       <c r="F397" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G397" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H397" s="54" t="n">
         <v>-0.9</v>
       </c>
-      <c r="G397" s="2" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="54" t="inlineStr">
@@ -42766,9 +44642,14 @@
         <v>0.3</v>
       </c>
       <c r="F398" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G398" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H398" s="54" t="n">
         <v>-2.4</v>
       </c>
-      <c r="G398" s="2" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="54" t="inlineStr">
@@ -42793,9 +44674,14 @@
         <v>0.3</v>
       </c>
       <c r="F399" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G399" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H399" s="54" t="n">
         <v>-0.9</v>
       </c>
-      <c r="G399" s="2" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="54" t="inlineStr">
@@ -42820,9 +44706,14 @@
         <v>1.5</v>
       </c>
       <c r="F400" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G400" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H400" s="54" t="n">
         <v>-4.5</v>
       </c>
-      <c r="G400" s="2" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="53" t="inlineStr">
@@ -42847,9 +44738,14 @@
         <v>5</v>
       </c>
       <c r="F401" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G401" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G401" s="2" t="n"/>
+      <c r="H401" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="53" t="inlineStr">
@@ -42874,9 +44770,14 @@
         <v>1</v>
       </c>
       <c r="F402" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G402" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H402" s="53" t="n">
         <v>15</v>
       </c>
-      <c r="G402" s="2" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="54" t="inlineStr">
@@ -42901,9 +44802,14 @@
         <v>0.5</v>
       </c>
       <c r="F403" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G403" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H403" s="54" t="n">
         <v>-1</v>
       </c>
-      <c r="G403" s="2" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="54" t="inlineStr">
@@ -42925,12 +44831,17 @@
         <v>4</v>
       </c>
       <c r="E404" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F404" s="54" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="G404" s="54" t="n">
         <v>0.3882</v>
       </c>
-      <c r="F404" s="54" t="n">
+      <c r="H404" s="54" t="n">
         <v>-1.55</v>
       </c>
-      <c r="G404" s="2" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="54" t="inlineStr">
@@ -42952,12 +44863,17 @@
         <v>15</v>
       </c>
       <c r="E405" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F405" s="54" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="G405" s="54" t="n">
         <v>1.9412</v>
       </c>
-      <c r="F405" s="54" t="n">
+      <c r="H405" s="54" t="n">
         <v>-29.12</v>
       </c>
-      <c r="G405" s="2" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="54" t="inlineStr">
@@ -42979,12 +44895,17 @@
         <v>14</v>
       </c>
       <c r="E406" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F406" s="54" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="G406" s="54" t="n">
         <v>1.2941</v>
       </c>
-      <c r="F406" s="54" t="n">
+      <c r="H406" s="54" t="n">
         <v>-18.12</v>
       </c>
-      <c r="G406" s="2" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="53" t="inlineStr">
@@ -43009,9 +44930,14 @@
         <v>1</v>
       </c>
       <c r="F407" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G407" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H407" s="53" t="n">
         <v>7</v>
       </c>
-      <c r="G407" s="2" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="54" t="inlineStr">
@@ -43036,9 +44962,14 @@
         <v>0.5</v>
       </c>
       <c r="F408" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G408" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H408" s="54" t="n">
         <v>-2</v>
       </c>
-      <c r="G408" s="2" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="54" t="inlineStr">
@@ -43060,12 +44991,17 @@
         <v>3</v>
       </c>
       <c r="E409" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F409" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G409" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F409" s="54" t="n">
+      <c r="H409" s="54" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G409" s="2" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="54" t="inlineStr">
@@ -43087,12 +45023,17 @@
         <v>7</v>
       </c>
       <c r="E410" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F410" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G410" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F410" s="54" t="n">
+      <c r="H410" s="54" t="n">
         <v>-4.2</v>
       </c>
-      <c r="G410" s="2" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="54" t="inlineStr">
@@ -43114,12 +45055,17 @@
         <v>5</v>
       </c>
       <c r="E411" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F411" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G411" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F411" s="54" t="n">
+      <c r="H411" s="54" t="n">
         <v>-3</v>
       </c>
-      <c r="G411" s="2" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="54" t="inlineStr">
@@ -43141,12 +45087,17 @@
         <v>12</v>
       </c>
       <c r="E412" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F412" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G412" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="F412" s="54" t="n">
+      <c r="H412" s="54" t="n">
         <v>-36</v>
       </c>
-      <c r="G412" s="2" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="54" t="inlineStr">
@@ -43168,12 +45119,17 @@
         <v>18</v>
       </c>
       <c r="E413" s="54" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F413" s="54" t="n">
-        <v>-10.8</v>
-      </c>
-      <c r="G413" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G413" s="54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H413" s="54" t="n">
+        <v>-7.2</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="53" t="inlineStr">
@@ -43198,9 +45154,14 @@
         <v>1</v>
       </c>
       <c r="F414" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G414" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H414" s="53" t="n">
         <v>9</v>
       </c>
-      <c r="G414" s="2" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="54" t="inlineStr">
@@ -43225,9 +45186,14 @@
         <v>0.5</v>
       </c>
       <c r="F415" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G415" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H415" s="54" t="n">
         <v>-1</v>
       </c>
-      <c r="G415" s="2" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="54" t="inlineStr">
@@ -43249,12 +45215,17 @@
         <v>4</v>
       </c>
       <c r="E416" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F416" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G416" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F416" s="54" t="n">
+      <c r="H416" s="54" t="n">
         <v>-2.4</v>
       </c>
-      <c r="G416" s="2" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="54" t="inlineStr">
@@ -43276,12 +45247,17 @@
         <v>7</v>
       </c>
       <c r="E417" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F417" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G417" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="F417" s="54" t="n">
+      <c r="H417" s="54" t="n">
         <v>-4.2</v>
       </c>
-      <c r="G417" s="2" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="54" t="inlineStr">
@@ -43303,12 +45279,17 @@
         <v>3</v>
       </c>
       <c r="E418" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F418" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G418" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="F418" s="54" t="n">
+      <c r="H418" s="54" t="n">
         <v>-9</v>
       </c>
-      <c r="G418" s="2" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="54" t="inlineStr">
@@ -43330,12 +45311,17 @@
         <v>77</v>
       </c>
       <c r="E419" s="54" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F419" s="54" t="n">
-        <v>-46.2</v>
-      </c>
-      <c r="G419" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G419" s="54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H419" s="54" t="n">
+        <v>-30.8</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="53" t="inlineStr">
@@ -43360,9 +45346,14 @@
         <v>1</v>
       </c>
       <c r="F420" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G420" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H420" s="53" t="n">
         <v>11</v>
       </c>
-      <c r="G420" s="2" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="54" t="inlineStr">
@@ -43387,9 +45378,14 @@
         <v>0.5</v>
       </c>
       <c r="F421" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G421" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H421" s="54" t="n">
         <v>-5</v>
       </c>
-      <c r="G421" s="2" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="54" t="inlineStr">
@@ -43414,9 +45410,14 @@
         <v>0.3</v>
       </c>
       <c r="F422" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G422" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H422" s="54" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G422" s="2" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="54" t="inlineStr">
@@ -43441,9 +45442,14 @@
         <v>0.3</v>
       </c>
       <c r="F423" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G423" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H423" s="54" t="n">
         <v>-3.9</v>
       </c>
-      <c r="G423" s="2" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="54" t="inlineStr">
@@ -43468,9 +45474,14 @@
         <v>0.3</v>
       </c>
       <c r="F424" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G424" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H424" s="54" t="n">
         <v>-4.5</v>
       </c>
-      <c r="G424" s="2" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="54" t="inlineStr">
@@ -43495,9 +45506,14 @@
         <v>0.3</v>
       </c>
       <c r="F425" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G425" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H425" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G425" s="2" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="54" t="inlineStr">
@@ -43522,9 +45538,14 @@
         <v>1.5</v>
       </c>
       <c r="F426" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G426" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H426" s="54" t="n">
         <v>-16.5</v>
       </c>
-      <c r="G426" s="2" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="54" t="inlineStr">
@@ -43546,12 +45567,17 @@
         <v>107</v>
       </c>
       <c r="E427" s="54" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F427" s="54" t="n">
-        <v>-32.1</v>
-      </c>
-      <c r="G427" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G427" s="54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H427" s="54" t="n">
+        <v>-21.4</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="53" t="inlineStr">
@@ -43576,9 +45602,14 @@
         <v>5</v>
       </c>
       <c r="F428" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G428" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G428" s="2" t="n"/>
+      <c r="H428" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="53" t="inlineStr">
@@ -43603,9 +45634,14 @@
         <v>1</v>
       </c>
       <c r="F429" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G429" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H429" s="53" t="n">
         <v>14</v>
       </c>
-      <c r="G429" s="2" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="54" t="inlineStr">
@@ -43630,9 +45666,14 @@
         <v>0.5</v>
       </c>
       <c r="F430" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G430" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H430" s="54" t="n">
         <v>-3.5</v>
       </c>
-      <c r="G430" s="2" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="54" t="inlineStr">
@@ -43654,12 +45695,17 @@
         <v>4</v>
       </c>
       <c r="E431" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F431" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G431" s="54" t="n">
         <v>0.3143</v>
       </c>
-      <c r="F431" s="54" t="n">
+      <c r="H431" s="54" t="n">
         <v>-1.26</v>
       </c>
-      <c r="G431" s="2" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="54" t="inlineStr">
@@ -43681,12 +45727,17 @@
         <v>16</v>
       </c>
       <c r="E432" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F432" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G432" s="54" t="n">
         <v>0.3143</v>
       </c>
-      <c r="F432" s="54" t="n">
+      <c r="H432" s="54" t="n">
         <v>-5.03</v>
       </c>
-      <c r="G432" s="2" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="54" t="inlineStr">
@@ -43708,12 +45759,17 @@
         <v>5</v>
       </c>
       <c r="E433" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F433" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G433" s="54" t="n">
         <v>0.3143</v>
       </c>
-      <c r="F433" s="54" t="n">
+      <c r="H433" s="54" t="n">
         <v>-1.57</v>
       </c>
-      <c r="G433" s="2" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="54" t="inlineStr">
@@ -43735,12 +45791,17 @@
         <v>8</v>
       </c>
       <c r="E434" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F434" s="54" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="G434" s="54" t="n">
         <v>1.5714</v>
       </c>
-      <c r="F434" s="54" t="n">
+      <c r="H434" s="54" t="n">
         <v>-12.57</v>
       </c>
-      <c r="G434" s="2" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="53" t="inlineStr">
@@ -43765,9 +45826,14 @@
         <v>5</v>
       </c>
       <c r="F435" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G435" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G435" s="2" t="n"/>
+      <c r="H435" s="53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="53" t="inlineStr">
@@ -43792,9 +45858,14 @@
         <v>1</v>
       </c>
       <c r="F436" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G436" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H436" s="53" t="n">
         <v>15</v>
       </c>
-      <c r="G436" s="2" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="54" t="inlineStr">
@@ -43819,9 +45890,14 @@
         <v>0.5</v>
       </c>
       <c r="F437" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G437" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H437" s="54" t="n">
         <v>-2.5</v>
       </c>
-      <c r="G437" s="2" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="54" t="inlineStr">
@@ -43843,12 +45919,17 @@
         <v>1</v>
       </c>
       <c r="E438" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F438" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G438" s="54" t="n">
         <v>0.33</v>
       </c>
-      <c r="F438" s="54" t="n">
+      <c r="H438" s="54" t="n">
         <v>-0.33</v>
       </c>
-      <c r="G438" s="2" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="54" t="inlineStr">
@@ -43870,12 +45951,17 @@
         <v>7</v>
       </c>
       <c r="E439" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F439" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G439" s="54" t="n">
         <v>0.33</v>
       </c>
-      <c r="F439" s="54" t="n">
+      <c r="H439" s="54" t="n">
         <v>-2.31</v>
       </c>
-      <c r="G439" s="2" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="54" t="inlineStr">
@@ -43897,12 +45983,17 @@
         <v>16</v>
       </c>
       <c r="E440" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F440" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G440" s="54" t="n">
         <v>0.33</v>
       </c>
-      <c r="F440" s="54" t="n">
+      <c r="H440" s="54" t="n">
         <v>-5.28</v>
       </c>
-      <c r="G440" s="2" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="54" t="inlineStr">
@@ -43924,12 +46015,17 @@
         <v>1</v>
       </c>
       <c r="E441" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F441" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G441" s="54" t="n">
         <v>0.33</v>
       </c>
-      <c r="F441" s="54" t="n">
+      <c r="H441" s="54" t="n">
         <v>-0.33</v>
       </c>
-      <c r="G441" s="2" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="54" t="inlineStr">
@@ -43951,18 +46047,23 @@
         <v>11</v>
       </c>
       <c r="E442" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F442" s="54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G442" s="54" t="n">
         <v>1.65</v>
       </c>
-      <c r="F442" s="54" t="n">
+      <c r="H442" s="54" t="n">
         <v>-18.15</v>
       </c>
-      <c r="G442" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G51"/>
+  <autoFilter ref="A2:H51"/>
   <mergeCells count="2">
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/historico/semanas_313-317.xlsx
+++ b/data/historico/semanas_313-317.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B22" s="43" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="C22" s="43" t="inlineStr">
